--- a/Data/National Accounts/PSA-08AFF_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-08AFF_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9B2247-C7FD-437A-9860-EAC8A91F7E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16976DA2-E70A-4E8E-8D39-A2C223FB7FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="AFF" sheetId="8" r:id="rId1"/>
@@ -732,10 +732,10 @@
     <t>Table 9.7 Gross Value Added in Agriculture, Forestry, and Fishing, by Industry</t>
   </si>
   <si>
-    <t>As of January 2026</t>
+    <t>Q1 2000 to Q4 2025</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -771,10 +771,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1279,7 +1281,7 @@
     </row>
     <row r="3" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="CP3" s="13"/>
       <c r="CQ3" s="13"/>
@@ -1327,7 +1329,7 @@
     </row>
     <row r="6" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CP6" s="13"/>
       <c r="CQ6" s="13"/>
@@ -2157,19 +2159,19 @@
         <v>167825.30170241185</v>
       </c>
       <c r="CT12" s="16">
-        <v>129393.76406607799</v>
+        <v>128486.6831450801</v>
       </c>
       <c r="CU12" s="16">
-        <v>96315.129520553266</v>
+        <v>96532.029486195679</v>
       </c>
       <c r="CV12" s="16">
-        <v>71842.727737423396</v>
+        <v>71887.30206569031</v>
       </c>
       <c r="CW12" s="16">
-        <v>157327.17612048832</v>
+        <v>157519.26156941528</v>
       </c>
       <c r="CX12" s="16">
-        <v>104873.58053502362</v>
+        <v>104292.72361587436</v>
       </c>
       <c r="CY12" s="16">
         <v>78058.377851620695</v>
@@ -2483,7 +2485,7 @@
         <v>31462.848273711112</v>
       </c>
       <c r="CW13" s="16">
-        <v>23699.249068947975</v>
+        <v>23699.250037483518</v>
       </c>
       <c r="CX13" s="16">
         <v>32515.502213688065</v>
@@ -2495,7 +2497,7 @@
         <v>32225.327425235362</v>
       </c>
       <c r="DA13" s="16">
-        <v>30656.624291376567</v>
+        <v>30523.532859554041</v>
       </c>
     </row>
     <row r="14" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -3117,7 +3119,7 @@
         <v>301.90045643666735</v>
       </c>
       <c r="CW15" s="16">
-        <v>14886.44611190242</v>
+        <v>14919.685255298136</v>
       </c>
       <c r="CX15" s="16">
         <v>17585.906603117866</v>
@@ -3425,16 +3427,16 @@
         <v>38637.203632417848</v>
       </c>
       <c r="CT16" s="16">
-        <v>39340.759417844965</v>
+        <v>39733.915781100033</v>
       </c>
       <c r="CU16" s="16">
-        <v>41168.812599998862</v>
+        <v>41332.75479483739</v>
       </c>
       <c r="CV16" s="16">
-        <v>41996.264608541722</v>
+        <v>42557.576797387228</v>
       </c>
       <c r="CW16" s="16">
-        <v>36969.557079683291</v>
+        <v>37840.439984129029</v>
       </c>
       <c r="CX16" s="16">
         <v>35744.413681306665</v>
@@ -3446,7 +3448,7 @@
         <v>31025.95067958357</v>
       </c>
       <c r="DA16" s="16">
-        <v>32693.777301190436</v>
+        <v>32685.266917563386</v>
       </c>
     </row>
     <row r="17" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -3745,13 +3747,13 @@
         <v>6478.039390429285</v>
       </c>
       <c r="CU17" s="16">
-        <v>17124.073357142344</v>
+        <v>17133.407115675775</v>
       </c>
       <c r="CV17" s="16">
-        <v>2587.0774900528932</v>
+        <v>2587.7425266597065</v>
       </c>
       <c r="CW17" s="16">
-        <v>10140.410761750458</v>
+        <v>10177.558233664782</v>
       </c>
       <c r="CX17" s="16">
         <v>7070.8177577421548</v>
@@ -4376,16 +4378,16 @@
         <v>4198.9531827400488</v>
       </c>
       <c r="CT19" s="16">
-        <v>3446.7661225851894</v>
+        <v>3344.5381197194683</v>
       </c>
       <c r="CU19" s="16">
-        <v>995.73357976851241</v>
+        <v>988.44449113663939</v>
       </c>
       <c r="CV19" s="16">
-        <v>870.83864329800303</v>
+        <v>865.72864091281122</v>
       </c>
       <c r="CW19" s="16">
-        <v>6495.4172366026005</v>
+        <v>6450.8651274070271</v>
       </c>
       <c r="CX19" s="16">
         <v>8385.7465915252669</v>
@@ -4693,28 +4695,28 @@
         <v>10064.952842221626</v>
       </c>
       <c r="CT20" s="16">
-        <v>5551.5013316164741</v>
+        <v>5549.2169536647125</v>
       </c>
       <c r="CU20" s="16">
-        <v>6169.4129196843123</v>
+        <v>6243.7429725011079</v>
       </c>
       <c r="CV20" s="16">
-        <v>9448.3944383293583</v>
+        <v>9899.8958284107885</v>
       </c>
       <c r="CW20" s="16">
-        <v>12571.878466987753</v>
+        <v>12661.64344003221</v>
       </c>
       <c r="CX20" s="16">
-        <v>4576.9596713777046</v>
+        <v>4575.5506547884333</v>
       </c>
       <c r="CY20" s="16">
-        <v>7169.7198089655594</v>
+        <v>7230.1843606600205</v>
       </c>
       <c r="CZ20" s="16">
-        <v>9909.5002604842284</v>
+        <v>10348.265590934563</v>
       </c>
       <c r="DA20" s="16">
-        <v>10193.109681950104</v>
+        <v>10181.779788558068</v>
       </c>
     </row>
     <row r="21" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -5031,7 +5033,7 @@
         <v>3032.5891445264024</v>
       </c>
       <c r="DA21" s="16">
-        <v>5131.3390809735993</v>
+        <v>5130.2907858419831</v>
       </c>
     </row>
     <row r="22" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -5333,7 +5335,7 @@
         <v>499.3164890215001</v>
       </c>
       <c r="CV22" s="16">
-        <v>900.45064830652495</v>
+        <v>887.30632186730008</v>
       </c>
       <c r="CW22" s="16">
         <v>1394.776933157025</v>
@@ -5650,10 +5652,10 @@
         <v>226.36044104935428</v>
       </c>
       <c r="CV23" s="16">
-        <v>455.8825099960452</v>
+        <v>455.75518799605902</v>
       </c>
       <c r="CW23" s="16">
-        <v>529.17596214928426</v>
+        <v>529.38467267529563</v>
       </c>
       <c r="CX23" s="16">
         <v>337.3215946158623</v>
@@ -5964,10 +5966,10 @@
         <v>273.90141816802134</v>
       </c>
       <c r="CU24" s="16">
-        <v>208.226043521522</v>
+        <v>208.24693418197648</v>
       </c>
       <c r="CV24" s="16">
-        <v>503.69926311947711</v>
+        <v>515.19762790589971</v>
       </c>
       <c r="CW24" s="16">
         <v>1197.5174726097252</v>
@@ -5979,7 +5981,7 @@
         <v>169.75175773946376</v>
       </c>
       <c r="CZ24" s="16">
-        <v>428.39140598088852</v>
+        <v>438.17065526314946</v>
       </c>
       <c r="DA24" s="16">
         <v>711.51753459193787</v>
@@ -6278,28 +6280,28 @@
         <v>35511.307194550951</v>
       </c>
       <c r="CT25" s="16">
-        <v>31605.622291191357</v>
+        <v>31736.086143822384</v>
       </c>
       <c r="CU25" s="16">
-        <v>20677.824017330255</v>
+        <v>20795.656763998635</v>
       </c>
       <c r="CV25" s="16">
-        <v>38630.903451538616</v>
+        <v>38232.124062054543</v>
       </c>
       <c r="CW25" s="16">
-        <v>37711.602596696423</v>
+        <v>37705.990994205247</v>
       </c>
       <c r="CX25" s="16">
-        <v>33204.550465377906</v>
+        <v>33368.155385607708</v>
       </c>
       <c r="CY25" s="16">
-        <v>21883.291122670096</v>
+        <v>22014.084617297769</v>
       </c>
       <c r="CZ25" s="16">
-        <v>36738.638707731268</v>
+        <v>36303.094673215121</v>
       </c>
       <c r="DA25" s="16">
-        <v>41173.367012181188</v>
+        <v>40931.95821556414</v>
       </c>
     </row>
     <row r="26" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -6595,28 +6597,28 @@
         <v>87814.502545770694</v>
       </c>
       <c r="CT26" s="16">
-        <v>71253.451770503161</v>
+        <v>71458.838501004328</v>
       </c>
       <c r="CU26" s="16">
-        <v>82370.513857531187</v>
+        <v>82538.904795710958</v>
       </c>
       <c r="CV26" s="16">
-        <v>77769.497196752345</v>
+        <v>77148.085978079413</v>
       </c>
       <c r="CW26" s="16">
-        <v>88085.483398739627</v>
+        <v>88087.868730093149</v>
       </c>
       <c r="CX26" s="16">
-        <v>80126.373360306839</v>
+        <v>80269.900563255185</v>
       </c>
       <c r="CY26" s="16">
-        <v>87382.569840776181</v>
+        <v>87171.200041119795</v>
       </c>
       <c r="CZ26" s="16">
-        <v>80274.289111519844</v>
+        <v>79739.383731123002</v>
       </c>
       <c r="DA26" s="16">
-        <v>92767.826292240468</v>
+        <v>92749.470311403391</v>
       </c>
     </row>
     <row r="27" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -6912,7 +6914,7 @@
         <v>73509.826706937834</v>
       </c>
       <c r="CT27" s="16">
-        <v>86350.405458862486</v>
+        <v>86350.405458864028</v>
       </c>
       <c r="CU27" s="16">
         <v>55572.67801668153</v>
@@ -6924,16 +6926,16 @@
         <v>76764.057805311051</v>
       </c>
       <c r="CX27" s="16">
-        <v>101184.12847089936</v>
+        <v>101151.23688912546</v>
       </c>
       <c r="CY27" s="16">
-        <v>60540.985732242028</v>
+        <v>60530.799808798736</v>
       </c>
       <c r="CZ27" s="16">
-        <v>65556.871587749716</v>
+        <v>65288.405196156906</v>
       </c>
       <c r="DA27" s="16">
-        <v>87452.520285574603</v>
+        <v>87443.654284111981</v>
       </c>
     </row>
     <row r="28" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -7866,25 +7868,25 @@
         <v>66519.367897588207</v>
       </c>
       <c r="CU30" s="16">
-        <v>54043.031545649748</v>
+        <v>54169.773401606799</v>
       </c>
       <c r="CV30" s="16">
-        <v>64314.721420448855</v>
+        <v>64411.193474179076</v>
       </c>
       <c r="CW30" s="16">
-        <v>69214.449408730463</v>
+        <v>68864.352272685486</v>
       </c>
       <c r="CX30" s="16">
-        <v>68730.927416053528</v>
+        <v>69249.112139010671</v>
       </c>
       <c r="CY30" s="16">
-        <v>56430.071772944313</v>
+        <v>56576.733658245212</v>
       </c>
       <c r="CZ30" s="16">
-        <v>65754.611399258443</v>
+        <v>65985.771629039518</v>
       </c>
       <c r="DA30" s="16">
-        <v>76386.122121029024</v>
+        <v>76196.58114435288</v>
       </c>
     </row>
     <row r="31" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -8498,28 +8500,28 @@
         <v>703599.19645156688</v>
       </c>
       <c r="CT33" s="18">
-        <v>614066.90701822203</v>
+        <v>613784.32066279557</v>
       </c>
       <c r="CU33" s="18">
-        <v>536544.23294451309</v>
+        <v>537414.4362591781</v>
       </c>
       <c r="CV33" s="18">
-        <v>548065.96194869815</v>
+        <v>548193.41305203398</v>
       </c>
       <c r="CW33" s="18">
-        <v>703321.49107169453</v>
+        <v>704146.9451761049</v>
       </c>
       <c r="CX33" s="18">
-        <v>626803.95607463922</v>
+        <v>627014.1154032622</v>
       </c>
       <c r="CY33" s="18">
-        <v>563588.84775933588</v>
+        <v>563705.21196785942</v>
       </c>
       <c r="CZ33" s="18">
-        <v>526660.26461287297</v>
+        <v>526101.0536158809</v>
       </c>
       <c r="DA33" s="18">
-        <v>690324.0956606851</v>
+        <v>689711.94390111906</v>
       </c>
     </row>
     <row r="34" spans="1:105" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8684,7 +8686,7 @@
     </row>
     <row r="40" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="CP40" s="13"/>
       <c r="CQ40" s="13"/>
@@ -8732,7 +8734,7 @@
     </row>
     <row r="43" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CP43" s="13"/>
       <c r="CQ43" s="13"/>
@@ -9574,7 +9576,7 @@
         <v>133649.04952631457</v>
       </c>
       <c r="CX49" s="16">
-        <v>94195.242824872199</v>
+        <v>93673.516883304488</v>
       </c>
       <c r="CY49" s="16">
         <v>86130.266095967381</v>
@@ -9888,7 +9890,7 @@
         <v>32000.28815175905</v>
       </c>
       <c r="CW50" s="16">
-        <v>23639.764913381026</v>
+        <v>23639.765878529448</v>
       </c>
       <c r="CX50" s="16">
         <v>31601.918678529066</v>
@@ -9900,7 +9902,7 @@
         <v>31065.135888783781</v>
       </c>
       <c r="DA50" s="16">
-        <v>24382.757067571853</v>
+        <v>24277.008031071346</v>
       </c>
     </row>
     <row r="51" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -10522,7 +10524,7 @@
         <v>284.72145981465184</v>
       </c>
       <c r="CW52" s="16">
-        <v>6537.3851793278509</v>
+        <v>6502.8411452129612</v>
       </c>
       <c r="CX52" s="16">
         <v>15552.335286009653</v>
@@ -12098,25 +12100,25 @@
         <v>5847.9412760270116</v>
       </c>
       <c r="CT57" s="16">
-        <v>3419.8023063024111</v>
+        <v>3419.3993161726767</v>
       </c>
       <c r="CU57" s="16">
         <v>5147.1783710561031</v>
       </c>
       <c r="CV57" s="16">
-        <v>4373.8059039314194</v>
+        <v>4582.814780239195</v>
       </c>
       <c r="CW57" s="16">
         <v>5350.6414849613329</v>
       </c>
       <c r="CX57" s="16">
-        <v>3419.3219698602361</v>
+        <v>3418.124400121269</v>
       </c>
       <c r="CY57" s="16">
         <v>5180.8028578876902</v>
       </c>
       <c r="CZ57" s="16">
-        <v>4141.8221484096293</v>
+        <v>4349.2633941083413</v>
       </c>
       <c r="DA57" s="16">
         <v>5203.6456562477179</v>
@@ -12738,7 +12740,7 @@
         <v>547.93988686201715</v>
       </c>
       <c r="CV59" s="16">
-        <v>415.46302290529508</v>
+        <v>409.39082768451851</v>
       </c>
       <c r="CW59" s="16">
         <v>560.49077830186854</v>
@@ -13055,10 +13057,10 @@
         <v>397.76375513695336</v>
       </c>
       <c r="CV60" s="16">
-        <v>317.03759599523403</v>
+        <v>316.94866735336302</v>
       </c>
       <c r="CW60" s="16">
-        <v>505.67393133656492</v>
+        <v>505.87324416034494</v>
       </c>
       <c r="CX60" s="16">
         <v>398.22856906690197</v>
@@ -13683,16 +13685,16 @@
         <v>25566.321123593025</v>
       </c>
       <c r="CT62" s="16">
-        <v>25649.491366823924</v>
+        <v>25768.846255837132</v>
       </c>
       <c r="CU62" s="16">
         <v>21936.519363191015</v>
       </c>
       <c r="CV62" s="16">
-        <v>18565.152054584658</v>
+        <v>18373.382547636844</v>
       </c>
       <c r="CW62" s="16">
-        <v>24109.022154153201</v>
+        <v>24127.701095584496</v>
       </c>
       <c r="CX62" s="16">
         <v>26148.248573075434</v>
@@ -13701,10 +13703,10 @@
         <v>23210.922585651337</v>
       </c>
       <c r="CZ62" s="16">
-        <v>17916.253848387769</v>
+        <v>17720.721958285445</v>
       </c>
       <c r="DA62" s="16">
-        <v>23952.727713820947</v>
+        <v>23946.930747284736</v>
       </c>
     </row>
     <row r="63" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -14000,28 +14002,28 @@
         <v>49739.325916925387</v>
       </c>
       <c r="CT63" s="16">
-        <v>45350.017181524279</v>
+        <v>45408.730422741646</v>
       </c>
       <c r="CU63" s="16">
-        <v>45333.023591629404</v>
+        <v>45347.93151782066</v>
       </c>
       <c r="CV63" s="16">
-        <v>43494.056673705869</v>
+        <v>43395.271200082119</v>
       </c>
       <c r="CW63" s="16">
-        <v>46798.35636825391</v>
+        <v>46799.624642459763</v>
       </c>
       <c r="CX63" s="16">
-        <v>44291.377023039298</v>
+        <v>44346.576119351172</v>
       </c>
       <c r="CY63" s="16">
-        <v>42763.492844920023</v>
+        <v>42769.746286120964</v>
       </c>
       <c r="CZ63" s="16">
-        <v>42797.288851189107</v>
+        <v>42707.327899158496</v>
       </c>
       <c r="DA63" s="16">
-        <v>47517.841788350459</v>
+        <v>47539.458717893867</v>
       </c>
     </row>
     <row r="64" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -14329,7 +14331,7 @@
         <v>61537.104335505865</v>
       </c>
       <c r="CX64" s="16">
-        <v>59123.722630163567</v>
+        <v>59102.058050045031</v>
       </c>
       <c r="CY64" s="16">
         <v>47730.897014201953</v>
@@ -15271,25 +15273,25 @@
         <v>45288.208702297547</v>
       </c>
       <c r="CU67" s="16">
-        <v>43466.865105178091</v>
+        <v>43433.801651921996</v>
       </c>
       <c r="CV67" s="16">
-        <v>47967.053077737815</v>
+        <v>48003.769730042855</v>
       </c>
       <c r="CW67" s="16">
-        <v>65255.427058363333</v>
+        <v>64925.936368500566</v>
       </c>
       <c r="CX67" s="16">
-        <v>45945.862432217429</v>
+        <v>46253.436601615162</v>
       </c>
       <c r="CY67" s="16">
-        <v>41527.106264799397</v>
+        <v>41568.961601757881</v>
       </c>
       <c r="CZ67" s="16">
-        <v>46758.060648620158</v>
+        <v>46764.12878669452</v>
       </c>
       <c r="DA67" s="16">
-        <v>67908.094439341527</v>
+        <v>67981.303807689488</v>
       </c>
     </row>
     <row r="68" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -15903,28 +15905,28 @@
         <v>532316.91804404301</v>
       </c>
       <c r="CT70" s="18">
-        <v>446899.32196405792</v>
+        <v>447076.98710415873</v>
       </c>
       <c r="CU70" s="18">
-        <v>408057.76515713695</v>
+        <v>408039.60963007214</v>
       </c>
       <c r="CV70" s="18">
-        <v>399493.16601983469</v>
+        <v>399442.17544401332</v>
       </c>
       <c r="CW70" s="18">
-        <v>523784.27977776574</v>
+        <v>523440.39254739753</v>
       </c>
       <c r="CX70" s="18">
-        <v>456879.88893348817</v>
+        <v>456698.07410777261</v>
       </c>
       <c r="CY70" s="18">
-        <v>436443.61944668175</v>
+        <v>436491.72822484112</v>
       </c>
       <c r="CZ70" s="18">
-        <v>410961.54188153578</v>
+        <v>410889.55842317583</v>
       </c>
       <c r="DA70" s="18">
-        <v>528825.65422774269</v>
+        <v>528808.93452259735</v>
       </c>
     </row>
     <row r="71" spans="1:105" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
@@ -16089,7 +16091,7 @@
     </row>
     <row r="77" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="CP77" s="13"/>
       <c r="CQ77" s="13"/>
@@ -16137,7 +16139,7 @@
     </row>
     <row r="80" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CP80" s="13"/>
       <c r="CQ80" s="13"/>
@@ -16945,28 +16947,28 @@
         <v>24.932693675292668</v>
       </c>
       <c r="CP86" s="23">
-        <v>37.895348794766136</v>
+        <v>36.928669752009426</v>
       </c>
       <c r="CQ86" s="23">
-        <v>17.29945799059594</v>
+        <v>17.563614292255721</v>
       </c>
       <c r="CR86" s="23">
-        <v>0.34759001381945609</v>
+        <v>0.40984998861353006</v>
       </c>
       <c r="CS86" s="23">
-        <v>-6.2553890715112885</v>
+        <v>-6.1409334757349399</v>
       </c>
       <c r="CT86" s="23">
-        <v>-18.950050420152053</v>
+        <v>-18.829935474236848</v>
       </c>
       <c r="CU86" s="23">
-        <v>-18.955227241880678</v>
+        <v>-19.137328545668623</v>
       </c>
       <c r="CV86" s="23">
-        <v>-22.184930297499065</v>
+        <v>-22.233180188110651</v>
       </c>
       <c r="CW86" s="23">
-        <v>-21.99602438210222</v>
+        <v>-22.091145629658655</v>
       </c>
       <c r="CX86" s="24"/>
       <c r="CY86" s="24"/>
@@ -17263,7 +17265,7 @@
         <v>-21.027419492576968</v>
       </c>
       <c r="CS87" s="23">
-        <v>-26.090333864959902</v>
+        <v>-26.090330844436409</v>
       </c>
       <c r="CT87" s="23">
         <v>-22.014136801561591</v>
@@ -17275,7 +17277,7 @@
         <v>2.4234269729525408</v>
       </c>
       <c r="CW87" s="23">
-        <v>29.356943767237397</v>
+        <v>28.795353487038682</v>
       </c>
       <c r="CX87" s="24"/>
       <c r="CY87" s="24"/>
@@ -17881,7 +17883,7 @@
         <v>-87.51478717647727</v>
       </c>
       <c r="CS89" s="23">
-        <v>-13.522989719711092</v>
+        <v>-13.329899863103805</v>
       </c>
       <c r="CT89" s="23">
         <v>6.5164724148715152</v>
@@ -17893,7 +17895,7 @@
         <v>115.80261049089705</v>
       </c>
       <c r="CW89" s="23">
-        <v>-35.881918292174021</v>
+        <v>-36.024765146894886</v>
       </c>
       <c r="CX89" s="24"/>
       <c r="CY89" s="24"/>
@@ -18181,28 +18183,28 @@
         <v>7.6888656811738656</v>
       </c>
       <c r="CP90" s="23">
-        <v>13.829830499669555</v>
+        <v>14.967401884956317</v>
       </c>
       <c r="CQ90" s="23">
-        <v>8.4983067974321926</v>
+        <v>8.9303680940612651</v>
       </c>
       <c r="CR90" s="23">
-        <v>6.7595521042739506</v>
+        <v>8.1864751516067713</v>
       </c>
       <c r="CS90" s="23">
-        <v>-4.3161678277755868</v>
+        <v>-2.0621669618458327</v>
       </c>
       <c r="CT90" s="23">
-        <v>-9.141525963799765</v>
+        <v>-10.04054602061403</v>
       </c>
       <c r="CU90" s="23">
-        <v>-14.803490855381654</v>
+        <v>-15.141414199012587</v>
       </c>
       <c r="CV90" s="23">
-        <v>-26.122118315081948</v>
+        <v>-27.096528951130566</v>
       </c>
       <c r="CW90" s="23">
-        <v>-11.565677590556305</v>
+        <v>-13.623449063297926</v>
       </c>
       <c r="CX90" s="24"/>
       <c r="CY90" s="24"/>
@@ -18493,25 +18495,25 @@
         <v>-0.18325393282377433</v>
       </c>
       <c r="CQ91" s="23">
-        <v>-27.213793201201739</v>
+        <v>-27.174119879051389</v>
       </c>
       <c r="CR91" s="23">
-        <v>-22.581909437298549</v>
+        <v>-22.562008269107125</v>
       </c>
       <c r="CS91" s="23">
-        <v>-6.9134478811322708</v>
+        <v>-6.5724429493123324</v>
       </c>
       <c r="CT91" s="23">
         <v>9.1505829400890377</v>
       </c>
       <c r="CU91" s="23">
-        <v>45.76276169676072</v>
+        <v>45.683354582247063</v>
       </c>
       <c r="CV91" s="23">
-        <v>9.6557520868502991</v>
+        <v>9.6275711188698665</v>
       </c>
       <c r="CW91" s="23">
-        <v>-12.009027493069226</v>
+        <v>-12.33018922016241</v>
       </c>
       <c r="CX91" s="24"/>
       <c r="CY91" s="24"/>
@@ -19108,28 +19110,28 @@
         <v>31.318877986198999</v>
       </c>
       <c r="CP93" s="23">
-        <v>78.229472822517295</v>
+        <v>72.943345939968452</v>
       </c>
       <c r="CQ93" s="23">
-        <v>57.796269561817923</v>
+        <v>56.641150343198774</v>
       </c>
       <c r="CR93" s="23">
-        <v>46.526862778517057</v>
+        <v>45.667056402151786</v>
       </c>
       <c r="CS93" s="23">
-        <v>54.691346960053096</v>
+        <v>53.630318002199829</v>
       </c>
       <c r="CT93" s="23">
-        <v>143.29317085302202</v>
+        <v>150.72958630917452</v>
       </c>
       <c r="CU93" s="23">
-        <v>94.265807024570648</v>
+        <v>95.698381841105004</v>
       </c>
       <c r="CV93" s="23">
-        <v>66.235127997891766</v>
+        <v>67.216338345369962</v>
       </c>
       <c r="CW93" s="23">
-        <v>45.908809512429173</v>
+        <v>46.916510818471949</v>
       </c>
       <c r="CX93" s="24"/>
       <c r="CY93" s="24"/>
@@ -19417,28 +19419,28 @@
         <v>16.222965409853259</v>
       </c>
       <c r="CP94" s="23">
-        <v>33.103321560325895</v>
+        <v>33.048551098262436</v>
       </c>
       <c r="CQ94" s="23">
-        <v>-0.34467441137582</v>
+        <v>0.85598855459996059</v>
       </c>
       <c r="CR94" s="23">
-        <v>14.041795343045578</v>
+        <v>19.491401565652794</v>
       </c>
       <c r="CS94" s="23">
-        <v>24.907475117516569</v>
+        <v>25.799331984127008</v>
       </c>
       <c r="CT94" s="23">
-        <v>-17.554560505797539</v>
+        <v>-17.546012473584554</v>
       </c>
       <c r="CU94" s="23">
-        <v>16.21397209594511</v>
+        <v>15.798878853652838</v>
       </c>
       <c r="CV94" s="23">
-        <v>4.8802558483830722</v>
+        <v>4.5290351564815552</v>
       </c>
       <c r="CW94" s="23">
-        <v>-18.921347285403783</v>
+        <v>-19.585638019418383</v>
       </c>
       <c r="CX94" s="24"/>
       <c r="CY94" s="24"/>
@@ -19747,7 +19749,7 @@
         <v>16.243950985960936</v>
       </c>
       <c r="CW95" s="23">
-        <v>-1.8544968322061379</v>
+        <v>-1.8745472423500047</v>
       </c>
       <c r="CX95" s="24"/>
       <c r="CY95" s="24"/>
@@ -20041,7 +20043,7 @@
         <v>33.112377000500089</v>
       </c>
       <c r="CR96" s="23">
-        <v>58.574695963699639</v>
+        <v>56.259902173870358</v>
       </c>
       <c r="CS96" s="23">
         <v>97.02304560848205</v>
@@ -20053,7 +20055,7 @@
         <v>102.42210092931373</v>
       </c>
       <c r="CV96" s="23">
-        <v>34.498257034033827</v>
+        <v>36.490679439231712</v>
       </c>
       <c r="CW96" s="23">
         <v>13.520994875484192</v>
@@ -20350,10 +20352,10 @@
         <v>-7.5655424160801772</v>
       </c>
       <c r="CR97" s="23">
-        <v>15.551647330546388</v>
+        <v>15.519375272467315</v>
       </c>
       <c r="CS97" s="23">
-        <v>-1.0668535215569221</v>
+        <v>-1.0278336292745678</v>
       </c>
       <c r="CT97" s="23">
         <v>-20.109112684750258</v>
@@ -20362,10 +20364,10 @@
         <v>-20.010665717828601</v>
       </c>
       <c r="CV97" s="23">
-        <v>-13.000742659360256</v>
+        <v>-12.976438121016713</v>
       </c>
       <c r="CW97" s="23">
-        <v>3.8255873807079297</v>
+        <v>3.7846540215191311</v>
       </c>
       <c r="CX97" s="24"/>
       <c r="CY97" s="24"/>
@@ -20656,10 +20658,10 @@
         <v>38.46067539195036</v>
       </c>
       <c r="CQ98" s="23">
-        <v>4.315614060977552</v>
+        <v>4.3260797166496161</v>
       </c>
       <c r="CR98" s="23">
-        <v>-46.722932824351574</v>
+        <v>-45.506732607296584</v>
       </c>
       <c r="CS98" s="23">
         <v>-12.349965312665901</v>
@@ -20668,10 +20670,10 @@
         <v>122.27315281190801</v>
       </c>
       <c r="CU98" s="23">
-        <v>-18.477172754848795</v>
+        <v>-18.485350861815689</v>
       </c>
       <c r="CV98" s="23">
-        <v>-14.95095638460873</v>
+        <v>-14.950956384608801</v>
       </c>
       <c r="CW98" s="23">
         <v>-40.583953815609696</v>
@@ -20962,28 +20964,28 @@
         <v>5.6523921915037789</v>
       </c>
       <c r="CP99" s="23">
-        <v>-10.78435841941959</v>
+        <v>-10.416087982966417</v>
       </c>
       <c r="CQ99" s="23">
-        <v>-4.0883175994222967</v>
+        <v>-3.5417641049456279</v>
       </c>
       <c r="CR99" s="23">
-        <v>32.794962935110448</v>
+        <v>31.424146062751902</v>
       </c>
       <c r="CS99" s="23">
-        <v>6.1960417004392809</v>
+        <v>6.1802394027079259</v>
       </c>
       <c r="CT99" s="23">
-        <v>5.0589991851930165</v>
+        <v>5.1426292277789685</v>
       </c>
       <c r="CU99" s="23">
-        <v>5.829758026422553</v>
+        <v>5.859049642560322</v>
       </c>
       <c r="CV99" s="23">
-        <v>-4.8983186380332455</v>
+        <v>-5.0455721102715074</v>
       </c>
       <c r="CW99" s="23">
-        <v>9.1795738635303223</v>
+        <v>8.5555826442929686</v>
       </c>
       <c r="CX99" s="24"/>
       <c r="CY99" s="24"/>
@@ -21271,28 +21273,28 @@
         <v>8.739871184497062</v>
       </c>
       <c r="CP100" s="23">
-        <v>2.2224251816056437</v>
+        <v>2.5170793937211897</v>
       </c>
       <c r="CQ100" s="23">
-        <v>11.871125814118443</v>
+        <v>12.099825174470254</v>
       </c>
       <c r="CR100" s="23">
-        <v>5.4918864207061659</v>
+        <v>4.6489615714564678</v>
       </c>
       <c r="CS100" s="23">
-        <v>0.30858325801901287</v>
+        <v>0.3112995876506659</v>
       </c>
       <c r="CT100" s="23">
-        <v>12.45262000552907</v>
+        <v>12.330262074056833</v>
       </c>
       <c r="CU100" s="23">
-        <v>6.0847695959671739</v>
+        <v>5.6122567374428627</v>
       </c>
       <c r="CV100" s="23">
-        <v>3.2207896476821958</v>
+        <v>3.3588620121824704</v>
       </c>
       <c r="CW100" s="23">
-        <v>5.3156805330852421</v>
+        <v>5.2919904278688961</v>
       </c>
       <c r="CX100" s="24"/>
       <c r="CY100" s="24"/>
@@ -21580,7 +21582,7 @@
         <v>8.8882870859577849</v>
       </c>
       <c r="CP101" s="23">
-        <v>3.1720551668007033</v>
+        <v>3.1720551668025507</v>
       </c>
       <c r="CQ101" s="23">
         <v>13.116030365581238</v>
@@ -21592,16 +21594,16 @@
         <v>4.4269334375482714</v>
       </c>
       <c r="CT101" s="23">
-        <v>17.178521552054193</v>
+        <v>17.14043072711722</v>
       </c>
       <c r="CU101" s="23">
-        <v>8.9401984803919987</v>
+        <v>8.9218694672747318</v>
       </c>
       <c r="CV101" s="23">
-        <v>8.8101910385478135</v>
+        <v>8.3645950445787776</v>
       </c>
       <c r="CW101" s="23">
-        <v>13.923785148736684</v>
+        <v>13.912235470780487</v>
       </c>
       <c r="CX101" s="24"/>
       <c r="CY101" s="24"/>
@@ -22510,25 +22512,25 @@
         <v>-7.0461117201547694</v>
       </c>
       <c r="CQ104" s="23">
-        <v>-8.9164739740190839</v>
+        <v>-8.70286465556525</v>
       </c>
       <c r="CR104" s="23">
-        <v>-9.1958051152434876</v>
+        <v>-9.0595988630141875</v>
       </c>
       <c r="CS104" s="23">
-        <v>-4.2319461454218441</v>
+        <v>-4.7163554221769886</v>
       </c>
       <c r="CT104" s="23">
-        <v>3.3246851080578352</v>
+        <v>4.1036833747806014</v>
       </c>
       <c r="CU104" s="23">
-        <v>4.4169251039854203</v>
+        <v>4.4433640857117069</v>
       </c>
       <c r="CV104" s="23">
-        <v>2.2388186514818358</v>
+        <v>2.4445722395931995</v>
       </c>
       <c r="CW104" s="23">
-        <v>10.361525336924743</v>
+        <v>10.647350377498086</v>
       </c>
       <c r="CX104" s="24"/>
       <c r="CY104" s="24"/>
@@ -23131,28 +23133,28 @@
         <v>10.136568127949317</v>
       </c>
       <c r="CP107" s="23">
-        <v>8.2978659177646676</v>
+        <v>8.2480285158783317</v>
       </c>
       <c r="CQ107" s="23">
-        <v>6.6138653475692308</v>
+        <v>6.7867788434529785</v>
       </c>
       <c r="CR107" s="23">
-        <v>7.1092157320140785</v>
+        <v>7.1341236603845033</v>
       </c>
       <c r="CS107" s="23">
-        <v>-3.9469257678646841E-2</v>
+        <v>7.7849538103563987E-2</v>
       </c>
       <c r="CT107" s="23">
-        <v>2.0742119320947552</v>
+        <v>2.1554468394012503</v>
       </c>
       <c r="CU107" s="23">
-        <v>5.0405191509382234</v>
+        <v>4.8920858716943911</v>
       </c>
       <c r="CV107" s="23">
-        <v>-3.9056790280708782</v>
+        <v>-4.0300300788284176</v>
       </c>
       <c r="CW107" s="23">
-        <v>-1.8480020269542052</v>
+        <v>-2.0499984234648139</v>
       </c>
       <c r="CX107" s="24"/>
       <c r="CY107" s="24"/>
@@ -23331,7 +23333,7 @@
     </row>
     <row r="114" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="CP114" s="13"/>
       <c r="CQ114" s="13"/>
@@ -23379,7 +23381,7 @@
     </row>
     <row r="117" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CP117" s="13"/>
       <c r="CQ117" s="13"/>
@@ -24199,7 +24201,7 @@
         <v>-0.10954944175074388</v>
       </c>
       <c r="CT123" s="23">
-        <v>1.0617862037472889</v>
+        <v>0.50202804630301046</v>
       </c>
       <c r="CU123" s="23">
         <v>14.179238234866617</v>
@@ -24505,7 +24507,7 @@
         <v>1.3003962670543388</v>
       </c>
       <c r="CS124" s="23">
-        <v>-0.54881224431369446</v>
+        <v>-0.54880818398748943</v>
       </c>
       <c r="CT124" s="23">
         <v>-3.04022788600588</v>
@@ -24517,7 +24519,7 @@
         <v>-2.9223245070181179</v>
       </c>
       <c r="CW124" s="23">
-        <v>3.1429760698265881</v>
+        <v>2.695636478873368</v>
       </c>
       <c r="CX124" s="24"/>
       <c r="CY124" s="24"/>
@@ -25123,7 +25125,7 @@
         <v>-62.246496748694021</v>
       </c>
       <c r="CS126" s="23">
-        <v>-22.871742060102264</v>
+        <v>-23.279293565851503</v>
       </c>
       <c r="CT126" s="23">
         <v>19.000951476513535</v>
@@ -25135,7 +25137,7 @@
         <v>42.023621559128088</v>
       </c>
       <c r="CW126" s="23">
-        <v>-0.34015884532431073</v>
+        <v>0.18924866684686492</v>
       </c>
       <c r="CX126" s="24"/>
       <c r="CY126" s="24"/>
@@ -26659,25 +26661,25 @@
         <v>-2.4711567905983998</v>
       </c>
       <c r="CP131" s="23">
-        <v>-8.8002519571153357</v>
+        <v>-8.8109989521178846</v>
       </c>
       <c r="CQ131" s="23">
         <v>-6.8733490012630227</v>
       </c>
       <c r="CR131" s="23">
-        <v>-4.1109966861681357</v>
+        <v>0.47120318120184379</v>
       </c>
       <c r="CS131" s="23">
         <v>-8.5038437903660906</v>
       </c>
       <c r="CT131" s="23">
-        <v>-1.4045737126082258E-2</v>
+        <v>-3.7284795764506384E-2</v>
       </c>
       <c r="CU131" s="23">
         <v>0.65326057128049797</v>
       </c>
       <c r="CV131" s="23">
-        <v>-5.3039334761807737</v>
+        <v>-5.0962431896203242</v>
       </c>
       <c r="CW131" s="23">
         <v>-2.7472561771661503</v>
@@ -27283,7 +27285,7 @@
         <v>6.1671225191559245</v>
       </c>
       <c r="CR133" s="23">
-        <v>1.5079270141567207</v>
+        <v>2.4339028453354672E-2</v>
       </c>
       <c r="CS133" s="23">
         <v>-5.4778894836748009</v>
@@ -27295,7 +27297,7 @@
         <v>10.120216583603451</v>
       </c>
       <c r="CV133" s="23">
-        <v>-0.32763858858153583</v>
+        <v>1.1507287701330284</v>
       </c>
       <c r="CW133" s="23">
         <v>7.0711332491187164</v>
@@ -27592,10 +27594,10 @@
         <v>-11.835939073202013</v>
       </c>
       <c r="CR134" s="23">
-        <v>0.36948822252000468</v>
+        <v>0.34133470891258355</v>
       </c>
       <c r="CS134" s="23">
-        <v>-0.16547165045719225</v>
+        <v>-0.12612158607183233</v>
       </c>
       <c r="CT134" s="23">
         <v>-15.427420782378732</v>
@@ -27604,10 +27606,10 @@
         <v>-17.758945539699383</v>
       </c>
       <c r="CV134" s="23">
-        <v>-11.686405254322025</v>
+        <v>-11.661626453057266</v>
       </c>
       <c r="CW134" s="23">
-        <v>-10.583405991298804</v>
+        <v>-10.618635911146129</v>
       </c>
       <c r="CX134" s="24"/>
       <c r="CY134" s="24"/>
@@ -28204,28 +28206,28 @@
         <v>-1.6551283622089272</v>
       </c>
       <c r="CP136" s="23">
-        <v>2.9438329856621408</v>
+        <v>3.422861968532743</v>
       </c>
       <c r="CQ136" s="23">
         <v>-8.2396361398786553</v>
       </c>
       <c r="CR136" s="23">
-        <v>7.8514877087777535</v>
+        <v>6.7374313002608801</v>
       </c>
       <c r="CS136" s="23">
-        <v>-5.7000730077469228</v>
+        <v>-5.6270122754616665</v>
       </c>
       <c r="CT136" s="23">
-        <v>1.9445110981679079</v>
+        <v>1.4723294689701589</v>
       </c>
       <c r="CU136" s="23">
         <v>5.8095051514815026</v>
       </c>
       <c r="CV136" s="23">
-        <v>-3.495248540324468</v>
+        <v>-3.5522070454867958</v>
       </c>
       <c r="CW136" s="23">
-        <v>-0.64828195574631309</v>
+        <v>-0.74922325829393799</v>
       </c>
       <c r="CX136" s="24"/>
       <c r="CY136" s="24"/>
@@ -28513,28 +28515,28 @@
         <v>2.7034528310534682</v>
       </c>
       <c r="CP137" s="23">
-        <v>-3.4300889556029261</v>
+        <v>-3.3050629284066417</v>
       </c>
       <c r="CQ137" s="23">
-        <v>-0.18892295542934789</v>
+        <v>-0.15609972742112177</v>
       </c>
       <c r="CR137" s="23">
-        <v>-6.2912967147993726</v>
+        <v>-6.5041317397349019</v>
       </c>
       <c r="CS137" s="23">
-        <v>-5.9127651902309282</v>
+        <v>-5.9102153482648987</v>
       </c>
       <c r="CT137" s="23">
-        <v>-2.3343765323120493</v>
+        <v>-2.339097115251036</v>
       </c>
       <c r="CU137" s="23">
-        <v>-5.668121257157523</v>
+        <v>-5.6853425181841715</v>
       </c>
       <c r="CV137" s="23">
-        <v>-1.6019839854073439</v>
+        <v>-1.5852955446498527</v>
       </c>
       <c r="CW137" s="23">
-        <v>1.5374160033206294</v>
+        <v>1.5808547207083308</v>
       </c>
       <c r="CX137" s="24"/>
       <c r="CY137" s="24"/>
@@ -28834,7 +28836,7 @@
         <v>6.1434154248431128</v>
       </c>
       <c r="CT138" s="23">
-        <v>9.8168011724537791</v>
+        <v>9.7765612352251452</v>
       </c>
       <c r="CU138" s="23">
         <v>6.9143284632165063</v>
@@ -29752,25 +29754,25 @@
         <v>-0.22444232982886092</v>
       </c>
       <c r="CQ141" s="23">
-        <v>2.7094035904057421</v>
+        <v>2.631276779181718</v>
       </c>
       <c r="CR141" s="23">
-        <v>-4.604208437964445</v>
+        <v>-4.5311871893071327</v>
       </c>
       <c r="CS141" s="23">
-        <v>-0.41660267527629458</v>
+        <v>-0.91942372422990104</v>
       </c>
       <c r="CT141" s="23">
-        <v>1.4521522240876834</v>
+        <v>2.1313006784228179</v>
       </c>
       <c r="CU141" s="23">
-        <v>-4.4626149957789636</v>
+        <v>-4.2935225083655411</v>
       </c>
       <c r="CV141" s="23">
-        <v>-2.5204642594121935</v>
+        <v>-2.5823824885413416</v>
       </c>
       <c r="CW141" s="23">
-        <v>4.0650525183226307</v>
+        <v>4.7059274152744734</v>
       </c>
       <c r="CX141" s="24"/>
       <c r="CY141" s="24"/>
@@ -30373,28 +30375,28 @@
         <v>1.2981862146848329</v>
       </c>
       <c r="CP144" s="23">
-        <v>0.48816829392694672</v>
+        <v>0.52811743598415717</v>
       </c>
       <c r="CQ144" s="23">
-        <v>-2.2919435673074986</v>
+        <v>-2.2962908470666008</v>
       </c>
       <c r="CR144" s="23">
-        <v>-2.6912688353491063</v>
+        <v>-2.7036891435209895</v>
       </c>
       <c r="CS144" s="23">
-        <v>-1.6029244942335765</v>
+        <v>-1.6675264669891732</v>
       </c>
       <c r="CT144" s="23">
-        <v>2.2332920366867199</v>
+        <v>2.1519978171840961</v>
       </c>
       <c r="CU144" s="23">
-        <v>6.9563323414796088</v>
+        <v>6.9728815348499182</v>
       </c>
       <c r="CV144" s="23">
-        <v>2.8707314260118437</v>
+        <v>2.8658423378647484</v>
       </c>
       <c r="CW144" s="23">
-        <v>0.96249059863269792</v>
+        <v>1.0256262320668554</v>
       </c>
       <c r="CX144" s="24"/>
       <c r="CY144" s="24"/>
@@ -30556,7 +30558,7 @@
     </row>
     <row r="150" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="CP150" s="13"/>
       <c r="CQ150" s="13"/>
@@ -30604,7 +30606,7 @@
     </row>
     <row r="153" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CP153" s="13"/>
       <c r="CQ153" s="13"/>
@@ -31434,19 +31436,19 @@
         <v>125.43407574946721</v>
       </c>
       <c r="CT159" s="23">
-        <v>138.82617134345534</v>
+        <v>137.85296701425347</v>
       </c>
       <c r="CU159" s="23">
-        <v>127.68087941230888</v>
+        <v>127.9684144911234</v>
       </c>
       <c r="CV159" s="23">
-        <v>113.59893109191729</v>
+        <v>113.66941277050513</v>
       </c>
       <c r="CW159" s="23">
-        <v>117.71664420966323</v>
+        <v>117.86036797695357</v>
       </c>
       <c r="CX159" s="23">
-        <v>111.336387475538</v>
+        <v>111.33640231080352</v>
       </c>
       <c r="CY159" s="23">
         <v>90.62827898923139</v>
@@ -31760,7 +31762,7 @@
         <v>98.320515504425558</v>
       </c>
       <c r="CW160" s="23">
-        <v>100.25162752584428</v>
+        <v>100.2516275298991</v>
       </c>
       <c r="CX160" s="23">
         <v>102.89091160714779</v>
@@ -31772,7 +31774,7 @@
         <v>103.73470613682547</v>
       </c>
       <c r="DA160" s="23">
-        <v>125.73075393573406</v>
+        <v>125.73020868340932</v>
       </c>
     </row>
     <row r="161" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -32394,7 +32396,7 @@
         <v>106.03361496994246</v>
       </c>
       <c r="CW162" s="23">
-        <v>227.71254413730273</v>
+        <v>229.43333417088314</v>
       </c>
       <c r="CX162" s="23">
         <v>113.07566535642751</v>
@@ -32702,16 +32704,16 @@
         <v>113.07891911504254</v>
       </c>
       <c r="CT163" s="23">
-        <v>135.52479191405661</v>
+        <v>136.87917436900386</v>
       </c>
       <c r="CU163" s="23">
-        <v>123.83517856263178</v>
+        <v>124.32831425661047</v>
       </c>
       <c r="CV163" s="23">
-        <v>120.24227708991543</v>
+        <v>121.84940706621768</v>
       </c>
       <c r="CW163" s="23">
-        <v>114.78159893067144</v>
+        <v>117.48548126386289</v>
       </c>
       <c r="CX163" s="23">
         <v>121.44513205187776</v>
@@ -32723,7 +32725,7 @@
         <v>89.050653351320122</v>
       </c>
       <c r="DA163" s="23">
-        <v>101.56193980712442</v>
+        <v>101.53550263341693</v>
       </c>
     </row>
     <row r="164" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -33022,13 +33024,13 @@
         <v>106.45776415339225</v>
       </c>
       <c r="CU164" s="23">
-        <v>86.399567771772311</v>
+        <v>86.446661280784753</v>
       </c>
       <c r="CV164" s="23">
-        <v>110.23081396012549</v>
+        <v>110.25914999828599</v>
       </c>
       <c r="CW164" s="23">
-        <v>136.36066327288648</v>
+        <v>136.86019470491237</v>
       </c>
       <c r="CX164" s="23">
         <v>126.22314470966288</v>
@@ -33653,16 +33655,16 @@
         <v>171.74135184343751</v>
       </c>
       <c r="CT166" s="23">
-        <v>118.7352620079154</v>
+        <v>115.2136802489235</v>
       </c>
       <c r="CU166" s="23">
-        <v>188.22699644517783</v>
+        <v>186.8491145620348</v>
       </c>
       <c r="CV166" s="23">
-        <v>142.37269885205635</v>
+        <v>141.53726873383727</v>
       </c>
       <c r="CW166" s="23">
-        <v>272.75303115859771</v>
+        <v>270.88221633870825</v>
       </c>
       <c r="CX166" s="23">
         <v>265.24423134703716</v>
@@ -33970,28 +33972,28 @@
         <v>172.11104501821498</v>
       </c>
       <c r="CT167" s="23">
-        <v>162.33398408397818</v>
+        <v>162.28630939412875</v>
       </c>
       <c r="CU167" s="23">
-        <v>119.8600956667151</v>
+        <v>121.30418886610317</v>
       </c>
       <c r="CV167" s="23">
-        <v>216.0222617523246</v>
+        <v>216.02216766644179</v>
       </c>
       <c r="CW167" s="23">
-        <v>234.96020995468743</v>
+        <v>236.6378587617838</v>
       </c>
       <c r="CX167" s="23">
-        <v>133.85576765573751</v>
+        <v>133.86144327064576</v>
       </c>
       <c r="CY167" s="23">
-        <v>138.39012997859538</v>
+        <v>139.55721842710497</v>
       </c>
       <c r="CZ167" s="23">
-        <v>239.25460595378928</v>
+        <v>237.93145305829654</v>
       </c>
       <c r="DA167" s="23">
-        <v>195.88400816092891</v>
+        <v>195.66627824347322</v>
       </c>
     </row>
     <row r="168" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -34308,7 +34310,7 @@
         <v>149.93385705643081</v>
       </c>
       <c r="DA168" s="23">
-        <v>159.77029751295396</v>
+        <v>159.73765760699243</v>
       </c>
     </row>
     <row r="169" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -34610,7 +34612,7 @@
         <v>91.126143760225759</v>
       </c>
       <c r="CV169" s="23">
-        <v>216.73424556769351</v>
+        <v>216.73820268173398</v>
       </c>
       <c r="CW169" s="23">
         <v>248.84922056751978</v>
@@ -34927,10 +34929,10 @@
         <v>56.908262285339831</v>
       </c>
       <c r="CV170" s="23">
-        <v>143.79446341843268</v>
+        <v>143.79463772533927</v>
       </c>
       <c r="CW170" s="23">
-        <v>104.64766509726935</v>
+        <v>104.64769164733654</v>
       </c>
       <c r="CX170" s="23">
         <v>84.705523615808858</v>
@@ -35241,10 +35243,10 @@
         <v>80.649455371372028</v>
       </c>
       <c r="CU171" s="23">
-        <v>57.460084749970861</v>
+        <v>57.465849538562608</v>
       </c>
       <c r="CV171" s="23">
-        <v>108.15141874992003</v>
+        <v>110.62028173227611</v>
       </c>
       <c r="CW171" s="23">
         <v>100.6950583972061</v>
@@ -35256,7 +35258,7 @@
         <v>43.265859184828919</v>
       </c>
       <c r="CZ171" s="23">
-        <v>79.513375773840835</v>
+        <v>81.328494172834041</v>
       </c>
       <c r="DA171" s="23">
         <v>58.563084232841646</v>
@@ -35555,28 +35557,28 @@
         <v>138.89877633501416</v>
       </c>
       <c r="CT172" s="23">
-        <v>123.22124380240666</v>
+        <v>123.15679882887096</v>
       </c>
       <c r="CU172" s="23">
-        <v>94.262100905703278</v>
+        <v>94.799254246748362</v>
       </c>
       <c r="CV172" s="23">
-        <v>208.08288204673619</v>
+        <v>208.08429783100499</v>
       </c>
       <c r="CW172" s="23">
-        <v>156.42112050654006</v>
+        <v>156.27676604923482</v>
       </c>
       <c r="CX172" s="23">
-        <v>126.98575345336234</v>
+        <v>127.61143558948163</v>
       </c>
       <c r="CY172" s="23">
-        <v>94.280143505360002</v>
+        <v>94.843643272097097</v>
       </c>
       <c r="CZ172" s="23">
-        <v>205.05759194206368</v>
+        <v>204.86239081383113</v>
       </c>
       <c r="DA172" s="23">
-        <v>171.89427235222055</v>
+        <v>170.92778463981352</v>
       </c>
     </row>
     <row r="173" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -35872,28 +35874,28 @@
         <v>176.54944237169289</v>
       </c>
       <c r="CT173" s="23">
-        <v>157.11890799356084</v>
+        <v>157.36806080184141</v>
       </c>
       <c r="CU173" s="23">
-        <v>181.70090439928353</v>
+        <v>182.01250207691419</v>
       </c>
       <c r="CV173" s="23">
-        <v>178.80488311353017</v>
+        <v>177.77993740924799</v>
       </c>
       <c r="CW173" s="23">
-        <v>188.223455340182</v>
+        <v>188.22345136968025</v>
       </c>
       <c r="CX173" s="23">
-        <v>180.90738817767408</v>
+        <v>181.00585792062634</v>
       </c>
       <c r="CY173" s="23">
-        <v>204.33917818094355</v>
+        <v>203.81509737738929</v>
       </c>
       <c r="CZ173" s="23">
-        <v>187.56863172020638</v>
+        <v>186.71124524438858</v>
       </c>
       <c r="DA173" s="23">
-        <v>195.22735629584835</v>
+        <v>195.09997129288402</v>
       </c>
     </row>
     <row r="174" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -36189,7 +36191,7 @@
         <v>126.79478760362748</v>
       </c>
       <c r="CT174" s="23">
-        <v>160.38782548849184</v>
+        <v>160.38782548849471</v>
       </c>
       <c r="CU174" s="23">
         <v>124.47944460981341</v>
@@ -36201,16 +36203,16 @@
         <v>124.74434511378121</v>
       </c>
       <c r="CX174" s="23">
-        <v>171.13964407118968</v>
+        <v>171.1467252180542</v>
       </c>
       <c r="CY174" s="23">
-        <v>126.83814786516277</v>
+        <v>126.81680755085804</v>
       </c>
       <c r="CZ174" s="23">
-        <v>126.65564494056558</v>
+        <v>126.13696881785677</v>
       </c>
       <c r="DA174" s="23">
-        <v>130.5353833275033</v>
+        <v>130.52214955338533</v>
       </c>
     </row>
     <row r="175" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -37143,25 +37145,25 @@
         <v>146.88010368185212</v>
       </c>
       <c r="CU177" s="23">
-        <v>124.33156017780482</v>
+        <v>124.71801072289909</v>
       </c>
       <c r="CV177" s="23">
-        <v>134.08103540615096</v>
+        <v>134.17944848166317</v>
       </c>
       <c r="CW177" s="23">
-        <v>106.0669625942778</v>
+        <v>106.06601325213336</v>
       </c>
       <c r="CX177" s="23">
-        <v>149.5911139277236</v>
+        <v>149.71668534699214</v>
       </c>
       <c r="CY177" s="23">
-        <v>135.88731999074415</v>
+        <v>136.10331237105686</v>
       </c>
       <c r="CZ177" s="23">
-        <v>140.62732818068423</v>
+        <v>141.10339129810541</v>
       </c>
       <c r="DA177" s="23">
-        <v>112.48456130551629</v>
+        <v>112.08461279281046</v>
       </c>
     </row>
     <row r="178" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -37775,28 +37777,28 @@
         <v>132.17674896317163</v>
       </c>
       <c r="CT180" s="23">
-        <v>137.40609502817921</v>
+        <v>137.28828330852957</v>
       </c>
       <c r="CU180" s="23">
-        <v>131.48732330529182</v>
+        <v>131.70643819270313</v>
       </c>
       <c r="CV180" s="23">
-        <v>137.19032227987771</v>
+        <v>137.23974250908063</v>
       </c>
       <c r="CW180" s="23">
-        <v>134.27693770613044</v>
+        <v>134.52285211488419</v>
       </c>
       <c r="CX180" s="23">
-        <v>137.19228428675447</v>
+        <v>137.29291865927556</v>
       </c>
       <c r="CY180" s="23">
-        <v>129.13210839783781</v>
+        <v>129.14453482552352</v>
       </c>
       <c r="CZ180" s="23">
-        <v>128.15317516126331</v>
+        <v>128.03952858642577</v>
       </c>
       <c r="DA180" s="23">
-        <v>130.53907089072345</v>
+        <v>130.42743775193267</v>
       </c>
     </row>
     <row r="181" spans="1:105" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
@@ -37959,7 +37961,7 @@
     </row>
     <row r="187" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="CP187" s="13"/>
       <c r="CQ187" s="13"/>
@@ -38007,7 +38009,7 @@
     </row>
     <row r="190" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CP190" s="13"/>
       <c r="CQ190" s="13"/>
@@ -38837,28 +38839,28 @@
         <v>23.85240099033631</v>
       </c>
       <c r="CT196" s="23">
-        <v>21.071606788645642</v>
+        <v>20.933523196932374</v>
       </c>
       <c r="CU196" s="23">
-        <v>17.951013841297542</v>
+        <v>17.962306736330643</v>
       </c>
       <c r="CV196" s="23">
-        <v>13.108408973616983</v>
+        <v>13.113492492633588</v>
       </c>
       <c r="CW196" s="23">
-        <v>22.369169450624803</v>
+        <v>22.370225795699533</v>
       </c>
       <c r="CX196" s="23">
-        <v>16.731480316715704</v>
+        <v>16.633233774776954</v>
       </c>
       <c r="CY196" s="23">
-        <v>13.850234645692144</v>
+        <v>13.847375577586698</v>
       </c>
       <c r="CZ196" s="23">
-        <v>10.614901563942203</v>
+        <v>10.626184509767434</v>
       </c>
       <c r="DA196" s="23">
-        <v>17.777367597736884</v>
+        <v>17.793145846832957</v>
       </c>
     </row>
     <row r="197" spans="1:105" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -39154,28 +39156,28 @@
         <v>4.5573041081675374</v>
       </c>
       <c r="CT197" s="23">
-        <v>6.7898298222865998</v>
+        <v>6.7929558605362805</v>
       </c>
       <c r="CU197" s="23">
-        <v>3.6227902434264569</v>
+        <v>3.6169240741063509</v>
       </c>
       <c r="CV197" s="23">
-        <v>5.7407046702630655</v>
+        <v>5.739369996903755</v>
       </c>
       <c r="CW197" s="23">
-        <v>3.3696182144009219</v>
+        <v>3.3656682315871453</v>
       </c>
       <c r="CX197" s="23">
-        <v>5.1875074971313921</v>
+        <v>5.1857687753609536</v>
       </c>
       <c r="CY197" s="23">
-        <v>3.6825961197713064</v>
+        <v>3.6818359309816855</v>
       </c>
       <c r="CZ197" s="23">
-        <v>6.1188074344137044</v>
+        <v>6.1253113263604773</v>
       </c>
       <c r="DA197" s="23">
-        <v>4.4409031184166015</v>
+        <v>4.4255479594724934</v>
       </c>
     </row>
     <row r="198" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -39471,28 +39473,28 @@
         <v>2.6559224905439436</v>
       </c>
       <c r="CT198" s="23">
-        <v>3.9635582398990161</v>
+        <v>3.9653830624626232</v>
       </c>
       <c r="CU198" s="23">
-        <v>3.3219917139003954</v>
+        <v>3.3166126097943582</v>
       </c>
       <c r="CV198" s="23">
-        <v>10.259984471413313</v>
+        <v>10.257599097364745</v>
       </c>
       <c r="CW198" s="23">
-        <v>3.8493957493670017</v>
+        <v>3.8448831976296365</v>
       </c>
       <c r="CX198" s="23">
-        <v>4.7685740664703564</v>
+        <v>4.7669757606273473</v>
       </c>
       <c r="CY198" s="23">
-        <v>5.0842411938052408</v>
+        <v>5.0831916670492348</v>
       </c>
       <c r="CZ198" s="23">
-        <v>10.113665990767217</v>
+        <v>10.124416155974208</v>
       </c>
       <c r="DA198" s="23">
-        <v>3.8158505029126664</v>
+        <v>3.8192372495396518</v>
       </c>
     </row>
     <row r="199" spans="1:105" s="9" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -39788,28 +39790,28 @@
         <v>2.4466115873024123</v>
       </c>
       <c r="CT199" s="23">
-        <v>2.6886377615672248</v>
+        <v>2.6898756106300401</v>
       </c>
       <c r="CU199" s="23">
-        <v>0.56438533675851599</v>
+        <v>0.56347146106471391</v>
       </c>
       <c r="CV199" s="23">
-        <v>5.5084693704245548E-2</v>
+        <v>5.5071886901350141E-2</v>
       </c>
       <c r="CW199" s="23">
-        <v>2.1165919570037621</v>
+        <v>2.1188312123638866</v>
       </c>
       <c r="CX199" s="23">
-        <v>2.8056470340821771</v>
+        <v>2.8047066519080746</v>
       </c>
       <c r="CY199" s="23">
-        <v>2.0577857099759052</v>
+        <v>2.0573609265955701</v>
       </c>
       <c r="CZ199" s="23">
-        <v>0.12370575679430838</v>
+        <v>0.12383724791966376</v>
       </c>
       <c r="DA199" s="23">
-        <v>1.3826699287218105</v>
+        <v>1.383897113254789</v>
       </c>
     </row>
     <row r="200" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -40105,28 +40107,28 @@
         <v>5.4913655142409601</v>
       </c>
       <c r="CT200" s="23">
-        <v>6.4065916870321677</v>
+        <v>6.4735957637681789</v>
       </c>
       <c r="CU200" s="23">
-        <v>7.6729578051873952</v>
+        <v>7.691039169424899</v>
       </c>
       <c r="CV200" s="23">
-        <v>7.6626295964851012</v>
+        <v>7.7632411816936049</v>
       </c>
       <c r="CW200" s="23">
-        <v>5.2564236339985131</v>
+        <v>5.3739408007607352</v>
       </c>
       <c r="CX200" s="23">
-        <v>5.7026464710203992</v>
+        <v>5.7007350876491438</v>
       </c>
       <c r="CY200" s="23">
-        <v>6.223400503919537</v>
+        <v>6.222115823454307</v>
       </c>
       <c r="CZ200" s="23">
-        <v>5.8910749043103738</v>
+        <v>5.8973367314782772</v>
       </c>
       <c r="DA200" s="23">
-        <v>4.7360040749990571</v>
+        <v>4.7389735971064075</v>
       </c>
     </row>
     <row r="201" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -40422,28 +40424,28 @@
         <v>1.5482577697976818</v>
       </c>
       <c r="CT201" s="23">
-        <v>1.0549403194328226</v>
+        <v>1.0554260140490341</v>
       </c>
       <c r="CU201" s="23">
-        <v>3.1915492340988854</v>
+        <v>3.1881181374541399</v>
       </c>
       <c r="CV201" s="23">
-        <v>0.47203761402264521</v>
+        <v>0.47204918283359243</v>
       </c>
       <c r="CW201" s="23">
-        <v>1.4417888391692519</v>
+        <v>1.4453741940355087</v>
       </c>
       <c r="CX201" s="23">
-        <v>1.1280748452870595</v>
+        <v>1.1276967430301916</v>
       </c>
       <c r="CY201" s="23">
-        <v>4.4288531151007708</v>
+        <v>4.4279388784102736</v>
       </c>
       <c r="CZ201" s="23">
-        <v>0.53865451210229176</v>
+        <v>0.53922706660427711</v>
       </c>
       <c r="DA201" s="23">
-        <v>1.2925300017120425</v>
+        <v>1.2936771828241524</v>
       </c>
     </row>
     <row r="202" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -40739,28 +40741,28 @@
         <v>1.7369562028575221</v>
       </c>
       <c r="CT202" s="23">
-        <v>1.6509288992682662</v>
+        <v>1.6516889870792559</v>
       </c>
       <c r="CU202" s="23">
-        <v>1.7757191941100683</v>
+        <v>1.7728438773631179</v>
       </c>
       <c r="CV202" s="23">
-        <v>2.6381896071268742</v>
+        <v>2.6375762466445485</v>
       </c>
       <c r="CW202" s="23">
-        <v>2.3704538918676903</v>
+        <v>2.3676750672093396</v>
       </c>
       <c r="CX202" s="23">
-        <v>2.1541350922639637</v>
+        <v>2.1534130804724718</v>
       </c>
       <c r="CY202" s="23">
-        <v>0.99640031443985166</v>
+        <v>0.99619463010076681</v>
       </c>
       <c r="CZ202" s="23">
-        <v>2.419171556359998</v>
+        <v>2.4217429774370496</v>
       </c>
       <c r="DA202" s="23">
-        <v>2.0520818076048011</v>
+        <v>2.0539031266357486</v>
       </c>
     </row>
     <row r="203" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -41056,28 +41058,28 @@
         <v>0.59678197529452248</v>
       </c>
       <c r="CT203" s="23">
-        <v>0.56130139618204644</v>
+        <v>0.54490445700989321</v>
       </c>
       <c r="CU203" s="23">
-        <v>0.18558275695258222</v>
+        <v>0.18392592837977723</v>
       </c>
       <c r="CV203" s="23">
-        <v>0.15889303546632549</v>
+        <v>0.15792394076625602</v>
       </c>
       <c r="CW203" s="23">
-        <v>0.92353458824429369</v>
+        <v>0.91612484746258271</v>
       </c>
       <c r="CX203" s="23">
-        <v>1.3378579554668126</v>
+        <v>1.3374095391986509</v>
       </c>
       <c r="CY203" s="23">
-        <v>0.34322358972191086</v>
+        <v>0.34315273896425125</v>
       </c>
       <c r="CZ203" s="23">
-        <v>0.27487164508331419</v>
+        <v>0.27516381565707648</v>
       </c>
       <c r="DA203" s="23">
-        <v>1.3728893460862761</v>
+        <v>1.3741078498925792</v>
       </c>
     </row>
     <row r="204" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -41373,28 +41375,28 @@
         <v>1.4304952155974298</v>
       </c>
       <c r="CT204" s="23">
-        <v>0.90405479731408767</v>
+        <v>0.90409884496110704</v>
       </c>
       <c r="CU204" s="23">
-        <v>1.1498423691607034</v>
+        <v>1.1618115464040022</v>
       </c>
       <c r="CV204" s="23">
-        <v>1.7239520594810771</v>
+        <v>1.8059129483686625</v>
       </c>
       <c r="CW204" s="23">
-        <v>1.7875009688430255</v>
+        <v>1.7981535710370189</v>
       </c>
       <c r="CX204" s="23">
-        <v>0.73020593233663078</v>
+        <v>0.72973646723179142</v>
       </c>
       <c r="CY204" s="23">
-        <v>1.272154308494617</v>
+        <v>1.2826179725072795</v>
       </c>
       <c r="CZ204" s="23">
-        <v>1.8815735543991168</v>
+        <v>1.9669729835762848</v>
       </c>
       <c r="DA204" s="23">
-        <v>1.4765687227235831</v>
+        <v>1.4762365475314698</v>
       </c>
     </row>
     <row r="205" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -41690,28 +41692,28 @@
         <v>0.46736061424660652</v>
       </c>
       <c r="CT205" s="23">
-        <v>0.19690531939437014</v>
+        <v>0.19699597462080484</v>
       </c>
       <c r="CU205" s="23">
-        <v>0.64577422890693392</v>
+        <v>0.64472856500845055</v>
       </c>
       <c r="CV205" s="23">
-        <v>0.47600375932202327</v>
+        <v>0.47589309180418526</v>
       </c>
       <c r="CW205" s="23">
-        <v>0.74337237842112458</v>
+        <v>0.74250094130835043</v>
       </c>
       <c r="CX205" s="23">
-        <v>0.34804219913923123</v>
+        <v>0.34792554416591137</v>
       </c>
       <c r="CY205" s="23">
-        <v>0.72828281826110541</v>
+        <v>0.72813248072309966</v>
       </c>
       <c r="CZ205" s="23">
-        <v>0.5758150649082171</v>
+        <v>0.57642711864640528</v>
       </c>
       <c r="DA205" s="23">
-        <v>0.74332318880779813</v>
+        <v>0.74383093278394641</v>
       </c>
     </row>
     <row r="206" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -42007,28 +42009,28 @@
         <v>0.10061492167027145</v>
       </c>
       <c r="CT206" s="23">
-        <v>7.7086687909572724E-2</v>
+        <v>7.7122178627492571E-2</v>
       </c>
       <c r="CU206" s="23">
-        <v>9.3061570391184706E-2</v>
+        <v>9.2910881311103352E-2</v>
       </c>
       <c r="CV206" s="23">
-        <v>0.16429603566419107</v>
+        <v>0.16186008455068354</v>
       </c>
       <c r="CW206" s="23">
-        <v>0.19831285562335327</v>
+        <v>0.19808037835173675</v>
       </c>
       <c r="CX206" s="23">
-        <v>0.22934383377129283</v>
+        <v>0.22926696349844711</v>
       </c>
       <c r="CY206" s="23">
-        <v>0.17933763795755731</v>
+        <v>0.17930061775292491</v>
       </c>
       <c r="CZ206" s="23">
-        <v>0.22995667393175342</v>
+        <v>0.23020110282998604</v>
       </c>
       <c r="DA206" s="23">
-        <v>0.22936540398437624</v>
+        <v>0.2295689765582227</v>
       </c>
     </row>
     <row r="207" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -42324,28 +42326,28 @@
         <v>7.6020890342917757E-2</v>
       </c>
       <c r="CT207" s="23">
-        <v>6.8759262004644495E-2</v>
+        <v>6.8790918774942436E-2</v>
       </c>
       <c r="CU207" s="23">
-        <v>4.2188588964437425E-2</v>
+        <v>4.2120275485154207E-2</v>
       </c>
       <c r="CV207" s="23">
-        <v>8.318022676962343E-2</v>
+        <v>8.3137662209158858E-2</v>
       </c>
       <c r="CW207" s="23">
-        <v>7.5239555291129537E-2</v>
+        <v>7.5180994010120752E-2</v>
       </c>
       <c r="CX207" s="23">
-        <v>5.3816124060278636E-2</v>
+        <v>5.3798086251840592E-2</v>
       </c>
       <c r="CY207" s="23">
-        <v>3.2127003682458188E-2</v>
+        <v>3.2120371788205003E-2</v>
       </c>
       <c r="CZ207" s="23">
-        <v>7.5307446696014288E-2</v>
+        <v>7.53874935844559E-2</v>
       </c>
       <c r="DA207" s="23">
-        <v>7.9588711220224234E-2</v>
+        <v>7.9659349941281432E-2</v>
       </c>
     </row>
     <row r="208" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -42641,28 +42643,28 @@
         <v>0.19417997091055367</v>
       </c>
       <c r="CT208" s="23">
-        <v>4.4604490982591498E-2</v>
+        <v>4.4625026894178174E-2</v>
       </c>
       <c r="CU208" s="23">
-        <v>3.8808737609347443E-2</v>
+        <v>3.874978417616335E-2</v>
       </c>
       <c r="CV208" s="23">
-        <v>9.190486147479926E-2</v>
+        <v>9.3980995692299146E-2</v>
       </c>
       <c r="CW208" s="23">
-        <v>0.17026601459099361</v>
+        <v>0.17006641593967717</v>
       </c>
       <c r="CX208" s="23">
-        <v>9.7129144106118698E-2</v>
+        <v>9.7096588864994754E-2</v>
       </c>
       <c r="CY208" s="23">
-        <v>3.0119786510032446E-2</v>
+        <v>3.0113568960427214E-2</v>
       </c>
       <c r="CZ208" s="23">
-        <v>8.1341129142480872E-2</v>
+        <v>8.3286405197558949E-2</v>
       </c>
       <c r="DA208" s="23">
-        <v>0.10307007086446393</v>
+        <v>0.10316155039558732</v>
       </c>
     </row>
     <row r="209" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -42958,28 +42960,28 @@
         <v>5.0470931993162695</v>
       </c>
       <c r="CT209" s="23">
-        <v>5.1469346304072179</v>
+        <v>5.1705599304902643</v>
       </c>
       <c r="CU209" s="23">
-        <v>3.8538899027675613</v>
+        <v>3.8695753892940719</v>
       </c>
       <c r="CV209" s="23">
-        <v>7.0485865084894055</v>
+        <v>6.9742034748647344</v>
       </c>
       <c r="CW209" s="23">
-        <v>5.3619295123817299</v>
+        <v>5.3548469183197414</v>
       </c>
       <c r="CX209" s="23">
-        <v>5.2974379219495455</v>
+        <v>5.3217550555695352</v>
       </c>
       <c r="CY209" s="23">
-        <v>3.8828467258838866</v>
+        <v>3.905247663126616</v>
       </c>
       <c r="CZ209" s="23">
-        <v>6.9757756899955963</v>
+        <v>6.9004033395684647</v>
       </c>
       <c r="DA209" s="23">
-        <v>5.9643531597684696</v>
+        <v>5.9346454092191818</v>
       </c>
     </row>
     <row r="210" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -43275,28 +43277,28 @@
         <v>12.48075651431127</v>
       </c>
       <c r="CT210" s="23">
-        <v>11.603532278997859</v>
+        <v>11.642336908156832</v>
       </c>
       <c r="CU210" s="23">
-        <v>15.352045330072453</v>
+        <v>15.358520208397422</v>
       </c>
       <c r="CV210" s="23">
-        <v>14.189806081048321</v>
+        <v>14.073150851733526</v>
       </c>
       <c r="CW210" s="23">
-        <v>12.524213253389757</v>
+        <v>12.509870181722176</v>
       </c>
       <c r="CX210" s="23">
-        <v>12.783322852985545</v>
+        <v>12.801928790969857</v>
       </c>
       <c r="CY210" s="23">
-        <v>15.504666245292764</v>
+        <v>15.463969143874086</v>
       </c>
       <c r="CZ210" s="23">
-        <v>15.242138909136477</v>
+        <v>15.156666800622427</v>
       </c>
       <c r="DA210" s="23">
-        <v>13.438300484565241</v>
+        <v>13.447566209568276</v>
       </c>
     </row>
     <row r="211" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -43592,28 +43594,28 @@
         <v>10.447684857752389</v>
       </c>
       <c r="CT211" s="23">
-        <v>14.062051622055591</v>
+        <v>14.068525791864229</v>
       </c>
       <c r="CU211" s="23">
-        <v>10.357520331865835</v>
+        <v>10.340749013649603</v>
       </c>
       <c r="CV211" s="23">
-        <v>10.992989599703783</v>
+        <v>10.990433807131158</v>
       </c>
       <c r="CW211" s="23">
-        <v>10.914504786188305</v>
+        <v>10.901709981304061</v>
       </c>
       <c r="CX211" s="23">
-        <v>16.142866918799481</v>
+        <v>16.132210488446557</v>
       </c>
       <c r="CY211" s="23">
-        <v>10.74204820995576</v>
+        <v>10.738023797489742</v>
       </c>
       <c r="CZ211" s="23">
-        <v>12.447658574724251</v>
+        <v>12.409860187017522</v>
       </c>
       <c r="DA211" s="23">
-        <v>12.668327939773977</v>
+        <v>12.678286211707013</v>
       </c>
     </row>
     <row r="212" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -43909,28 +43911,28 @@
         <v>3.5311369345558998</v>
       </c>
       <c r="CT212" s="23">
-        <v>3.63121634124361</v>
+        <v>3.6328881535677322</v>
       </c>
       <c r="CU212" s="23">
-        <v>2.9947239867878421</v>
+        <v>2.9898748078972464</v>
       </c>
       <c r="CV212" s="23">
-        <v>3.4643446615428548</v>
+        <v>3.4635392258354267</v>
       </c>
       <c r="CW212" s="23">
-        <v>3.6872480735908653</v>
+        <v>3.6829256035763667</v>
       </c>
       <c r="CX212" s="23">
-        <v>4.1771874508429603</v>
+        <v>4.175787362888582</v>
       </c>
       <c r="CY212" s="23">
-        <v>3.0760668568793457</v>
+        <v>3.0754318723562886</v>
       </c>
       <c r="CZ212" s="23">
-        <v>3.8178876166469955</v>
+        <v>3.821945781377583</v>
       </c>
       <c r="DA212" s="23">
-        <v>4.1081200931674857</v>
+        <v>4.1117662427894812</v>
       </c>
     </row>
     <row r="213" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -44226,28 +44228,28 @@
         <v>1.2693007572769872E-2</v>
       </c>
       <c r="CT213" s="23">
-        <v>5.0259835968271951E-2</v>
+        <v>5.028297560118937E-2</v>
       </c>
       <c r="CU213" s="23">
-        <v>4.7009906303576279E-2</v>
+        <v>4.6933785951149172E-2</v>
       </c>
       <c r="CV213" s="23">
-        <v>7.3421269484991836E-2</v>
+        <v>7.3404199557514815E-2</v>
       </c>
       <c r="CW213" s="23">
-        <v>1.4465628263995797E-2</v>
+        <v>1.4448670564604792E-2</v>
       </c>
       <c r="CX213" s="23">
-        <v>4.782626449537454E-2</v>
+        <v>4.7810234336898079E-2</v>
       </c>
       <c r="CY213" s="23">
-        <v>3.7400496278129393E-2</v>
+        <v>3.7392775790442929E-2</v>
       </c>
       <c r="CZ213" s="23">
-        <v>8.1909172840869793E-2</v>
+        <v>8.1996236932249819E-2</v>
       </c>
       <c r="DA213" s="23">
-        <v>1.6863416452201588E-2</v>
+        <v>1.6878383526709711E-2</v>
       </c>
     </row>
     <row r="214" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -44543,28 +44545,28 @@
         <v>10.271899737929466</v>
       </c>
       <c r="CT214" s="23">
-        <v>10.832592855490629</v>
+        <v>10.837580182197748</v>
       </c>
       <c r="CU214" s="23">
-        <v>10.072427998911811</v>
+        <v>10.079701948215328</v>
       </c>
       <c r="CV214" s="23">
-        <v>11.734850526343953</v>
+        <v>11.749720434540361</v>
       </c>
       <c r="CW214" s="23">
-        <v>9.8410826751880016</v>
+        <v>9.7798268876197039</v>
       </c>
       <c r="CX214" s="23">
-        <v>10.965298918417981</v>
+        <v>11.044266857449186</v>
       </c>
       <c r="CY214" s="23">
-        <v>10.012631015907029</v>
+        <v>10.036581613418011</v>
       </c>
       <c r="CZ214" s="23">
-        <v>12.48520456495651</v>
+        <v>12.542413890928513</v>
       </c>
       <c r="DA214" s="23">
-        <v>11.065255088325221</v>
+        <v>11.0475948427648</v>
       </c>
     </row>
     <row r="215" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -44860,28 +44862,28 @@
         <v>13.054463497253273</v>
       </c>
       <c r="CT215" s="23">
-        <v>9.1946069639177708</v>
+        <v>9.1988401617757862</v>
       </c>
       <c r="CU215" s="23">
-        <v>17.066716922526464</v>
+        <v>17.039081800292287</v>
       </c>
       <c r="CV215" s="23">
-        <v>9.8607317485764057</v>
+        <v>9.8584391979708492</v>
       </c>
       <c r="CW215" s="23">
-        <v>12.984887973551478</v>
+        <v>12.969666109498096</v>
       </c>
       <c r="CX215" s="23">
-        <v>9.3115991606576962</v>
+        <v>9.3084781473025959</v>
       </c>
       <c r="CY215" s="23">
-        <v>17.835583702470657</v>
+        <v>17.831901949070065</v>
       </c>
       <c r="CZ215" s="23">
-        <v>10.010578238848314</v>
+        <v>10.021218828520086</v>
       </c>
       <c r="DA215" s="23">
-        <v>13.236567342156807</v>
+        <v>13.248315417655231</v>
       </c>
     </row>
     <row r="216" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -45364,7 +45366,7 @@
     </row>
     <row r="224" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="CP224" s="13"/>
       <c r="CQ224" s="13"/>
@@ -45412,7 +45414,7 @@
     </row>
     <row r="227" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CP227" s="13"/>
       <c r="CQ227" s="13"/>
@@ -46242,28 +46244,28 @@
         <v>25.134580049568235</v>
       </c>
       <c r="CT233" s="23">
-        <v>20.856061769750482</v>
+        <v>20.847773722628503</v>
       </c>
       <c r="CU233" s="23">
-        <v>18.486172490921255</v>
+        <v>18.486995024315224</v>
       </c>
       <c r="CV233" s="23">
-        <v>15.830667017560604</v>
+        <v>15.8326878728345</v>
       </c>
       <c r="CW233" s="23">
-        <v>25.51604824471249</v>
+        <v>25.532811649458758</v>
       </c>
       <c r="CX233" s="23">
-        <v>20.617069191807868</v>
+        <v>20.511038297306065</v>
       </c>
       <c r="CY233" s="23">
-        <v>19.734568741126825</v>
+        <v>19.732393657549643</v>
       </c>
       <c r="CZ233" s="23">
-        <v>17.327229952623934</v>
+        <v>17.330265498089179</v>
       </c>
       <c r="DA233" s="23">
-        <v>23.948170519460309</v>
+        <v>23.948927704756766</v>
       </c>
     </row>
     <row r="234" spans="1:105" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -46559,28 +46561,28 @@
         <v>4.4654261359779284</v>
       </c>
       <c r="CT234" s="23">
-        <v>7.2931000143352174</v>
+        <v>7.2902017894809061</v>
       </c>
       <c r="CU234" s="23">
-        <v>3.9111183990075653</v>
+        <v>3.9112924223481214</v>
       </c>
       <c r="CV234" s="23">
-        <v>8.0102216692663646</v>
+        <v>8.0112442098003438</v>
       </c>
       <c r="CW234" s="23">
-        <v>4.5132635373117811</v>
+        <v>4.5162288228241509</v>
       </c>
       <c r="CX234" s="23">
-        <v>6.9168986081437307</v>
+        <v>6.9196522757990824</v>
       </c>
       <c r="CY234" s="23">
-        <v>4.7470733745350433</v>
+        <v>4.7465501666822609</v>
       </c>
       <c r="CZ234" s="23">
-        <v>7.5591345473729632</v>
+        <v>7.5604588269409732</v>
       </c>
       <c r="DA234" s="23">
-        <v>4.6107364256332461</v>
+        <v>4.5908846175203815</v>
       </c>
     </row>
     <row r="235" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -46876,28 +46878,28 @@
         <v>4.1615843800730872</v>
       </c>
       <c r="CT235" s="23">
-        <v>5.8386748115853173</v>
+        <v>5.8363545647188388</v>
       </c>
       <c r="CU235" s="23">
-        <v>3.2559240229126969</v>
+        <v>3.2560688936931896</v>
       </c>
       <c r="CV235" s="23">
-        <v>5.4070730962371485</v>
+        <v>5.4077633332417383</v>
       </c>
       <c r="CW235" s="23">
-        <v>4.0820207804643331</v>
+        <v>4.0847025658987128</v>
       </c>
       <c r="CX235" s="23">
-        <v>5.6685907758419116</v>
+        <v>5.6708474830679618</v>
       </c>
       <c r="CY235" s="23">
-        <v>3.1049250334425236</v>
+        <v>3.1045828181381396</v>
       </c>
       <c r="CZ235" s="23">
-        <v>5.1449233675448207</v>
+        <v>5.1458247031212565</v>
       </c>
       <c r="DA235" s="23">
-        <v>4.0477176567491</v>
+        <v>4.0478456361407371</v>
       </c>
     </row>
     <row r="236" spans="1:105" s="9" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -47193,28 +47195,28 @@
         <v>1.5922830893696653</v>
       </c>
       <c r="CT236" s="23">
-        <v>2.9243912842272164</v>
+        <v>2.923229152419478</v>
       </c>
       <c r="CU236" s="23">
-        <v>0.83780394409962811</v>
+        <v>0.83784122178498788</v>
       </c>
       <c r="CV236" s="23">
-        <v>7.1270670948227324E-2</v>
+        <v>7.1279768967350568E-2</v>
       </c>
       <c r="CW236" s="23">
-        <v>1.2481064116894784</v>
+        <v>1.2423269655530316</v>
       </c>
       <c r="CX236" s="23">
-        <v>3.4040314889574264</v>
+        <v>3.4053866586570232</v>
       </c>
       <c r="CY236" s="23">
-        <v>3.1899334944161142</v>
+        <v>3.1895819097401565</v>
       </c>
       <c r="CZ236" s="23">
-        <v>9.8396489056718286E-2</v>
+        <v>9.841372706977454E-2</v>
       </c>
       <c r="DA236" s="23">
-        <v>1.2320029547170284</v>
+        <v>1.2320419077770022</v>
       </c>
     </row>
     <row r="237" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -47510,28 +47512,28 @@
         <v>6.4187988948002799</v>
       </c>
       <c r="CT237" s="23">
-        <v>6.4955255324304986</v>
+        <v>6.4929442578692136</v>
       </c>
       <c r="CU237" s="23">
-        <v>8.1470927352704585</v>
+        <v>8.14745523626096</v>
       </c>
       <c r="CV237" s="23">
-        <v>8.7426706254657791</v>
+        <v>8.7437866663768666</v>
       </c>
       <c r="CW237" s="23">
-        <v>6.1492127260377876</v>
+        <v>6.1532526048156013</v>
       </c>
       <c r="CX237" s="23">
-        <v>6.4420786788299367</v>
+        <v>6.4446433172171798</v>
       </c>
       <c r="CY237" s="23">
-        <v>7.4715317263800056</v>
+        <v>7.470708237092369</v>
       </c>
       <c r="CZ237" s="23">
-        <v>8.477871028320962</v>
+        <v>8.4793562606994382</v>
       </c>
       <c r="DA237" s="23">
-        <v>6.0872564354239405</v>
+        <v>6.0874489002748531</v>
       </c>
     </row>
     <row r="238" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -47827,28 +47829,28 @@
         <v>1.4524094031328363</v>
       </c>
       <c r="CT238" s="23">
-        <v>1.3616219627925106</v>
+        <v>1.3610808641366599</v>
       </c>
       <c r="CU238" s="23">
-        <v>4.8570644137622674</v>
+        <v>4.8572805265178394</v>
       </c>
       <c r="CV238" s="23">
-        <v>0.58748538697552311</v>
+        <v>0.58756038210625816</v>
       </c>
       <c r="CW238" s="23">
-        <v>1.4197568821962336</v>
+        <v>1.4206896269155294</v>
       </c>
       <c r="CX238" s="23">
-        <v>1.2261076621672153</v>
+        <v>1.2265957845472821</v>
       </c>
       <c r="CY238" s="23">
-        <v>4.1150000433306282</v>
+        <v>4.1145465006598076</v>
       </c>
       <c r="CZ238" s="23">
-        <v>0.61392175016197648</v>
+        <v>0.6140293026899809</v>
       </c>
       <c r="DA238" s="23">
-        <v>1.4357195229455999</v>
+        <v>1.4357649170483238</v>
       </c>
     </row>
     <row r="239" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -48144,28 +48146,28 @@
         <v>1.7654240701100263</v>
       </c>
       <c r="CT239" s="23">
-        <v>1.6112400210118849</v>
+        <v>1.6105997259568356</v>
       </c>
       <c r="CU239" s="23">
-        <v>1.5782643792775104</v>
+        <v>1.5783346033954075</v>
       </c>
       <c r="CV239" s="23">
-        <v>1.6909687380867369</v>
+        <v>1.6911845977904727</v>
       </c>
       <c r="CW239" s="23">
-        <v>1.7608569489587704</v>
+        <v>1.7620137878804003</v>
       </c>
       <c r="CX239" s="23">
-        <v>1.6081927420698707</v>
+        <v>1.6088329752998614</v>
       </c>
       <c r="CY239" s="23">
-        <v>1.4732689536082477</v>
+        <v>1.4731065744274405</v>
       </c>
       <c r="CZ239" s="23">
-        <v>1.5922173392185663</v>
+        <v>1.5924962786761119</v>
       </c>
       <c r="DA239" s="23">
-        <v>1.6934991063970382</v>
+        <v>1.69355265088896</v>
       </c>
     </row>
     <row r="240" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -48461,28 +48463,28 @@
         <v>0.45929940860229668</v>
       </c>
       <c r="CT240" s="23">
-        <v>0.64956468431508063</v>
+        <v>0.64930655203815246</v>
       </c>
       <c r="CU240" s="23">
-        <v>0.12964017077337114</v>
+        <v>0.12964593905069915</v>
       </c>
       <c r="CV240" s="23">
-        <v>0.15310931744227727</v>
+        <v>0.15312886252975161</v>
       </c>
       <c r="CW240" s="23">
-        <v>0.45465817867676822</v>
+        <v>0.45495687771500731</v>
       </c>
       <c r="CX240" s="23">
-        <v>0.69198032330270065</v>
+        <v>0.69225580570346545</v>
       </c>
       <c r="CY240" s="23">
-        <v>0.13675204454117942</v>
+        <v>0.13673697215068892</v>
       </c>
       <c r="CZ240" s="23">
-        <v>0.18498002561610932</v>
+        <v>0.18501243213922094</v>
       </c>
       <c r="DA240" s="23">
-        <v>0.49034450982708733</v>
+        <v>0.49036001337683605</v>
       </c>
     </row>
     <row r="241" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -48778,28 +48780,28 @@
         <v>1.0985826446235853</v>
       </c>
       <c r="CT241" s="23">
-        <v>0.76522879723175108</v>
+        <v>0.76483456201158362</v>
       </c>
       <c r="CU241" s="23">
-        <v>1.2613847377892691</v>
+        <v>1.2614408624992373</v>
       </c>
       <c r="CV241" s="23">
-        <v>1.094838729660337</v>
+        <v>1.1473036804751562</v>
       </c>
       <c r="CW241" s="23">
-        <v>1.0215353326815257</v>
+        <v>1.0222064558147053</v>
       </c>
       <c r="CX241" s="23">
-        <v>0.74840719687664237</v>
+        <v>0.74844291971212751</v>
       </c>
       <c r="CY241" s="23">
-        <v>1.187049741832829</v>
+        <v>1.1869189088547878</v>
       </c>
       <c r="CZ241" s="23">
-        <v>1.0078369205660502</v>
+        <v>1.0584993716557352</v>
       </c>
       <c r="DA241" s="23">
-        <v>0.98400023044395069</v>
+        <v>0.98403134223621036</v>
       </c>
     </row>
     <row r="242" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -49095,28 +49097,28 @@
         <v>0.58583876183983785</v>
       </c>
       <c r="CT242" s="23">
-        <v>0.1946485280638183</v>
+        <v>0.19457117615574343</v>
       </c>
       <c r="CU242" s="23">
-        <v>0.67029116001610456</v>
+        <v>0.67032098430034015</v>
       </c>
       <c r="CV242" s="23">
-        <v>0.47358704127646417</v>
+        <v>0.47364749677520912</v>
       </c>
       <c r="CW242" s="23">
-        <v>0.58216739211467605</v>
+        <v>0.5825498615131699</v>
       </c>
       <c r="CX242" s="23">
-        <v>0.21620347230114084</v>
+        <v>0.21628954447631327</v>
       </c>
       <c r="CY242" s="23">
-        <v>0.67262457115957019</v>
+        <v>0.67255043654444235</v>
       </c>
       <c r="CZ242" s="23">
-        <v>0.49216721508007061</v>
+        <v>0.49225343751504513</v>
       </c>
       <c r="DA242" s="23">
-        <v>0.6073263926333522</v>
+        <v>0.60734559487739326</v>
       </c>
     </row>
     <row r="243" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -49412,28 +49414,28 @@
         <v>0.1113947677535706</v>
       </c>
       <c r="CT243" s="23">
-        <v>0.13707922499976269</v>
+        <v>0.13702475071363976</v>
       </c>
       <c r="CU243" s="23">
-        <v>0.13427998034812882</v>
+        <v>0.13428595507156238</v>
       </c>
       <c r="CV243" s="23">
-        <v>0.10399752943074562</v>
+        <v>0.10249063640549384</v>
       </c>
       <c r="CW243" s="23">
-        <v>0.10700794199850305</v>
+        <v>0.10707824353679699</v>
       </c>
       <c r="CX243" s="23">
-        <v>0.16448601213901934</v>
+        <v>0.16455149521706411</v>
       </c>
       <c r="CY243" s="23">
-        <v>0.13825212771477316</v>
+        <v>0.13823688998972086</v>
       </c>
       <c r="CZ243" s="23">
-        <v>0.10076412596299325</v>
+        <v>0.10078177876072622</v>
       </c>
       <c r="DA243" s="23">
-        <v>0.11348235912665625</v>
+        <v>0.11348594717417194</v>
       </c>
     </row>
     <row r="244" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -49729,28 +49731,28 @@
         <v>9.5152351548730182E-2</v>
       </c>
       <c r="CT244" s="23">
-        <v>0.10536421648936621</v>
+        <v>0.1053223455167504</v>
       </c>
       <c r="CU244" s="23">
-        <v>9.7477315493256333E-2</v>
+        <v>9.7481652699737936E-2</v>
       </c>
       <c r="CV244" s="23">
-        <v>7.9359954803205124E-2</v>
+        <v>7.9347822247625224E-2</v>
       </c>
       <c r="CW244" s="23">
-        <v>9.6542403210557445E-2</v>
+        <v>9.6643906615314967E-2</v>
       </c>
       <c r="CX244" s="23">
-        <v>8.7162639177772047E-2</v>
+        <v>8.7197339258524464E-2</v>
       </c>
       <c r="CY244" s="23">
-        <v>7.4952431862847266E-2</v>
+        <v>7.494417083592779E-2</v>
       </c>
       <c r="CZ244" s="23">
-        <v>6.8129805148380587E-2</v>
+        <v>6.8141740761957115E-2</v>
       </c>
       <c r="DA244" s="23">
-        <v>8.5501980203919942E-2</v>
+        <v>8.5504683577113966E-2</v>
       </c>
     </row>
     <row r="245" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -50046,28 +50048,28 @@
         <v>0.17728562084790425</v>
       </c>
       <c r="CT245" s="23">
-        <v>7.5994672232009924E-2</v>
+        <v>7.5964472502481312E-2</v>
       </c>
       <c r="CU245" s="23">
-        <v>8.8806987516896974E-2</v>
+        <v>8.8810938941286555E-2</v>
       </c>
       <c r="CV245" s="23">
-        <v>0.1165815271824583</v>
+        <v>0.1165964093345359</v>
       </c>
       <c r="CW245" s="23">
-        <v>0.22704986122079948</v>
+        <v>0.22719902729403796</v>
       </c>
       <c r="CX245" s="23">
-        <v>0.13240309843171422</v>
+        <v>0.1324558090684135</v>
       </c>
       <c r="CY245" s="23">
-        <v>8.9896089198595278E-2</v>
+        <v>8.9886181127644557E-2</v>
       </c>
       <c r="CZ245" s="23">
-        <v>0.13109899899685468</v>
+        <v>0.13112196614007327</v>
       </c>
       <c r="DA245" s="23">
-        <v>0.22974663072377755</v>
+        <v>0.22975389477639285</v>
       </c>
     </row>
     <row r="246" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -50363,28 +50365,28 @@
         <v>4.8028383575585902</v>
       </c>
       <c r="CT246" s="23">
-        <v>5.7394339409820798</v>
+        <v>5.7638498511741956</v>
       </c>
       <c r="CU246" s="23">
-        <v>5.3758367653519814</v>
+        <v>5.376075960634954</v>
       </c>
       <c r="CV246" s="23">
-        <v>4.6471763809003193</v>
+        <v>4.5997602850057824</v>
       </c>
       <c r="CW246" s="23">
-        <v>4.6028533281644721</v>
+        <v>4.6094457820046308</v>
       </c>
       <c r="CX246" s="23">
-        <v>5.7232216182932172</v>
+        <v>5.7255000744550797</v>
       </c>
       <c r="CY246" s="23">
-        <v>5.3181949629777794</v>
+        <v>5.3176088078569874</v>
       </c>
       <c r="CZ246" s="23">
-        <v>4.3595937873798247</v>
+        <v>4.3127700850540585</v>
       </c>
       <c r="DA246" s="23">
-        <v>4.5294186320820069</v>
+        <v>4.5284656109117654</v>
       </c>
     </row>
     <row r="247" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -50680,28 +50682,28 @@
         <v>9.3439310739340495</v>
       </c>
       <c r="CT247" s="23">
-        <v>10.147703286328005</v>
+        <v>10.15680335435437</v>
       </c>
       <c r="CU247" s="23">
-        <v>11.109462302272899</v>
+        <v>11.113610161261796</v>
       </c>
       <c r="CV247" s="23">
-        <v>10.887309314208995</v>
+        <v>10.863968270712689</v>
       </c>
       <c r="CW247" s="23">
-        <v>8.9346622598352496</v>
+        <v>8.9407744050287548</v>
       </c>
       <c r="CX247" s="23">
-        <v>9.6943153104047362</v>
+        <v>9.7102612499491663</v>
       </c>
       <c r="CY247" s="23">
-        <v>9.7981711587707689</v>
+        <v>9.7985238941549557</v>
       </c>
       <c r="CZ247" s="23">
-        <v>10.413940111098254</v>
+        <v>10.393870329304924</v>
       </c>
       <c r="DA247" s="23">
-        <v>8.9855402075267996</v>
+        <v>8.9899121619062541</v>
       </c>
     </row>
     <row r="248" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -50997,28 +50999,28 @@
         <v>10.891149745101664</v>
       </c>
       <c r="CT248" s="23">
-        <v>12.047121379608532</v>
+        <v>12.042333941271382</v>
       </c>
       <c r="CU248" s="23">
-        <v>10.940622596654899</v>
+        <v>10.941109394419065</v>
       </c>
       <c r="CV248" s="23">
-        <v>11.711414386687276</v>
+        <v>11.712909400984643</v>
       </c>
       <c r="CW248" s="23">
-        <v>11.748558845946119</v>
+        <v>11.756277354910795</v>
       </c>
       <c r="CX248" s="23">
-        <v>12.940758405492151</v>
+        <v>12.941166473169316</v>
       </c>
       <c r="CY248" s="23">
-        <v>10.936325996634947</v>
+        <v>10.935120628360522</v>
       </c>
       <c r="CZ248" s="23">
-        <v>12.594835156560173</v>
+        <v>12.597041637044908</v>
       </c>
       <c r="DA248" s="23">
-        <v>12.66868581408346</v>
+        <v>12.669086368381171</v>
       </c>
     </row>
     <row r="249" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -51314,28 +51316,28 @@
         <v>3.8717079994847041</v>
       </c>
       <c r="CT249" s="23">
-        <v>4.3075149472837655</v>
+        <v>4.3058031722010162</v>
       </c>
       <c r="CU249" s="23">
-        <v>4.3648378201662901</v>
+        <v>4.3650320315352529</v>
       </c>
       <c r="CV249" s="23">
-        <v>4.421260720933633</v>
+        <v>4.4218251145902778</v>
       </c>
       <c r="CW249" s="23">
-        <v>3.9358012515561445</v>
+        <v>3.9383869744215332</v>
       </c>
       <c r="CX249" s="23">
-        <v>4.3726227708655214</v>
+        <v>4.3743635438008086</v>
       </c>
       <c r="CY249" s="23">
-        <v>4.1146711646490202</v>
+        <v>4.114217658226198</v>
       </c>
       <c r="CZ249" s="23">
-        <v>4.4995635700799079</v>
+        <v>4.5003518455185141</v>
       </c>
       <c r="DA249" s="23">
-        <v>4.0974527094239921</v>
+        <v>4.0975822613219952</v>
       </c>
     </row>
     <row r="250" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -51631,28 +51633,28 @@
         <v>3.8760386418753637E-2</v>
       </c>
       <c r="CT250" s="23">
-        <v>0.18217367237656248</v>
+        <v>0.18210127788532485</v>
       </c>
       <c r="CU250" s="23">
-        <v>0.17641941298248182</v>
+        <v>0.17642726267979444</v>
       </c>
       <c r="CV250" s="23">
-        <v>0.25369964283828189</v>
+        <v>0.25373202872958051</v>
       </c>
       <c r="CW250" s="23">
-        <v>4.4709020143440761E-2</v>
+        <v>4.4738392850110914E-2</v>
       </c>
       <c r="CX250" s="23">
-        <v>0.17354954954788407</v>
+        <v>0.17361864088610723</v>
       </c>
       <c r="CY250" s="23">
-        <v>0.13956589909722983</v>
+        <v>0.13955051657232934</v>
       </c>
       <c r="CZ250" s="23">
-        <v>0.26697235725739482</v>
+        <v>0.26701912796053856</v>
       </c>
       <c r="DA250" s="23">
-        <v>5.093161827076393E-2</v>
+        <v>5.09332286097436E-2</v>
       </c>
     </row>
     <row r="251" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -51948,28 +51950,28 @@
         <v>12.310038999099195</v>
       </c>
       <c r="CT251" s="23">
-        <v>10.133872770999611</v>
+        <v>10.129845643731697</v>
       </c>
       <c r="CU251" s="23">
-        <v>10.652135265319519</v>
+        <v>10.644506226074226</v>
       </c>
       <c r="CV251" s="23">
-        <v>12.006977129455143</v>
+        <v>12.017701855514545</v>
       </c>
       <c r="CW251" s="23">
-        <v>12.458454668790422</v>
+        <v>12.403692434305501</v>
       </c>
       <c r="CX251" s="23">
-        <v>10.056442304665801</v>
+        <v>10.127793223559811</v>
       </c>
       <c r="CY251" s="23">
-        <v>9.5148844923994975</v>
+        <v>9.5234248242947928</v>
       </c>
       <c r="CZ251" s="23">
-        <v>11.377721729031931</v>
+        <v>11.381191813721406</v>
       </c>
       <c r="DA251" s="23">
-        <v>12.841301078426199</v>
+        <v>12.855551290762934</v>
       </c>
     </row>
     <row r="252" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -52265,28 +52267,28 @@
         <v>11.223513860155071</v>
       </c>
       <c r="CT252" s="23">
-        <v>9.1336844829565234</v>
+        <v>9.1300548232332339</v>
       </c>
       <c r="CU252" s="23">
-        <v>13.925365100063534</v>
+        <v>13.925984702516322</v>
       </c>
       <c r="CV252" s="23">
-        <v>13.710331120640509</v>
+        <v>13.712081305577206</v>
       </c>
       <c r="CW252" s="23">
-        <v>11.09673398429045</v>
+        <v>11.104024260643445</v>
       </c>
       <c r="CX252" s="23">
-        <v>9.1154781506837388</v>
+        <v>9.1191070888493275</v>
       </c>
       <c r="CY252" s="23">
-        <v>14.042357952321559</v>
+        <v>14.040810246741181</v>
       </c>
       <c r="CZ252" s="23">
-        <v>13.688701722922101</v>
+        <v>13.691099837136186</v>
       </c>
       <c r="DA252" s="23">
-        <v>11.261165215901782</v>
+        <v>11.261521267680999</v>
       </c>
     </row>
     <row r="253" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/Data/National Accounts/PSA-08AFF_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-08AFF_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16976DA2-E70A-4E8E-8D39-A2C223FB7FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C8832C4-910F-42FE-BA24-FD9440A1D727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="AFF" sheetId="8" r:id="rId1"/>
@@ -521,7 +521,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="72">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -732,23 +732,27 @@
     <t>Table 9.7 Gross Value Added in Agriculture, Forestry, and Fishing, by Industry</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>Q1 2000 to Q1 2026</t>
   </si>
   <si>
-    <t>As of April 2026</t>
+    <t>As of May 2026</t>
+  </si>
+  <si>
+    <t>2025 - 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -791,6 +795,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Microsoft Sans Serif"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="Microsoft Sans Serif"/>
       <family val="2"/>
     </font>
@@ -838,7 +848,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -894,6 +904,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma 2" xfId="3" xr:uid="{0662CF8E-D90D-4FC2-9E33-010BFB9B5552}"/>
@@ -1236,16 +1248,16 @@
   <sheetPr transitionEvaluation="1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:DA262"/>
+  <dimension ref="A1:DB262"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
     <col min="2" max="93" width="13" style="8" customWidth="1"/>
-    <col min="94" max="105" width="13" style="17" customWidth="1"/>
-    <col min="106" max="16384" width="10" style="8"/>
+    <col min="94" max="106" width="13" style="17" customWidth="1"/>
+    <col min="107" max="16384" width="10" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1261,8 +1273,9 @@
       <c r="CY1" s="13"/>
       <c r="CZ1" s="13"/>
       <c r="DA1" s="13"/>
+      <c r="DB1" s="13"/>
     </row>
-    <row r="2" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>58</v>
       </c>
@@ -1278,8 +1291,9 @@
       <c r="CY2" s="13"/>
       <c r="CZ2" s="13"/>
       <c r="DA2" s="13"/>
+      <c r="DB2" s="13"/>
     </row>
-    <row r="3" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>70</v>
       </c>
@@ -1295,8 +1309,9 @@
       <c r="CY3" s="13"/>
       <c r="CZ3" s="13"/>
       <c r="DA3" s="13"/>
+      <c r="DB3" s="13"/>
     </row>
-    <row r="4" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP4" s="13"/>
       <c r="CQ4" s="13"/>
       <c r="CR4" s="13"/>
@@ -1309,8 +1324,9 @@
       <c r="CY4" s="13"/>
       <c r="CZ4" s="13"/>
       <c r="DA4" s="13"/>
+      <c r="DB4" s="13"/>
     </row>
-    <row r="5" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>61</v>
       </c>
@@ -1326,8 +1342,9 @@
       <c r="CY5" s="13"/>
       <c r="CZ5" s="13"/>
       <c r="DA5" s="13"/>
+      <c r="DB5" s="13"/>
     </row>
-    <row r="6" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>69</v>
       </c>
@@ -1343,8 +1360,9 @@
       <c r="CY6" s="13"/>
       <c r="CZ6" s="13"/>
       <c r="DA6" s="13"/>
+      <c r="DB6" s="13"/>
     </row>
-    <row r="7" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
@@ -1360,8 +1378,9 @@
       <c r="CY7" s="13"/>
       <c r="CZ7" s="13"/>
       <c r="DA7" s="13"/>
+      <c r="DB7" s="13"/>
     </row>
-    <row r="8" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP8" s="13"/>
       <c r="CQ8" s="13"/>
       <c r="CR8" s="13"/>
@@ -1374,8 +1393,9 @@
       <c r="CY8" s="13"/>
       <c r="CZ8" s="13"/>
       <c r="DA8" s="13"/>
+      <c r="DB8" s="13"/>
     </row>
-    <row r="9" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6"/>
       <c r="B9" s="6">
         <v>2000</v>
@@ -1533,8 +1553,11 @@
       <c r="CY9" s="14"/>
       <c r="CZ9" s="14"/>
       <c r="DA9" s="14"/>
+      <c r="DB9" s="14">
+        <v>2026</v>
+      </c>
     </row>
-    <row r="10" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
@@ -1850,8 +1873,11 @@
       <c r="DA10" s="15" t="s">
         <v>5</v>
       </c>
+      <c r="DB10" s="15" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="11" spans="1:105" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:106" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
       <c r="CP11" s="13"/>
       <c r="CQ11" s="13"/>
@@ -1865,8 +1891,9 @@
       <c r="CY11" s="13"/>
       <c r="CZ11" s="13"/>
       <c r="DA11" s="13"/>
+      <c r="DB11" s="13"/>
     </row>
-    <row r="12" spans="1:105" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:106" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>38</v>
       </c>
@@ -2182,8 +2209,11 @@
       <c r="DA12" s="16">
         <v>122721.45210135281</v>
       </c>
+      <c r="DB12" s="29">
+        <v>108757.51438354692</v>
+      </c>
     </row>
-    <row r="13" spans="1:105" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:106" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>39</v>
       </c>
@@ -2499,8 +2529,11 @@
       <c r="DA13" s="16">
         <v>30523.532859554041</v>
       </c>
+      <c r="DB13" s="29">
+        <v>39459.75368267858</v>
+      </c>
     </row>
-    <row r="14" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>40</v>
       </c>
@@ -2816,8 +2849,11 @@
       <c r="DA14" s="16">
         <v>26341.735475995567</v>
       </c>
+      <c r="DB14" s="29">
+        <v>30162.110239639835</v>
+      </c>
     </row>
-    <row r="15" spans="1:105" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:106" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>41</v>
       </c>
@@ -3133,8 +3169,11 @@
       <c r="DA15" s="16">
         <v>9544.9036814210776</v>
       </c>
+      <c r="DB15" s="29">
+        <v>12969.373879613013</v>
+      </c>
     </row>
-    <row r="16" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -3450,8 +3489,11 @@
       <c r="DA16" s="16">
         <v>32685.266917563386</v>
       </c>
+      <c r="DB16" s="29">
+        <v>31773.037706684332</v>
+      </c>
     </row>
-    <row r="17" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>43</v>
       </c>
@@ -3767,8 +3809,11 @@
       <c r="DA17" s="16">
         <v>8922.6460454616954</v>
       </c>
+      <c r="DB17" s="29">
+        <v>6558.1369477891358</v>
+      </c>
     </row>
-    <row r="18" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>44</v>
       </c>
@@ -4084,8 +4129,11 @@
       <c r="DA18" s="16">
         <v>14166.015180565282</v>
       </c>
+      <c r="DB18" s="29">
+        <v>8596.8199891107197</v>
+      </c>
     </row>
-    <row r="19" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>45</v>
       </c>
@@ -4401,8 +4449,11 @@
       <c r="DA19" s="16">
         <v>9477.3859627919792</v>
       </c>
+      <c r="DB19" s="29">
+        <v>6971.4273511133897</v>
+      </c>
     </row>
-    <row r="20" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>46</v>
       </c>
@@ -4718,8 +4769,11 @@
       <c r="DA20" s="16">
         <v>10181.779788558068</v>
       </c>
+      <c r="DB20" s="29">
+        <v>4900.800166702038</v>
+      </c>
     </row>
-    <row r="21" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>47</v>
       </c>
@@ -5035,8 +5089,11 @@
       <c r="DA21" s="16">
         <v>5130.2907858419831</v>
       </c>
+      <c r="DB21" s="29">
+        <v>2314.5240609476923</v>
+      </c>
     </row>
-    <row r="22" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>48</v>
       </c>
@@ -5352,8 +5409,11 @@
       <c r="DA22" s="16">
         <v>1583.3646508136221</v>
       </c>
+      <c r="DB22" s="29">
+        <v>976.81507743891757</v>
+      </c>
     </row>
-    <row r="23" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>49</v>
       </c>
@@ -5669,8 +5729,11 @@
       <c r="DA23" s="16">
         <v>549.4200509790071</v>
       </c>
+      <c r="DB23" s="29">
+        <v>277.71710778113635</v>
+      </c>
     </row>
-    <row r="24" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>50</v>
       </c>
@@ -5986,8 +6049,11 @@
       <c r="DA24" s="16">
         <v>711.51753459193787</v>
       </c>
+      <c r="DB24" s="29">
+        <v>682.47082975460739</v>
+      </c>
     </row>
-    <row r="25" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>51</v>
       </c>
@@ -6303,8 +6369,11 @@
       <c r="DA25" s="16">
         <v>40931.95821556414</v>
       </c>
+      <c r="DB25" s="29">
+        <v>34612.022699261142</v>
+      </c>
     </row>
-    <row r="26" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>52</v>
       </c>
@@ -6620,8 +6689,11 @@
       <c r="DA26" s="16">
         <v>92749.470311403391</v>
       </c>
+      <c r="DB26" s="29">
+        <v>73228.141925532691</v>
+      </c>
     </row>
-    <row r="27" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>53</v>
       </c>
@@ -6937,8 +7009,11 @@
       <c r="DA27" s="16">
         <v>87443.654284111981</v>
       </c>
+      <c r="DB27" s="29">
+        <v>103814.20643894127</v>
+      </c>
     </row>
-    <row r="28" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>54</v>
       </c>
@@ -7254,8 +7329,11 @@
       <c r="DA28" s="16">
         <v>28359.34288181334</v>
       </c>
+      <c r="DB28" s="29">
+        <v>25394.898459068885</v>
+      </c>
     </row>
-    <row r="29" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>55</v>
       </c>
@@ -7571,8 +7649,11 @@
       <c r="DA29" s="16">
         <v>116.41222712115581</v>
       </c>
+      <c r="DB29" s="29">
+        <v>297.84178580125354</v>
+      </c>
     </row>
-    <row r="30" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>56</v>
       </c>
@@ -7888,8 +7969,11 @@
       <c r="DA30" s="16">
         <v>76196.58114435288</v>
       </c>
+      <c r="DB30" s="29">
+        <v>68942.99913585496</v>
+      </c>
     </row>
-    <row r="31" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>57</v>
       </c>
@@ -8205,9 +8289,12 @@
       <c r="DA31" s="16">
         <v>91375.213801261561</v>
       </c>
+      <c r="DB31" s="29">
+        <v>57714.234934125532</v>
+      </c>
     </row>
-    <row r="32" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" spans="1:105" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" spans="1:106" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>62</v>
       </c>
@@ -8523,8 +8610,11 @@
       <c r="DA33" s="18">
         <v>689711.94390111906</v>
       </c>
+      <c r="DB33" s="30">
+        <v>618404.8468013861</v>
+      </c>
     </row>
-    <row r="34" spans="1:105" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:106" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
@@ -8630,8 +8720,9 @@
       <c r="CY34" s="19"/>
       <c r="CZ34" s="19"/>
       <c r="DA34" s="19"/>
+      <c r="DB34" s="19"/>
     </row>
-    <row r="35" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>6</v>
       </c>
@@ -8647,10 +8738,11 @@
       <c r="CY35" s="13"/>
       <c r="CZ35" s="13"/>
       <c r="DA35" s="13"/>
+      <c r="DB35" s="13"/>
     </row>
-    <row r="36" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>0</v>
       </c>
@@ -8666,8 +8758,9 @@
       <c r="CY38" s="13"/>
       <c r="CZ38" s="13"/>
       <c r="DA38" s="13"/>
+      <c r="DB38" s="13"/>
     </row>
-    <row r="39" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>58</v>
       </c>
@@ -8683,8 +8776,9 @@
       <c r="CY39" s="13"/>
       <c r="CZ39" s="13"/>
       <c r="DA39" s="13"/>
+      <c r="DB39" s="13"/>
     </row>
-    <row r="40" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>70</v>
       </c>
@@ -8700,8 +8794,9 @@
       <c r="CY40" s="13"/>
       <c r="CZ40" s="13"/>
       <c r="DA40" s="13"/>
+      <c r="DB40" s="13"/>
     </row>
-    <row r="41" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP41" s="13"/>
       <c r="CQ41" s="13"/>
       <c r="CR41" s="13"/>
@@ -8714,8 +8809,9 @@
       <c r="CY41" s="13"/>
       <c r="CZ41" s="13"/>
       <c r="DA41" s="13"/>
+      <c r="DB41" s="13"/>
     </row>
-    <row r="42" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>63</v>
       </c>
@@ -8731,8 +8827,9 @@
       <c r="CY42" s="13"/>
       <c r="CZ42" s="13"/>
       <c r="DA42" s="13"/>
+      <c r="DB42" s="13"/>
     </row>
-    <row r="43" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>69</v>
       </c>
@@ -8748,8 +8845,9 @@
       <c r="CY43" s="13"/>
       <c r="CZ43" s="13"/>
       <c r="DA43" s="13"/>
+      <c r="DB43" s="13"/>
     </row>
-    <row r="44" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>7</v>
       </c>
@@ -8765,8 +8863,9 @@
       <c r="CY44" s="13"/>
       <c r="CZ44" s="13"/>
       <c r="DA44" s="13"/>
+      <c r="DB44" s="13"/>
     </row>
-    <row r="45" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP45" s="13"/>
       <c r="CQ45" s="13"/>
       <c r="CR45" s="13"/>
@@ -8779,8 +8878,9 @@
       <c r="CY45" s="13"/>
       <c r="CZ45" s="13"/>
       <c r="DA45" s="13"/>
+      <c r="DB45" s="13"/>
     </row>
-    <row r="46" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6"/>
       <c r="B46" s="6">
         <v>2000</v>
@@ -8938,8 +9038,11 @@
       <c r="CY46" s="14"/>
       <c r="CZ46" s="14"/>
       <c r="DA46" s="14"/>
+      <c r="DB46" s="14">
+        <v>2026</v>
+      </c>
     </row>
-    <row r="47" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>37</v>
       </c>
@@ -9255,8 +9358,11 @@
       <c r="DA47" s="15" t="s">
         <v>5</v>
       </c>
+      <c r="DB47" s="15" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:105" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:106" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4"/>
       <c r="CP48" s="13"/>
       <c r="CQ48" s="13"/>
@@ -9270,8 +9376,9 @@
       <c r="CY48" s="13"/>
       <c r="CZ48" s="13"/>
       <c r="DA48" s="13"/>
+      <c r="DB48" s="13"/>
     </row>
-    <row r="49" spans="1:105" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:106" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>38</v>
       </c>
@@ -9587,8 +9694,11 @@
       <c r="DA49" s="16">
         <v>126644.06942511139</v>
       </c>
+      <c r="DB49" s="29">
+        <v>87809.533085649833</v>
+      </c>
     </row>
-    <row r="50" spans="1:105" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:106" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>39</v>
       </c>
@@ -9904,8 +10014,11 @@
       <c r="DA50" s="16">
         <v>24277.008031071346</v>
       </c>
+      <c r="DB50" s="29">
+        <v>29863.217815205055</v>
+      </c>
     </row>
-    <row r="51" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>40</v>
       </c>
@@ -10221,8 +10334,11 @@
       <c r="DA51" s="16">
         <v>21405.369379595286</v>
       </c>
+      <c r="DB51" s="29">
+        <v>26264.765030406281</v>
+      </c>
     </row>
-    <row r="52" spans="1:105" s="9" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:106" s="9" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
         <v>41</v>
       </c>
@@ -10538,8 +10654,11 @@
       <c r="DA52" s="16">
         <v>6515.1476853874465</v>
       </c>
+      <c r="DB52" s="29">
+        <v>14312.103769934742</v>
+      </c>
     </row>
-    <row r="53" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>42</v>
       </c>
@@ -10855,8 +10974,11 @@
       <c r="DA53" s="16">
         <v>32190.973669151022</v>
       </c>
+      <c r="DB53" s="29">
+        <v>28650.550411213746</v>
+      </c>
     </row>
-    <row r="54" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>43</v>
       </c>
@@ -11172,8 +11294,11 @@
       <c r="DA54" s="16">
         <v>7592.4531600924947</v>
       </c>
+      <c r="DB54" s="29">
+        <v>5580.8925768254903</v>
+      </c>
     </row>
-    <row r="55" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>44</v>
       </c>
@@ -11489,8 +11614,11 @@
       <c r="DA55" s="16">
         <v>8955.6577287451128</v>
       </c>
+      <c r="DB55" s="29">
+        <v>7811.2380724622381</v>
+      </c>
     </row>
-    <row r="56" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>45</v>
       </c>
@@ -11806,8 +11934,11 @@
       <c r="DA56" s="16">
         <v>2593.0675620629127</v>
       </c>
+      <c r="DB56" s="29">
+        <v>3153.3054281355685</v>
+      </c>
     </row>
-    <row r="57" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>46</v>
       </c>
@@ -12123,8 +12254,11 @@
       <c r="DA57" s="16">
         <v>5203.6456562477179</v>
       </c>
+      <c r="DB57" s="29">
+        <v>3480.91643731574</v>
+      </c>
     </row>
-    <row r="58" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>47</v>
       </c>
@@ -12440,8 +12574,11 @@
       <c r="DA58" s="16">
         <v>3211.6977691410739</v>
       </c>
+      <c r="DB58" s="29">
+        <v>1055.5270307099286</v>
+      </c>
     </row>
-    <row r="59" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>48</v>
       </c>
@@ -12757,8 +12894,11 @@
       <c r="DA59" s="16">
         <v>600.12382808461632</v>
       </c>
+      <c r="DB59" s="29">
+        <v>853.38252652886604</v>
+      </c>
     </row>
-    <row r="60" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>49</v>
       </c>
@@ -13074,8 +13214,11 @@
       <c r="DA60" s="16">
         <v>452.15640619105466</v>
       </c>
+      <c r="DB60" s="29">
+        <v>400.35078514152951</v>
+      </c>
     </row>
-    <row r="61" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>50</v>
       </c>
@@ -13391,8 +13534,11 @@
       <c r="DA61" s="16">
         <v>1214.9591229912126</v>
       </c>
+      <c r="DB61" s="29">
+        <v>856.4332438234419</v>
+      </c>
     </row>
-    <row r="62" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>51</v>
       </c>
@@ -13708,8 +13854,11 @@
       <c r="DA62" s="16">
         <v>23946.930747284736</v>
       </c>
+      <c r="DB62" s="29">
+        <v>28186.923109356303</v>
+      </c>
     </row>
-    <row r="63" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>52</v>
       </c>
@@ -14025,8 +14174,11 @@
       <c r="DA63" s="16">
         <v>47539.458717893867</v>
       </c>
+      <c r="DB63" s="29">
+        <v>46577.615523783024</v>
+      </c>
     </row>
-    <row r="64" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>53</v>
       </c>
@@ -14342,8 +14494,11 @@
       <c r="DA64" s="16">
         <v>66995.26063838409</v>
       </c>
+      <c r="DB64" s="29">
+        <v>63264.11831125959</v>
+      </c>
     </row>
-    <row r="65" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>54</v>
       </c>
@@ -14659,8 +14814,11 @@
       <c r="DA65" s="16">
         <v>21668.381097283796</v>
       </c>
+      <c r="DB65" s="29">
+        <v>21213.123321251296</v>
+      </c>
     </row>
-    <row r="66" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>55</v>
       </c>
@@ -14976,8 +15134,11 @@
       <c r="DA66" s="16">
         <v>269.33946352914387</v>
       </c>
+      <c r="DB66" s="29">
+        <v>778.89280009014419</v>
+      </c>
     </row>
-    <row r="67" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>56</v>
       </c>
@@ -15293,8 +15454,11 @@
       <c r="DA67" s="16">
         <v>67981.303807689488</v>
       </c>
+      <c r="DB67" s="29">
+        <v>43938.349624153096</v>
+      </c>
     </row>
-    <row r="68" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>57</v>
       </c>
@@ -15610,9 +15774,12 @@
       <c r="DA68" s="16">
         <v>59551.930626659589</v>
       </c>
+      <c r="DB68" s="29">
+        <v>41690.009991389001</v>
+      </c>
     </row>
-    <row r="69" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" spans="1:105" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" spans="1:106" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
         <v>62</v>
       </c>
@@ -15928,8 +16095,11 @@
       <c r="DA70" s="18">
         <v>528808.93452259735</v>
       </c>
+      <c r="DB70" s="30">
+        <v>455741.24889463489</v>
+      </c>
     </row>
-    <row r="71" spans="1:105" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:106" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="10"/>
       <c r="B71" s="10"/>
       <c r="C71" s="10"/>
@@ -16035,8 +16205,9 @@
       <c r="CY71" s="19"/>
       <c r="CZ71" s="19"/>
       <c r="DA71" s="19"/>
+      <c r="DB71" s="19"/>
     </row>
-    <row r="72" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>6</v>
       </c>
@@ -16052,10 +16223,11 @@
       <c r="CY72" s="13"/>
       <c r="CZ72" s="13"/>
       <c r="DA72" s="13"/>
+      <c r="DB72" s="13"/>
     </row>
-    <row r="73" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>0</v>
       </c>
@@ -16071,8 +16243,9 @@
       <c r="CY75" s="20"/>
       <c r="CZ75" s="20"/>
       <c r="DA75" s="20"/>
+      <c r="DB75" s="20"/>
     </row>
-    <row r="76" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>8</v>
       </c>
@@ -16088,8 +16261,9 @@
       <c r="CY76" s="20"/>
       <c r="CZ76" s="20"/>
       <c r="DA76" s="20"/>
+      <c r="DB76" s="20"/>
     </row>
-    <row r="77" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>70</v>
       </c>
@@ -16105,8 +16279,9 @@
       <c r="CY77" s="20"/>
       <c r="CZ77" s="20"/>
       <c r="DA77" s="20"/>
+      <c r="DB77" s="20"/>
     </row>
-    <row r="78" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP78" s="13"/>
       <c r="CQ78" s="13"/>
       <c r="CR78" s="13"/>
@@ -16119,8 +16294,9 @@
       <c r="CY78" s="20"/>
       <c r="CZ78" s="20"/>
       <c r="DA78" s="20"/>
+      <c r="DB78" s="20"/>
     </row>
-    <row r="79" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>64</v>
       </c>
@@ -16136,8 +16312,9 @@
       <c r="CY79" s="20"/>
       <c r="CZ79" s="20"/>
       <c r="DA79" s="20"/>
+      <c r="DB79" s="20"/>
     </row>
-    <row r="80" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>69</v>
       </c>
@@ -16153,8 +16330,9 @@
       <c r="CY80" s="20"/>
       <c r="CZ80" s="20"/>
       <c r="DA80" s="20"/>
+      <c r="DB80" s="20"/>
     </row>
-    <row r="81" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>9</v>
       </c>
@@ -16170,8 +16348,9 @@
       <c r="CY81" s="20"/>
       <c r="CZ81" s="20"/>
       <c r="DA81" s="20"/>
+      <c r="DB81" s="20"/>
     </row>
-    <row r="82" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP82" s="13"/>
       <c r="CQ82" s="13"/>
       <c r="CR82" s="13"/>
@@ -16184,8 +16363,9 @@
       <c r="CY82" s="20"/>
       <c r="CZ82" s="20"/>
       <c r="DA82" s="20"/>
+      <c r="DB82" s="20"/>
     </row>
-    <row r="83" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6"/>
       <c r="B83" s="6" t="s">
         <v>10</v>
@@ -16337,12 +16517,15 @@
       <c r="CU83" s="14"/>
       <c r="CV83" s="14"/>
       <c r="CW83" s="14"/>
-      <c r="CX83" s="21"/>
+      <c r="CX83" s="14" t="s">
+        <v>71</v>
+      </c>
       <c r="CY83" s="21"/>
       <c r="CZ83" s="21"/>
       <c r="DA83" s="21"/>
+      <c r="DB83" s="21"/>
     </row>
-    <row r="84" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
         <v>37</v>
       </c>
@@ -16646,12 +16829,15 @@
       <c r="CW84" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="CX84" s="22"/>
+      <c r="CX84" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="CY84" s="22"/>
       <c r="CZ84" s="22"/>
       <c r="DA84" s="22"/>
+      <c r="DB84" s="22"/>
     </row>
-    <row r="85" spans="1:105" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:106" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="4"/>
       <c r="CP85" s="13"/>
       <c r="CQ85" s="13"/>
@@ -16661,12 +16847,13 @@
       <c r="CU85" s="13"/>
       <c r="CV85" s="13"/>
       <c r="CW85" s="13"/>
-      <c r="CX85" s="20"/>
+      <c r="CX85" s="13"/>
       <c r="CY85" s="20"/>
       <c r="CZ85" s="20"/>
       <c r="DA85" s="20"/>
+      <c r="DB85" s="20"/>
     </row>
-    <row r="86" spans="1:105" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:106" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>38</v>
       </c>
@@ -16970,12 +17157,15 @@
       <c r="CW86" s="23">
         <v>-22.091145629658655</v>
       </c>
-      <c r="CX86" s="24"/>
+      <c r="CX86" s="23">
+        <v>4.2810184765305905</v>
+      </c>
       <c r="CY86" s="24"/>
       <c r="CZ86" s="24"/>
       <c r="DA86" s="24"/>
+      <c r="DB86" s="24"/>
     </row>
-    <row r="87" spans="1:105" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:106" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>39</v>
       </c>
@@ -17279,12 +17469,15 @@
       <c r="CW87" s="23">
         <v>28.795353487038682</v>
       </c>
-      <c r="CX87" s="24"/>
+      <c r="CX87" s="23">
+        <v>21.356740619762562</v>
+      </c>
       <c r="CY87" s="24"/>
       <c r="CZ87" s="24"/>
       <c r="DA87" s="24"/>
+      <c r="DB87" s="24"/>
     </row>
-    <row r="88" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>40</v>
       </c>
@@ -17588,12 +17781,15 @@
       <c r="CW88" s="23">
         <v>-2.7033396374175283</v>
       </c>
-      <c r="CX88" s="24"/>
+      <c r="CX88" s="23">
+        <v>0.91168581482546074</v>
+      </c>
       <c r="CY88" s="24"/>
       <c r="CZ88" s="24"/>
       <c r="DA88" s="24"/>
+      <c r="DB88" s="24"/>
     </row>
-    <row r="89" spans="1:105" s="9" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:106" s="9" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
         <v>41</v>
       </c>
@@ -17897,12 +18093,15 @@
       <c r="CW89" s="23">
         <v>-36.024765146894886</v>
       </c>
-      <c r="CX89" s="24"/>
+      <c r="CX89" s="23">
+        <v>-26.251320604002132</v>
+      </c>
       <c r="CY89" s="24"/>
       <c r="CZ89" s="24"/>
       <c r="DA89" s="24"/>
+      <c r="DB89" s="24"/>
     </row>
-    <row r="90" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>42</v>
       </c>
@@ -18206,12 +18405,15 @@
       <c r="CW90" s="23">
         <v>-13.623449063297926</v>
       </c>
-      <c r="CX90" s="24"/>
+      <c r="CX90" s="23">
+        <v>-11.110480115943972</v>
+      </c>
       <c r="CY90" s="24"/>
       <c r="CZ90" s="24"/>
       <c r="DA90" s="24"/>
+      <c r="DB90" s="24"/>
     </row>
-    <row r="91" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>43</v>
       </c>
@@ -18515,12 +18717,15 @@
       <c r="CW91" s="23">
         <v>-12.33018922016241</v>
       </c>
-      <c r="CX91" s="24"/>
+      <c r="CX91" s="23">
+        <v>-7.2506579510080229</v>
+      </c>
       <c r="CY91" s="24"/>
       <c r="CZ91" s="24"/>
       <c r="DA91" s="24"/>
+      <c r="DB91" s="24"/>
     </row>
-    <row r="92" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>44</v>
       </c>
@@ -18824,12 +19029,15 @@
       <c r="CW92" s="23">
         <v>-15.030648724471007</v>
       </c>
-      <c r="CX92" s="24"/>
+      <c r="CX92" s="23">
+        <v>-36.330246503202325</v>
+      </c>
       <c r="CY92" s="24"/>
       <c r="CZ92" s="24"/>
       <c r="DA92" s="24"/>
+      <c r="DB92" s="24"/>
     </row>
-    <row r="93" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>45</v>
       </c>
@@ -19133,12 +19341,15 @@
       <c r="CW93" s="23">
         <v>46.916510818471949</v>
       </c>
-      <c r="CX93" s="24"/>
+      <c r="CX93" s="23">
+        <v>-16.865752201970963</v>
+      </c>
       <c r="CY93" s="24"/>
       <c r="CZ93" s="24"/>
       <c r="DA93" s="24"/>
+      <c r="DB93" s="24"/>
     </row>
-    <row r="94" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>46</v>
       </c>
@@ -19442,12 +19653,15 @@
       <c r="CW94" s="23">
         <v>-19.585638019418383</v>
       </c>
-      <c r="CX94" s="24"/>
+      <c r="CX94" s="23">
+        <v>7.1084233669934918</v>
+      </c>
       <c r="CY94" s="24"/>
       <c r="CZ94" s="24"/>
       <c r="DA94" s="24"/>
+      <c r="DB94" s="24"/>
     </row>
-    <row r="95" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>47</v>
       </c>
@@ -19751,12 +19965,15 @@
       <c r="CW95" s="23">
         <v>-1.8745472423500047</v>
       </c>
-      <c r="CX95" s="24"/>
+      <c r="CX95" s="23">
+        <v>6.0957694736805763</v>
+      </c>
       <c r="CY95" s="24"/>
       <c r="CZ95" s="24"/>
       <c r="DA95" s="24"/>
+      <c r="DB95" s="24"/>
     </row>
-    <row r="96" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>48</v>
       </c>
@@ -20060,12 +20277,15 @@
       <c r="CW96" s="23">
         <v>13.520994875484192</v>
       </c>
-      <c r="CX96" s="24"/>
+      <c r="CX96" s="23">
+        <v>-32.049359052804789</v>
+      </c>
       <c r="CY96" s="24"/>
       <c r="CZ96" s="24"/>
       <c r="DA96" s="24"/>
+      <c r="DB96" s="24"/>
     </row>
-    <row r="97" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>49</v>
       </c>
@@ -20369,12 +20589,15 @@
       <c r="CW97" s="23">
         <v>3.7846540215191311</v>
       </c>
-      <c r="CX97" s="24"/>
+      <c r="CX97" s="23">
+        <v>-17.669929167328519</v>
+      </c>
       <c r="CY97" s="24"/>
       <c r="CZ97" s="24"/>
       <c r="DA97" s="24"/>
+      <c r="DB97" s="24"/>
     </row>
-    <row r="98" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>50</v>
       </c>
@@ -20678,12 +20901,15 @@
       <c r="CW98" s="23">
         <v>-40.583953815609696</v>
       </c>
-      <c r="CX98" s="24"/>
+      <c r="CX98" s="23">
+        <v>12.099274739620043</v>
+      </c>
       <c r="CY98" s="24"/>
       <c r="CZ98" s="24"/>
       <c r="DA98" s="24"/>
+      <c r="DB98" s="24"/>
     </row>
-    <row r="99" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
         <v>51</v>
       </c>
@@ -20987,12 +21213,15 @@
       <c r="CW99" s="23">
         <v>8.5555826442929686</v>
       </c>
-      <c r="CX99" s="24"/>
+      <c r="CX99" s="23">
+        <v>3.7277077479384246</v>
+      </c>
       <c r="CY99" s="24"/>
       <c r="CZ99" s="24"/>
       <c r="DA99" s="24"/>
+      <c r="DB99" s="24"/>
     </row>
-    <row r="100" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
         <v>52</v>
       </c>
@@ -21296,12 +21525,15 @@
       <c r="CW100" s="23">
         <v>5.2919904278688961</v>
       </c>
-      <c r="CX100" s="24"/>
+      <c r="CX100" s="23">
+        <v>-8.7726016705020839</v>
+      </c>
       <c r="CY100" s="24"/>
       <c r="CZ100" s="24"/>
       <c r="DA100" s="24"/>
+      <c r="DB100" s="24"/>
     </row>
-    <row r="101" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>53</v>
       </c>
@@ -21605,12 +21837,15 @@
       <c r="CW101" s="23">
         <v>13.912235470780487</v>
       </c>
-      <c r="CX101" s="24"/>
+      <c r="CX101" s="23">
+        <v>2.6326613808338948</v>
+      </c>
       <c r="CY101" s="24"/>
       <c r="CZ101" s="24"/>
       <c r="DA101" s="24"/>
+      <c r="DB101" s="24"/>
     </row>
-    <row r="102" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
         <v>54</v>
       </c>
@@ -21914,12 +22149,15 @@
       <c r="CW102" s="23">
         <v>9.355320556157622</v>
       </c>
-      <c r="CX102" s="24"/>
+      <c r="CX102" s="23">
+        <v>-3.0091451327172649</v>
+      </c>
       <c r="CY102" s="24"/>
       <c r="CZ102" s="24"/>
       <c r="DA102" s="24"/>
+      <c r="DB102" s="24"/>
     </row>
-    <row r="103" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>55</v>
       </c>
@@ -22223,12 +22461,15 @@
       <c r="CW103" s="23">
         <v>14.421440066642006</v>
       </c>
-      <c r="CX103" s="24"/>
+      <c r="CX103" s="23">
+        <v>-0.6455240490270171</v>
+      </c>
       <c r="CY103" s="24"/>
       <c r="CZ103" s="24"/>
       <c r="DA103" s="24"/>
+      <c r="DB103" s="24"/>
     </row>
-    <row r="104" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>56</v>
       </c>
@@ -22532,12 +22773,15 @@
       <c r="CW104" s="23">
         <v>10.647350377498086</v>
       </c>
-      <c r="CX104" s="24"/>
+      <c r="CX104" s="23">
+        <v>-0.4420461052861242</v>
+      </c>
       <c r="CY104" s="24"/>
       <c r="CZ104" s="24"/>
       <c r="DA104" s="24"/>
+      <c r="DB104" s="24"/>
     </row>
-    <row r="105" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>57</v>
       </c>
@@ -22841,18 +23085,21 @@
       <c r="CW105" s="23">
         <v>5.442739157632559E-2</v>
       </c>
-      <c r="CX105" s="24"/>
+      <c r="CX105" s="23">
+        <v>-1.1157915071133431</v>
+      </c>
       <c r="CY105" s="24"/>
       <c r="CZ105" s="24"/>
       <c r="DA105" s="24"/>
+      <c r="DB105" s="24"/>
     </row>
-    <row r="106" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="CX106" s="25"/>
+    <row r="106" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="CY106" s="25"/>
       <c r="CZ106" s="25"/>
       <c r="DA106" s="25"/>
+      <c r="DB106" s="25"/>
     </row>
-    <row r="107" spans="1:105" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:106" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
         <v>62</v>
       </c>
@@ -23156,12 +23403,15 @@
       <c r="CW107" s="23">
         <v>-2.0499984234648139</v>
       </c>
-      <c r="CX107" s="24"/>
+      <c r="CX107" s="23">
+        <v>-1.3730581800920305</v>
+      </c>
       <c r="CY107" s="24"/>
       <c r="CZ107" s="24"/>
       <c r="DA107" s="24"/>
+      <c r="DB107" s="24"/>
     </row>
-    <row r="108" spans="1:105" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:106" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="10"/>
       <c r="B108" s="10"/>
       <c r="C108" s="10"/>
@@ -23263,12 +23513,13 @@
       <c r="CU108" s="19"/>
       <c r="CV108" s="19"/>
       <c r="CW108" s="19"/>
-      <c r="CX108" s="22"/>
+      <c r="CX108" s="19"/>
       <c r="CY108" s="22"/>
       <c r="CZ108" s="22"/>
       <c r="DA108" s="22"/>
+      <c r="DB108" s="22"/>
     </row>
-    <row r="109" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>6</v>
       </c>
@@ -23280,24 +23531,25 @@
       <c r="CU109" s="13"/>
       <c r="CV109" s="13"/>
       <c r="CW109" s="13"/>
-      <c r="CX109" s="20"/>
+      <c r="CX109" s="13"/>
       <c r="CY109" s="20"/>
       <c r="CZ109" s="20"/>
       <c r="DA109" s="20"/>
+      <c r="DB109" s="20"/>
     </row>
-    <row r="110" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="CX110" s="25"/>
+    <row r="110" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="CY110" s="25"/>
       <c r="CZ110" s="25"/>
       <c r="DA110" s="25"/>
+      <c r="DB110" s="25"/>
     </row>
-    <row r="111" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="CX111" s="25"/>
+    <row r="111" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="CY111" s="25"/>
       <c r="CZ111" s="25"/>
       <c r="DA111" s="25"/>
+      <c r="DB111" s="25"/>
     </row>
-    <row r="112" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
         <v>0</v>
       </c>
@@ -23309,12 +23561,13 @@
       <c r="CU112" s="13"/>
       <c r="CV112" s="13"/>
       <c r="CW112" s="13"/>
-      <c r="CX112" s="20"/>
+      <c r="CX112" s="13"/>
       <c r="CY112" s="20"/>
       <c r="CZ112" s="20"/>
       <c r="DA112" s="20"/>
+      <c r="DB112" s="20"/>
     </row>
-    <row r="113" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>8</v>
       </c>
@@ -23326,12 +23579,13 @@
       <c r="CU113" s="13"/>
       <c r="CV113" s="13"/>
       <c r="CW113" s="13"/>
-      <c r="CX113" s="20"/>
+      <c r="CX113" s="13"/>
       <c r="CY113" s="20"/>
       <c r="CZ113" s="20"/>
       <c r="DA113" s="20"/>
+      <c r="DB113" s="20"/>
     </row>
-    <row r="114" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>70</v>
       </c>
@@ -23343,12 +23597,13 @@
       <c r="CU114" s="13"/>
       <c r="CV114" s="13"/>
       <c r="CW114" s="13"/>
-      <c r="CX114" s="20"/>
+      <c r="CX114" s="13"/>
       <c r="CY114" s="20"/>
       <c r="CZ114" s="20"/>
       <c r="DA114" s="20"/>
+      <c r="DB114" s="20"/>
     </row>
-    <row r="115" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP115" s="13"/>
       <c r="CQ115" s="13"/>
       <c r="CR115" s="13"/>
@@ -23357,12 +23612,13 @@
       <c r="CU115" s="13"/>
       <c r="CV115" s="13"/>
       <c r="CW115" s="13"/>
-      <c r="CX115" s="20"/>
+      <c r="CX115" s="13"/>
       <c r="CY115" s="20"/>
       <c r="CZ115" s="20"/>
       <c r="DA115" s="20"/>
+      <c r="DB115" s="20"/>
     </row>
-    <row r="116" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>65</v>
       </c>
@@ -23374,12 +23630,13 @@
       <c r="CU116" s="13"/>
       <c r="CV116" s="13"/>
       <c r="CW116" s="13"/>
-      <c r="CX116" s="20"/>
+      <c r="CX116" s="13"/>
       <c r="CY116" s="20"/>
       <c r="CZ116" s="20"/>
       <c r="DA116" s="20"/>
+      <c r="DB116" s="20"/>
     </row>
-    <row r="117" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
         <v>69</v>
       </c>
@@ -23391,12 +23648,13 @@
       <c r="CU117" s="13"/>
       <c r="CV117" s="13"/>
       <c r="CW117" s="13"/>
-      <c r="CX117" s="20"/>
+      <c r="CX117" s="13"/>
       <c r="CY117" s="20"/>
       <c r="CZ117" s="20"/>
       <c r="DA117" s="20"/>
+      <c r="DB117" s="20"/>
     </row>
-    <row r="118" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
         <v>35</v>
       </c>
@@ -23408,12 +23666,13 @@
       <c r="CU118" s="13"/>
       <c r="CV118" s="13"/>
       <c r="CW118" s="13"/>
-      <c r="CX118" s="20"/>
+      <c r="CX118" s="13"/>
       <c r="CY118" s="20"/>
       <c r="CZ118" s="20"/>
       <c r="DA118" s="20"/>
+      <c r="DB118" s="20"/>
     </row>
-    <row r="119" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP119" s="13"/>
       <c r="CQ119" s="13"/>
       <c r="CR119" s="13"/>
@@ -23422,12 +23681,13 @@
       <c r="CU119" s="13"/>
       <c r="CV119" s="13"/>
       <c r="CW119" s="13"/>
-      <c r="CX119" s="20"/>
+      <c r="CX119" s="13"/>
       <c r="CY119" s="20"/>
       <c r="CZ119" s="20"/>
       <c r="DA119" s="20"/>
+      <c r="DB119" s="20"/>
     </row>
-    <row r="120" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A120" s="6"/>
       <c r="B120" s="6" t="s">
         <v>10</v>
@@ -23579,12 +23839,15 @@
       <c r="CU120" s="14"/>
       <c r="CV120" s="14"/>
       <c r="CW120" s="14"/>
-      <c r="CX120" s="21"/>
+      <c r="CX120" s="14" t="s">
+        <v>71</v>
+      </c>
       <c r="CY120" s="21"/>
       <c r="CZ120" s="21"/>
       <c r="DA120" s="21"/>
+      <c r="DB120" s="21"/>
     </row>
-    <row r="121" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
         <v>37</v>
       </c>
@@ -23888,12 +24151,15 @@
       <c r="CW121" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="CX121" s="22"/>
+      <c r="CX121" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="CY121" s="22"/>
       <c r="CZ121" s="22"/>
       <c r="DA121" s="22"/>
+      <c r="DB121" s="22"/>
     </row>
-    <row r="122" spans="1:105" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:106" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="4"/>
       <c r="CP122" s="13"/>
       <c r="CQ122" s="13"/>
@@ -23903,12 +24169,13 @@
       <c r="CU122" s="13"/>
       <c r="CV122" s="13"/>
       <c r="CW122" s="13"/>
-      <c r="CX122" s="20"/>
+      <c r="CX122" s="13"/>
       <c r="CY122" s="20"/>
       <c r="CZ122" s="20"/>
       <c r="DA122" s="20"/>
+      <c r="DB122" s="20"/>
     </row>
-    <row r="123" spans="1:105" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:106" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>38</v>
       </c>
@@ -24212,12 +24479,15 @@
       <c r="CW123" s="23">
         <v>-5.2413242937608402</v>
       </c>
-      <c r="CX123" s="24"/>
+      <c r="CX123" s="23">
+        <v>-6.2600231023244532</v>
+      </c>
       <c r="CY123" s="24"/>
       <c r="CZ123" s="24"/>
       <c r="DA123" s="24"/>
+      <c r="DB123" s="24"/>
     </row>
-    <row r="124" spans="1:105" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:106" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
         <v>39</v>
       </c>
@@ -24521,12 +24791,15 @@
       <c r="CW124" s="23">
         <v>2.695636478873368</v>
       </c>
-      <c r="CX124" s="24"/>
+      <c r="CX124" s="23">
+        <v>-5.5018838603154734</v>
+      </c>
       <c r="CY124" s="24"/>
       <c r="CZ124" s="24"/>
       <c r="DA124" s="24"/>
+      <c r="DB124" s="24"/>
     </row>
-    <row r="125" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>40</v>
       </c>
@@ -24830,12 +25103,15 @@
       <c r="CW125" s="23">
         <v>0.11405571996236574</v>
       </c>
-      <c r="CX125" s="24"/>
+      <c r="CX125" s="23">
+        <v>1.4136403716252062</v>
+      </c>
       <c r="CY125" s="24"/>
       <c r="CZ125" s="24"/>
       <c r="DA125" s="24"/>
+      <c r="DB125" s="24"/>
     </row>
-    <row r="126" spans="1:105" s="9" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:106" s="9" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="s">
         <v>41</v>
       </c>
@@ -25139,12 +25415,15 @@
       <c r="CW126" s="23">
         <v>0.18924866684686492</v>
       </c>
-      <c r="CX126" s="24"/>
+      <c r="CX126" s="23">
+        <v>-7.9745677627628027</v>
+      </c>
       <c r="CY126" s="24"/>
       <c r="CZ126" s="24"/>
       <c r="DA126" s="24"/>
+      <c r="DB126" s="24"/>
     </row>
-    <row r="127" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
         <v>42</v>
       </c>
@@ -25448,12 +25727,15 @@
       <c r="CW127" s="23">
         <v>-5.4755297275249859E-2</v>
       </c>
-      <c r="CX127" s="24"/>
+      <c r="CX127" s="23">
+        <v>-2.6569603555002459</v>
+      </c>
       <c r="CY127" s="24"/>
       <c r="CZ127" s="24"/>
       <c r="DA127" s="24"/>
+      <c r="DB127" s="24"/>
     </row>
-    <row r="128" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
         <v>43</v>
       </c>
@@ -25757,12 +26039,15 @@
       <c r="CW128" s="23">
         <v>2.0976342184996213</v>
       </c>
-      <c r="CX128" s="24"/>
+      <c r="CX128" s="23">
+        <v>-0.37392626016890063</v>
+      </c>
       <c r="CY128" s="24"/>
       <c r="CZ128" s="24"/>
       <c r="DA128" s="24"/>
+      <c r="DB128" s="24"/>
     </row>
-    <row r="129" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
         <v>44</v>
       </c>
@@ -26066,12 +26351,15 @@
       <c r="CW129" s="23">
         <v>-2.8996150371513068</v>
       </c>
-      <c r="CX129" s="24"/>
+      <c r="CX129" s="23">
+        <v>6.3113749865831181</v>
+      </c>
       <c r="CY129" s="24"/>
       <c r="CZ129" s="24"/>
       <c r="DA129" s="24"/>
+      <c r="DB129" s="24"/>
     </row>
-    <row r="130" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
         <v>45</v>
       </c>
@@ -26375,12 +26663,15 @@
       <c r="CW130" s="23">
         <v>8.887083275596865</v>
       </c>
-      <c r="CX130" s="24"/>
+      <c r="CX130" s="23">
+        <v>-0.25979614820100494</v>
+      </c>
       <c r="CY130" s="24"/>
       <c r="CZ130" s="24"/>
       <c r="DA130" s="24"/>
+      <c r="DB130" s="24"/>
     </row>
-    <row r="131" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
         <v>46</v>
       </c>
@@ -26684,12 +26975,15 @@
       <c r="CW131" s="23">
         <v>-2.7472561771661503</v>
       </c>
-      <c r="CX131" s="24"/>
+      <c r="CX131" s="23">
+        <v>1.8370319462990778</v>
+      </c>
       <c r="CY131" s="24"/>
       <c r="CZ131" s="24"/>
       <c r="DA131" s="24"/>
+      <c r="DB131" s="24"/>
     </row>
-    <row r="132" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
         <v>47</v>
       </c>
@@ -26993,12 +27287,15 @@
       <c r="CW132" s="23">
         <v>5.3256950441978574</v>
       </c>
-      <c r="CX132" s="24"/>
+      <c r="CX132" s="23">
+        <v>6.8574124018544182</v>
+      </c>
       <c r="CY132" s="24"/>
       <c r="CZ132" s="24"/>
       <c r="DA132" s="24"/>
+      <c r="DB132" s="24"/>
     </row>
-    <row r="133" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
         <v>48</v>
       </c>
@@ -27302,12 +27599,15 @@
       <c r="CW133" s="23">
         <v>7.0711332491187164</v>
       </c>
-      <c r="CX133" s="24"/>
+      <c r="CX133" s="23">
+        <v>13.556692105806704</v>
+      </c>
       <c r="CY133" s="24"/>
       <c r="CZ133" s="24"/>
       <c r="DA133" s="24"/>
+      <c r="DB133" s="24"/>
     </row>
-    <row r="134" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
         <v>49</v>
       </c>
@@ -27611,12 +27911,15 @@
       <c r="CW134" s="23">
         <v>-10.618635911146129</v>
       </c>
-      <c r="CX134" s="24"/>
+      <c r="CX134" s="23">
+        <v>0.53291406982683043</v>
+      </c>
       <c r="CY134" s="24"/>
       <c r="CZ134" s="24"/>
       <c r="DA134" s="24"/>
+      <c r="DB134" s="24"/>
     </row>
-    <row r="135" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
         <v>50</v>
       </c>
@@ -27920,12 +28223,15 @@
       <c r="CW135" s="23">
         <v>2.1616658111923641</v>
       </c>
-      <c r="CX135" s="24"/>
+      <c r="CX135" s="23">
+        <v>41.57720257038946</v>
+      </c>
       <c r="CY135" s="24"/>
       <c r="CZ135" s="24"/>
       <c r="DA135" s="24"/>
+      <c r="DB135" s="24"/>
     </row>
-    <row r="136" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
         <v>51</v>
       </c>
@@ -28229,12 +28535,15 @@
       <c r="CW136" s="23">
         <v>-0.74922325829393799</v>
       </c>
-      <c r="CX136" s="24"/>
+      <c r="CX136" s="23">
+        <v>7.7966007191015763</v>
+      </c>
       <c r="CY136" s="24"/>
       <c r="CZ136" s="24"/>
       <c r="DA136" s="24"/>
+      <c r="DB136" s="24"/>
     </row>
-    <row r="137" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
         <v>52</v>
       </c>
@@ -28538,12 +28847,15 @@
       <c r="CW137" s="23">
         <v>1.5808547207083308</v>
       </c>
-      <c r="CX137" s="24"/>
+      <c r="CX137" s="23">
+        <v>5.0309169267710701</v>
+      </c>
       <c r="CY137" s="24"/>
       <c r="CZ137" s="24"/>
       <c r="DA137" s="24"/>
+      <c r="DB137" s="24"/>
     </row>
-    <row r="138" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
         <v>53</v>
       </c>
@@ -28847,12 +29159,15 @@
       <c r="CW138" s="23">
         <v>8.8696996093931659</v>
       </c>
-      <c r="CX138" s="24"/>
+      <c r="CX138" s="23">
+        <v>7.0421579189176668</v>
+      </c>
       <c r="CY138" s="24"/>
       <c r="CZ138" s="24"/>
       <c r="DA138" s="24"/>
+      <c r="DB138" s="24"/>
     </row>
-    <row r="139" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
         <v>54</v>
       </c>
@@ -29156,12 +29471,15 @@
       <c r="CW139" s="23">
         <v>5.1092278833939417</v>
       </c>
-      <c r="CX139" s="24"/>
+      <c r="CX139" s="23">
+        <v>6.1843622652765049</v>
+      </c>
       <c r="CY139" s="24"/>
       <c r="CZ139" s="24"/>
       <c r="DA139" s="24"/>
+      <c r="DB139" s="24"/>
     </row>
-    <row r="140" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
         <v>55</v>
       </c>
@@ -29465,12 +29783,15 @@
       <c r="CW140" s="23">
         <v>15.014442596536298</v>
       </c>
-      <c r="CX140" s="24"/>
+      <c r="CX140" s="23">
+        <v>-1.7681875968015248</v>
+      </c>
       <c r="CY140" s="24"/>
       <c r="CZ140" s="24"/>
       <c r="DA140" s="24"/>
+      <c r="DB140" s="24"/>
     </row>
-    <row r="141" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
         <v>56</v>
       </c>
@@ -29774,12 +30095,15 @@
       <c r="CW141" s="23">
         <v>4.7059274152744734</v>
       </c>
-      <c r="CX141" s="24"/>
+      <c r="CX141" s="23">
+        <v>-5.0052215522969874</v>
+      </c>
       <c r="CY141" s="24"/>
       <c r="CZ141" s="24"/>
       <c r="DA141" s="24"/>
+      <c r="DB141" s="24"/>
     </row>
-    <row r="142" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
         <v>57</v>
       </c>
@@ -30083,18 +30407,21 @@
       <c r="CW142" s="23">
         <v>2.4585512142321022</v>
       </c>
-      <c r="CX142" s="24"/>
+      <c r="CX142" s="23">
+        <v>0.10378601681553334</v>
+      </c>
       <c r="CY142" s="24"/>
       <c r="CZ142" s="24"/>
       <c r="DA142" s="24"/>
+      <c r="DB142" s="24"/>
     </row>
-    <row r="143" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="CX143" s="25"/>
+    <row r="143" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="CY143" s="25"/>
       <c r="CZ143" s="25"/>
       <c r="DA143" s="25"/>
+      <c r="DB143" s="25"/>
     </row>
-    <row r="144" spans="1:105" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:106" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="5" t="s">
         <v>62</v>
       </c>
@@ -30398,12 +30725,15 @@
       <c r="CW144" s="23">
         <v>1.0256262320668554</v>
       </c>
-      <c r="CX144" s="24"/>
+      <c r="CX144" s="23">
+        <v>-0.20950936020631161</v>
+      </c>
       <c r="CY144" s="24"/>
       <c r="CZ144" s="24"/>
       <c r="DA144" s="24"/>
+      <c r="DB144" s="24"/>
     </row>
-    <row r="145" spans="1:105" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:106" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="10"/>
       <c r="B145" s="10"/>
       <c r="C145" s="10"/>
@@ -30505,12 +30835,13 @@
       <c r="CU145" s="19"/>
       <c r="CV145" s="19"/>
       <c r="CW145" s="19"/>
-      <c r="CX145" s="22"/>
+      <c r="CX145" s="19"/>
       <c r="CY145" s="22"/>
       <c r="CZ145" s="22"/>
       <c r="DA145" s="22"/>
+      <c r="DB145" s="22"/>
     </row>
-    <row r="146" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
         <v>6</v>
       </c>
@@ -30522,24 +30853,26 @@
       <c r="CU146" s="13"/>
       <c r="CV146" s="13"/>
       <c r="CW146" s="13"/>
-      <c r="CX146" s="20"/>
+      <c r="CX146" s="13"/>
       <c r="CY146" s="20"/>
       <c r="CZ146" s="20"/>
       <c r="DA146" s="20"/>
+      <c r="DB146" s="20"/>
     </row>
-    <row r="147" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="CX147" s="25"/>
+    <row r="147" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="CY147" s="25"/>
       <c r="CZ147" s="25"/>
       <c r="DA147" s="25"/>
+      <c r="DB147" s="25"/>
     </row>
-    <row r="148" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="CX148" s="25"/>
       <c r="CY148" s="25"/>
       <c r="CZ148" s="25"/>
       <c r="DA148" s="25"/>
+      <c r="DB148" s="25"/>
     </row>
-    <row r="149" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
         <v>0</v>
       </c>
@@ -30555,8 +30888,9 @@
       <c r="CY149" s="13"/>
       <c r="CZ149" s="13"/>
       <c r="DA149" s="13"/>
+      <c r="DB149" s="13"/>
     </row>
-    <row r="150" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
         <v>70</v>
       </c>
@@ -30572,8 +30906,9 @@
       <c r="CY150" s="13"/>
       <c r="CZ150" s="13"/>
       <c r="DA150" s="13"/>
+      <c r="DB150" s="13"/>
     </row>
-    <row r="151" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP151" s="13"/>
       <c r="CQ151" s="13"/>
       <c r="CR151" s="13"/>
@@ -30586,8 +30921,9 @@
       <c r="CY151" s="13"/>
       <c r="CZ151" s="13"/>
       <c r="DA151" s="13"/>
+      <c r="DB151" s="13"/>
     </row>
-    <row r="152" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
         <v>66</v>
       </c>
@@ -30603,8 +30939,9 @@
       <c r="CY152" s="13"/>
       <c r="CZ152" s="13"/>
       <c r="DA152" s="13"/>
+      <c r="DB152" s="13"/>
     </row>
-    <row r="153" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
         <v>69</v>
       </c>
@@ -30620,8 +30957,9 @@
       <c r="CY153" s="13"/>
       <c r="CZ153" s="13"/>
       <c r="DA153" s="13"/>
+      <c r="DB153" s="13"/>
     </row>
-    <row r="154" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
         <v>36</v>
       </c>
@@ -30637,8 +30975,9 @@
       <c r="CY154" s="13"/>
       <c r="CZ154" s="13"/>
       <c r="DA154" s="13"/>
+      <c r="DB154" s="13"/>
     </row>
-    <row r="155" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP155" s="13"/>
       <c r="CQ155" s="13"/>
       <c r="CR155" s="13"/>
@@ -30651,8 +30990,9 @@
       <c r="CY155" s="13"/>
       <c r="CZ155" s="13"/>
       <c r="DA155" s="13"/>
+      <c r="DB155" s="13"/>
     </row>
-    <row r="156" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A156" s="6"/>
       <c r="B156" s="6">
         <v>2000</v>
@@ -30810,8 +31150,11 @@
       <c r="CY156" s="14"/>
       <c r="CZ156" s="14"/>
       <c r="DA156" s="14"/>
+      <c r="DB156" s="14">
+        <v>2026</v>
+      </c>
     </row>
-    <row r="157" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A157" s="3" t="s">
         <v>37</v>
       </c>
@@ -31127,8 +31470,11 @@
       <c r="DA157" s="15" t="s">
         <v>5</v>
       </c>
+      <c r="DB157" s="15" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="158" spans="1:105" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:106" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="4"/>
       <c r="CP158" s="13"/>
       <c r="CQ158" s="13"/>
@@ -31142,8 +31488,9 @@
       <c r="CY158" s="13"/>
       <c r="CZ158" s="13"/>
       <c r="DA158" s="13"/>
+      <c r="DB158" s="13"/>
     </row>
-    <row r="159" spans="1:105" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:106" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
         <v>38</v>
       </c>
@@ -31459,8 +31806,11 @@
       <c r="DA159" s="23">
         <v>96.902644283648726</v>
       </c>
+      <c r="DB159" s="23">
+        <v>123.85615839394606</v>
+      </c>
     </row>
-    <row r="160" spans="1:105" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:106" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
         <v>39</v>
       </c>
@@ -31776,8 +32126,11 @@
       <c r="DA160" s="23">
         <v>125.73020868340932</v>
       </c>
+      <c r="DB160" s="23">
+        <v>132.13496926840679</v>
+      </c>
     </row>
-    <row r="161" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
         <v>40</v>
       </c>
@@ -32093,8 +32446,11 @@
       <c r="DA161" s="23">
         <v>123.0613450712319</v>
       </c>
+      <c r="DB161" s="23">
+        <v>114.83868294546578</v>
+      </c>
     </row>
-    <row r="162" spans="1:105" s="9" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:106" s="9" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="5" t="s">
         <v>41</v>
       </c>
@@ -32410,8 +32766,11 @@
       <c r="DA162" s="23">
         <v>146.50325890277122</v>
       </c>
+      <c r="DB162" s="23">
+        <v>90.618221388651577</v>
+      </c>
     </row>
-    <row r="163" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
         <v>42</v>
       </c>
@@ -32727,8 +33086,11 @@
       <c r="DA163" s="23">
         <v>101.53550263341693</v>
       </c>
+      <c r="DB163" s="23">
+        <v>110.89852463793663</v>
+      </c>
     </row>
-    <row r="164" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
         <v>43</v>
       </c>
@@ -33044,8 +33406,11 @@
       <c r="DA164" s="23">
         <v>117.5199353531869</v>
       </c>
+      <c r="DB164" s="23">
+        <v>117.51053899552961</v>
+      </c>
     </row>
-    <row r="165" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
         <v>44</v>
       </c>
@@ -33361,8 +33726,11 @@
       <c r="DA165" s="23">
         <v>158.17950629238996</v>
       </c>
+      <c r="DB165" s="23">
+        <v>110.05707301916676</v>
+      </c>
     </row>
-    <row r="166" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
         <v>45</v>
       </c>
@@ -33678,8 +34046,11 @@
       <c r="DA166" s="23">
         <v>365.48935714009139</v>
       </c>
+      <c r="DB166" s="23">
+        <v>221.08316209747349</v>
+      </c>
     </row>
-    <row r="167" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
         <v>46</v>
       </c>
@@ -33995,8 +34366,11 @@
       <c r="DA167" s="23">
         <v>195.66627824347322</v>
       </c>
+      <c r="DB167" s="23">
+        <v>140.79051465197543</v>
+      </c>
     </row>
-    <row r="168" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
         <v>47</v>
       </c>
@@ -34312,8 +34686,11 @@
       <c r="DA168" s="23">
         <v>159.73765760699243</v>
       </c>
+      <c r="DB168" s="23">
+        <v>219.27662614106481</v>
+      </c>
     </row>
-    <row r="169" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
         <v>48</v>
       </c>
@@ -34629,8 +35006,11 @@
       <c r="DA169" s="23">
         <v>263.83965720327484</v>
       </c>
+      <c r="DB169" s="23">
+        <v>114.46391823982071</v>
+      </c>
     </row>
-    <row r="170" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
         <v>49</v>
       </c>
@@ -34946,8 +35326,11 @@
       <c r="DA170" s="23">
         <v>121.51106198125048</v>
       </c>
+      <c r="DB170" s="23">
+        <v>69.368443397197169</v>
+      </c>
     </row>
-    <row r="171" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
         <v>50</v>
       </c>
@@ -35263,8 +35646,11 @@
       <c r="DA171" s="23">
         <v>58.563084232841646</v>
       </c>
+      <c r="DB171" s="23">
+        <v>79.687568724889687</v>
+      </c>
     </row>
-    <row r="172" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
         <v>51</v>
       </c>
@@ -35580,8 +35966,11 @@
       <c r="DA172" s="23">
         <v>170.92778463981352</v>
       </c>
+      <c r="DB172" s="23">
+        <v>122.79461140535805</v>
+      </c>
     </row>
-    <row r="173" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
         <v>52</v>
       </c>
@@ -35897,8 +36286,11 @@
       <c r="DA173" s="23">
         <v>195.09997129288402</v>
       </c>
+      <c r="DB173" s="23">
+        <v>157.21745542800838</v>
+      </c>
     </row>
-    <row r="174" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
         <v>53</v>
       </c>
@@ -36214,8 +36606,11 @@
       <c r="DA174" s="23">
         <v>130.52214955338533</v>
       </c>
+      <c r="DB174" s="23">
+        <v>164.09650400591244</v>
+      </c>
     </row>
-    <row r="175" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
         <v>54</v>
       </c>
@@ -36531,8 +36926,11 @@
       <c r="DA175" s="23">
         <v>130.87891870873676</v>
       </c>
+      <c r="DB175" s="23">
+        <v>119.71315149819681</v>
+      </c>
     </row>
-    <row r="176" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
         <v>55</v>
       </c>
@@ -36848,8 +37246,11 @@
       <c r="DA176" s="23">
         <v>43.221377809182215</v>
       </c>
+      <c r="DB176" s="23">
+        <v>38.239124275738995</v>
+      </c>
     </row>
-    <row r="177" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
         <v>56</v>
       </c>
@@ -37165,8 +37566,11 @@
       <c r="DA177" s="23">
         <v>112.08461279281046</v>
       </c>
+      <c r="DB177" s="23">
+        <v>156.90848592537191</v>
+      </c>
     </row>
-    <row r="178" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
         <v>57</v>
       </c>
@@ -37482,9 +37886,12 @@
       <c r="DA178" s="23">
         <v>153.4378698385232</v>
       </c>
+      <c r="DB178" s="23">
+        <v>138.43660614628374</v>
+      </c>
     </row>
-    <row r="179" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" spans="1:105" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" spans="1:106" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="5" t="s">
         <v>62</v>
       </c>
@@ -37800,8 +38207,11 @@
       <c r="DA180" s="23">
         <v>130.42743775193267</v>
       </c>
+      <c r="DB180" s="23">
+        <v>135.69209464828543</v>
+      </c>
     </row>
-    <row r="181" spans="1:105" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:106" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="10"/>
       <c r="B181" s="10"/>
       <c r="C181" s="10"/>
@@ -37907,8 +38317,9 @@
       <c r="CY181" s="19"/>
       <c r="CZ181" s="19"/>
       <c r="DA181" s="19"/>
+      <c r="DB181" s="19"/>
     </row>
-    <row r="182" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
         <v>6</v>
       </c>
@@ -37924,8 +38335,9 @@
       <c r="CY182" s="13"/>
       <c r="CZ182" s="13"/>
       <c r="DA182" s="13"/>
+      <c r="DB182" s="13"/>
     </row>
-    <row r="185" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
         <v>0</v>
       </c>
@@ -37941,8 +38353,9 @@
       <c r="CY185" s="13"/>
       <c r="CZ185" s="13"/>
       <c r="DA185" s="13"/>
+      <c r="DB185" s="13"/>
     </row>
-    <row r="186" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
         <v>8</v>
       </c>
@@ -37958,8 +38371,9 @@
       <c r="CY186" s="13"/>
       <c r="CZ186" s="13"/>
       <c r="DA186" s="13"/>
+      <c r="DB186" s="13"/>
     </row>
-    <row r="187" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
         <v>70</v>
       </c>
@@ -37975,8 +38389,9 @@
       <c r="CY187" s="13"/>
       <c r="CZ187" s="13"/>
       <c r="DA187" s="13"/>
+      <c r="DB187" s="13"/>
     </row>
-    <row r="188" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP188" s="13"/>
       <c r="CQ188" s="13"/>
       <c r="CR188" s="13"/>
@@ -37989,8 +38404,9 @@
       <c r="CY188" s="13"/>
       <c r="CZ188" s="13"/>
       <c r="DA188" s="13"/>
+      <c r="DB188" s="13"/>
     </row>
-    <row r="189" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
         <v>67</v>
       </c>
@@ -38006,8 +38422,9 @@
       <c r="CY189" s="13"/>
       <c r="CZ189" s="13"/>
       <c r="DA189" s="13"/>
+      <c r="DB189" s="13"/>
     </row>
-    <row r="190" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
         <v>69</v>
       </c>
@@ -38023,8 +38440,9 @@
       <c r="CY190" s="13"/>
       <c r="CZ190" s="13"/>
       <c r="DA190" s="13"/>
+      <c r="DB190" s="13"/>
     </row>
-    <row r="191" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
         <v>59</v>
       </c>
@@ -38040,8 +38458,9 @@
       <c r="CY191" s="13"/>
       <c r="CZ191" s="13"/>
       <c r="DA191" s="13"/>
+      <c r="DB191" s="13"/>
     </row>
-    <row r="192" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP192" s="13"/>
       <c r="CQ192" s="13"/>
       <c r="CR192" s="13"/>
@@ -38054,8 +38473,9 @@
       <c r="CY192" s="13"/>
       <c r="CZ192" s="13"/>
       <c r="DA192" s="13"/>
+      <c r="DB192" s="13"/>
     </row>
-    <row r="193" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A193" s="6"/>
       <c r="B193" s="6">
         <v>2000</v>
@@ -38213,8 +38633,11 @@
       <c r="CY193" s="14"/>
       <c r="CZ193" s="14"/>
       <c r="DA193" s="14"/>
+      <c r="DB193" s="14">
+        <v>2026</v>
+      </c>
     </row>
-    <row r="194" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A194" s="3" t="s">
         <v>37</v>
       </c>
@@ -38530,8 +38953,11 @@
       <c r="DA194" s="15" t="s">
         <v>5</v>
       </c>
+      <c r="DB194" s="15" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="195" spans="1:105" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:106" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="4"/>
       <c r="CP195" s="13"/>
       <c r="CQ195" s="13"/>
@@ -38545,8 +38971,9 @@
       <c r="CY195" s="13"/>
       <c r="CZ195" s="13"/>
       <c r="DA195" s="13"/>
+      <c r="DB195" s="13"/>
     </row>
-    <row r="196" spans="1:105" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:106" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
         <v>38</v>
       </c>
@@ -38862,8 +39289,11 @@
       <c r="DA196" s="23">
         <v>17.793145846832957</v>
       </c>
+      <c r="DB196" s="23">
+        <v>17.58678233944643</v>
+      </c>
     </row>
-    <row r="197" spans="1:105" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:106" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
         <v>39</v>
       </c>
@@ -39179,8 +39609,11 @@
       <c r="DA197" s="23">
         <v>4.4255479594724934</v>
       </c>
+      <c r="DB197" s="23">
+        <v>6.3808933398207852</v>
+      </c>
     </row>
-    <row r="198" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
         <v>40</v>
       </c>
@@ -39496,8 +39929,11 @@
       <c r="DA198" s="23">
         <v>3.8192372495396518</v>
       </c>
+      <c r="DB198" s="23">
+        <v>4.8774052136960435</v>
+      </c>
     </row>
-    <row r="199" spans="1:105" s="9" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:106" s="9" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="5" t="s">
         <v>41</v>
       </c>
@@ -39813,8 +40249,11 @@
       <c r="DA199" s="23">
         <v>1.383897113254789</v>
       </c>
+      <c r="DB199" s="23">
+        <v>2.0972303090273812</v>
+      </c>
     </row>
-    <row r="200" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
         <v>42</v>
       </c>
@@ -40130,8 +40569,11 @@
       <c r="DA200" s="23">
         <v>4.7389735971064075</v>
       </c>
+      <c r="DB200" s="23">
+        <v>5.1379024389970409</v>
+      </c>
     </row>
-    <row r="201" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
         <v>43</v>
       </c>
@@ -40447,8 +40889,11 @@
       <c r="DA201" s="23">
         <v>1.2936771828241524</v>
       </c>
+      <c r="DB201" s="23">
+        <v>1.0604924883286726</v>
+      </c>
     </row>
-    <row r="202" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
         <v>44</v>
       </c>
@@ -40764,8 +41209,11 @@
       <c r="DA202" s="23">
         <v>2.0539031266357486</v>
       </c>
+      <c r="DB202" s="23">
+        <v>1.3901605127412224</v>
+      </c>
     </row>
-    <row r="203" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
         <v>45</v>
       </c>
@@ -41081,8 +41529,11 @@
       <c r="DA203" s="23">
         <v>1.3741078498925792</v>
       </c>
+      <c r="DB203" s="23">
+        <v>1.1273241772234059</v>
+      </c>
     </row>
-    <row r="204" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
         <v>46</v>
       </c>
@@ -41398,8 +41849,11 @@
       <c r="DA204" s="23">
         <v>1.4762365475314698</v>
       </c>
+      <c r="DB204" s="23">
+        <v>0.79249058154229424</v>
+      </c>
     </row>
-    <row r="205" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
         <v>47</v>
       </c>
@@ -41715,8 +42169,11 @@
       <c r="DA205" s="23">
         <v>0.74383093278394641</v>
       </c>
+      <c r="DB205" s="23">
+        <v>0.37427327307010111</v>
+      </c>
     </row>
-    <row r="206" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
         <v>48</v>
       </c>
@@ -42032,8 +42489,11 @@
       <c r="DA206" s="23">
         <v>0.2295689765582227</v>
       </c>
+      <c r="DB206" s="23">
+        <v>0.15795721564786547</v>
+      </c>
     </row>
-    <row r="207" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
         <v>49</v>
       </c>
@@ -42349,8 +42809,11 @@
       <c r="DA207" s="23">
         <v>7.9659349941281432E-2</v>
       </c>
+      <c r="DB207" s="23">
+        <v>4.4908624053900906E-2</v>
+      </c>
     </row>
-    <row r="208" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
         <v>50</v>
       </c>
@@ -42666,8 +43129,11 @@
       <c r="DA208" s="23">
         <v>0.10316155039558732</v>
       </c>
+      <c r="DB208" s="23">
+        <v>0.11035987723650514</v>
+      </c>
     </row>
-    <row r="209" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
         <v>51</v>
       </c>
@@ -42983,8 +43449,11 @@
       <c r="DA209" s="23">
         <v>5.9346454092191818</v>
       </c>
+      <c r="DB209" s="23">
+        <v>5.5969843830117219</v>
+      </c>
     </row>
-    <row r="210" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
         <v>52</v>
       </c>
@@ -43300,8 +43769,11 @@
       <c r="DA210" s="23">
         <v>13.447566209568276</v>
       </c>
+      <c r="DB210" s="23">
+        <v>11.84145666132715</v>
+      </c>
     </row>
-    <row r="211" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
         <v>53</v>
       </c>
@@ -43617,8 +44089,11 @@
       <c r="DA211" s="23">
         <v>12.678286211707013</v>
       </c>
+      <c r="DB211" s="23">
+        <v>16.787417979646499</v>
+      </c>
     </row>
-    <row r="212" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
         <v>54</v>
       </c>
@@ -43934,8 +44409,11 @@
       <c r="DA212" s="23">
         <v>4.1117662427894812</v>
       </c>
+      <c r="DB212" s="23">
+        <v>4.1065167245083058</v>
+      </c>
     </row>
-    <row r="213" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
         <v>55</v>
       </c>
@@ -44251,8 +44729,11 @@
       <c r="DA213" s="23">
         <v>1.6878383526709711E-2</v>
       </c>
+      <c r="DB213" s="23">
+        <v>4.8162912587409228E-2</v>
+      </c>
     </row>
-    <row r="214" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
         <v>56</v>
       </c>
@@ -44568,8 +45049,11 @@
       <c r="DA214" s="23">
         <v>11.0475948427648</v>
       </c>
+      <c r="DB214" s="23">
+        <v>11.1485217964337</v>
+      </c>
     </row>
-    <row r="215" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="s">
         <v>57</v>
       </c>
@@ -44885,9 +45369,12 @@
       <c r="DA215" s="23">
         <v>13.248315417655231</v>
       </c>
+      <c r="DB215" s="23">
+        <v>9.3327591516535602</v>
+      </c>
     </row>
-    <row r="216" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" spans="1:105" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" spans="1:106" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="5" t="s">
         <v>62</v>
       </c>
@@ -45203,8 +45690,11 @@
       <c r="DA217" s="23">
         <v>100</v>
       </c>
+      <c r="DB217" s="23">
+        <v>100</v>
+      </c>
     </row>
-    <row r="218" spans="1:105" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:106" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="10"/>
       <c r="B218" s="10"/>
       <c r="C218" s="10"/>
@@ -45310,8 +45800,9 @@
       <c r="CY218" s="19"/>
       <c r="CZ218" s="19"/>
       <c r="DA218" s="19"/>
+      <c r="DB218" s="19"/>
     </row>
-    <row r="219" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
         <v>6</v>
       </c>
@@ -45327,10 +45818,11 @@
       <c r="CY219" s="13"/>
       <c r="CZ219" s="13"/>
       <c r="DA219" s="13"/>
+      <c r="DB219" s="13"/>
     </row>
-    <row r="220" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
         <v>0</v>
       </c>
@@ -45346,8 +45838,9 @@
       <c r="CY222" s="13"/>
       <c r="CZ222" s="13"/>
       <c r="DA222" s="13"/>
+      <c r="DB222" s="13"/>
     </row>
-    <row r="223" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
         <v>8</v>
       </c>
@@ -45363,8 +45856,9 @@
       <c r="CY223" s="13"/>
       <c r="CZ223" s="13"/>
       <c r="DA223" s="13"/>
+      <c r="DB223" s="13"/>
     </row>
-    <row r="224" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
         <v>70</v>
       </c>
@@ -45380,8 +45874,9 @@
       <c r="CY224" s="13"/>
       <c r="CZ224" s="13"/>
       <c r="DA224" s="13"/>
+      <c r="DB224" s="13"/>
     </row>
-    <row r="225" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP225" s="13"/>
       <c r="CQ225" s="13"/>
       <c r="CR225" s="13"/>
@@ -45394,8 +45889,9 @@
       <c r="CY225" s="13"/>
       <c r="CZ225" s="13"/>
       <c r="DA225" s="13"/>
+      <c r="DB225" s="13"/>
     </row>
-    <row r="226" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A226" s="1" t="s">
         <v>68</v>
       </c>
@@ -45411,8 +45907,9 @@
       <c r="CY226" s="13"/>
       <c r="CZ226" s="13"/>
       <c r="DA226" s="13"/>
+      <c r="DB226" s="13"/>
     </row>
-    <row r="227" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
         <v>69</v>
       </c>
@@ -45428,8 +45925,9 @@
       <c r="CY227" s="13"/>
       <c r="CZ227" s="13"/>
       <c r="DA227" s="13"/>
+      <c r="DB227" s="13"/>
     </row>
-    <row r="228" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A228" s="1" t="s">
         <v>60</v>
       </c>
@@ -45445,8 +45943,9 @@
       <c r="CY228" s="13"/>
       <c r="CZ228" s="13"/>
       <c r="DA228" s="13"/>
+      <c r="DB228" s="13"/>
     </row>
-    <row r="229" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP229" s="13"/>
       <c r="CQ229" s="13"/>
       <c r="CR229" s="13"/>
@@ -45459,8 +45958,9 @@
       <c r="CY229" s="13"/>
       <c r="CZ229" s="13"/>
       <c r="DA229" s="13"/>
+      <c r="DB229" s="13"/>
     </row>
-    <row r="230" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A230" s="6"/>
       <c r="B230" s="6">
         <v>2000</v>
@@ -45618,8 +46118,11 @@
       <c r="CY230" s="14"/>
       <c r="CZ230" s="14"/>
       <c r="DA230" s="14"/>
+      <c r="DB230" s="14">
+        <v>2026</v>
+      </c>
     </row>
-    <row r="231" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A231" s="3" t="s">
         <v>37</v>
       </c>
@@ -45935,8 +46438,11 @@
       <c r="DA231" s="15" t="s">
         <v>5</v>
       </c>
+      <c r="DB231" s="15" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="232" spans="1:105" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:106" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="4"/>
       <c r="CP232" s="13"/>
       <c r="CQ232" s="13"/>
@@ -45950,8 +46456,9 @@
       <c r="CY232" s="13"/>
       <c r="CZ232" s="13"/>
       <c r="DA232" s="13"/>
+      <c r="DB232" s="13"/>
     </row>
-    <row r="233" spans="1:105" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:106" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="s">
         <v>38</v>
       </c>
@@ -46267,8 +46774,11 @@
       <c r="DA233" s="23">
         <v>23.948927704756766</v>
       </c>
+      <c r="DB233" s="23">
+        <v>19.267409587924082</v>
+      </c>
     </row>
-    <row r="234" spans="1:105" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:106" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="1" t="s">
         <v>39</v>
       </c>
@@ -46584,8 +47094,11 @@
       <c r="DA234" s="23">
         <v>4.5908846175203815</v>
       </c>
+      <c r="DB234" s="23">
+        <v>6.5526694999928097</v>
+      </c>
     </row>
-    <row r="235" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
         <v>40</v>
       </c>
@@ -46901,8 +47414,11 @@
       <c r="DA235" s="23">
         <v>4.0478456361407371</v>
       </c>
+      <c r="DB235" s="23">
+        <v>5.7630870793700231</v>
+      </c>
     </row>
-    <row r="236" spans="1:105" s="9" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:106" s="9" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="5" t="s">
         <v>41</v>
       </c>
@@ -47218,8 +47734,11 @@
       <c r="DA236" s="23">
         <v>1.2320419077770022</v>
       </c>
+      <c r="DB236" s="23">
+        <v>3.1404012264958774</v>
+      </c>
     </row>
-    <row r="237" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="1" t="s">
         <v>42</v>
       </c>
@@ -47535,8 +48054,11 @@
       <c r="DA237" s="23">
         <v>6.0874489002748531</v>
       </c>
+      <c r="DB237" s="23">
+        <v>6.2865826783736241</v>
+      </c>
     </row>
-    <row r="238" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
         <v>43</v>
       </c>
@@ -47852,8 +48374,11 @@
       <c r="DA238" s="23">
         <v>1.4357649170483238</v>
       </c>
+      <c r="DB238" s="23">
+        <v>1.2245748196726791</v>
+      </c>
     </row>
-    <row r="239" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="1" t="s">
         <v>44</v>
       </c>
@@ -48169,8 +48694,11 @@
       <c r="DA239" s="23">
         <v>1.69355265088896</v>
       </c>
+      <c r="DB239" s="23">
+        <v>1.713963370971531</v>
+      </c>
     </row>
-    <row r="240" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="1" t="s">
         <v>45</v>
       </c>
@@ -48486,8 +49014,11 @@
       <c r="DA240" s="23">
         <v>0.49036001337683605</v>
       </c>
+      <c r="DB240" s="23">
+        <v>0.6919069616330904</v>
+      </c>
     </row>
-    <row r="241" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="1" t="s">
         <v>46</v>
       </c>
@@ -48803,8 +49334,11 @@
       <c r="DA241" s="23">
         <v>0.98403134223621036</v>
       </c>
+      <c r="DB241" s="23">
+        <v>0.76379227154847917</v>
+      </c>
     </row>
-    <row r="242" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="1" t="s">
         <v>47</v>
       </c>
@@ -49120,8 +49654,11 @@
       <c r="DA242" s="23">
         <v>0.60734559487739326</v>
       </c>
+      <c r="DB242" s="23">
+        <v>0.2316066481298385</v>
+      </c>
     </row>
-    <row r="243" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="s">
         <v>48</v>
       </c>
@@ -49437,8 +49974,11 @@
       <c r="DA243" s="23">
         <v>0.11348594717417194</v>
       </c>
+      <c r="DB243" s="23">
+        <v>0.1872515442915644</v>
+      </c>
     </row>
-    <row r="244" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
         <v>49</v>
       </c>
@@ -49754,8 +50294,11 @@
       <c r="DA244" s="23">
         <v>8.5504683577113966E-2</v>
       </c>
+      <c r="DB244" s="23">
+        <v>8.7846071891133248E-2</v>
+      </c>
     </row>
-    <row r="245" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="1" t="s">
         <v>50</v>
       </c>
@@ -50071,8 +50614,11 @@
       <c r="DA245" s="23">
         <v>0.22975389477639285</v>
       </c>
+      <c r="DB245" s="23">
+        <v>0.18792094108239149</v>
+      </c>
     </row>
-    <row r="246" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="1" t="s">
         <v>51</v>
       </c>
@@ -50388,8 +50934,11 @@
       <c r="DA246" s="23">
         <v>4.5284656109117654</v>
       </c>
+      <c r="DB246" s="23">
+        <v>6.1848522989133636</v>
+      </c>
     </row>
-    <row r="247" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="1" t="s">
         <v>52</v>
       </c>
@@ -50705,8 +51254,11 @@
       <c r="DA247" s="23">
         <v>8.9899121619062541</v>
       </c>
+      <c r="DB247" s="23">
+        <v>10.220188678719213</v>
+      </c>
     </row>
-    <row r="248" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="s">
         <v>53</v>
       </c>
@@ -51022,8 +51574,11 @@
       <c r="DA248" s="23">
         <v>12.669086368381171</v>
       </c>
+      <c r="DB248" s="23">
+        <v>13.881587077031499</v>
+      </c>
     </row>
-    <row r="249" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="1" t="s">
         <v>54</v>
       </c>
@@ -51339,8 +51894,11 @@
       <c r="DA249" s="23">
         <v>4.0975822613219952</v>
       </c>
+      <c r="DB249" s="23">
+        <v>4.65464194270369</v>
+      </c>
     </row>
-    <row r="250" spans="1:105" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="1" t="s">
         <v>55</v>
       </c>
@@ -51656,8 +52214,11 @@
       <c r="DA250" s="23">
         <v>5.09332286097436E-2</v>
       </c>
+      <c r="DB250" s="23">
+        <v>0.17090680336249753</v>
+      </c>
     </row>
-    <row r="251" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="1" t="s">
         <v>56</v>
       </c>
@@ -51973,8 +52534,11 @@
       <c r="DA251" s="23">
         <v>12.855551290762934</v>
       </c>
+      <c r="DB251" s="23">
+        <v>9.6410736861590127</v>
+      </c>
     </row>
-    <row r="252" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="1" t="s">
         <v>57</v>
       </c>
@@ -52290,9 +52854,12 @@
       <c r="DA252" s="23">
         <v>11.261521267680999</v>
       </c>
+      <c r="DB252" s="23">
+        <v>9.1477368117336066</v>
+      </c>
     </row>
-    <row r="253" spans="1:105" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" spans="1:105" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" spans="1:106" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="5" t="s">
         <v>62</v>
       </c>
@@ -52608,8 +53175,11 @@
       <c r="DA254" s="23">
         <v>100</v>
       </c>
+      <c r="DB254" s="23">
+        <v>100</v>
+      </c>
     </row>
-    <row r="255" spans="1:105" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:106" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="10"/>
       <c r="B255" s="10"/>
       <c r="C255" s="10"/>
@@ -52715,8 +53285,9 @@
       <c r="CY255" s="19"/>
       <c r="CZ255" s="19"/>
       <c r="DA255" s="19"/>
+      <c r="DB255" s="19"/>
     </row>
-    <row r="256" spans="1:105" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A256" s="1" t="s">
         <v>6</v>
       </c>
@@ -52732,8 +53303,9 @@
       <c r="CY256" s="13"/>
       <c r="CZ256" s="13"/>
       <c r="DA256" s="13"/>
+      <c r="DB256" s="13"/>
     </row>
-    <row r="257" spans="1:105" s="12" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:106" s="12" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="1"/>
       <c r="CP257" s="26"/>
       <c r="CQ257" s="26"/>
@@ -52747,8 +53319,9 @@
       <c r="CY257" s="27"/>
       <c r="CZ257" s="27"/>
       <c r="DA257" s="27"/>
+      <c r="DB257" s="27"/>
     </row>
-    <row r="258" spans="1:105" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:106" x14ac:dyDescent="0.2">
       <c r="CT258" s="28"/>
       <c r="CU258" s="28"/>
       <c r="CV258" s="28"/>
@@ -52757,8 +53330,9 @@
       <c r="CY258" s="28"/>
       <c r="CZ258" s="28"/>
       <c r="DA258" s="28"/>
+      <c r="DB258" s="28"/>
     </row>
-    <row r="259" spans="1:105" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:106" x14ac:dyDescent="0.2">
       <c r="CT259" s="28"/>
       <c r="CU259" s="28"/>
       <c r="CV259" s="28"/>
@@ -52767,8 +53341,9 @@
       <c r="CY259" s="28"/>
       <c r="CZ259" s="28"/>
       <c r="DA259" s="28"/>
+      <c r="DB259" s="28"/>
     </row>
-    <row r="260" spans="1:105" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:106" x14ac:dyDescent="0.2">
       <c r="CT260" s="28"/>
       <c r="CU260" s="28"/>
       <c r="CV260" s="28"/>
@@ -52778,7 +53353,7 @@
       <c r="CZ260" s="28"/>
       <c r="DA260" s="28"/>
     </row>
-    <row r="261" spans="1:105" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:106" x14ac:dyDescent="0.2">
       <c r="CS261" s="28"/>
       <c r="CT261" s="28"/>
       <c r="CU261" s="28"/>
@@ -52789,7 +53364,7 @@
       <c r="CZ261" s="28"/>
       <c r="DA261" s="28"/>
     </row>
-    <row r="262" spans="1:105" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:106" x14ac:dyDescent="0.2">
       <c r="CS262" s="28"/>
       <c r="CT262" s="28"/>
       <c r="CU262" s="28"/>

--- a/Data/National Accounts/PSA-08AFF_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-08AFF_2018PSNA_Qrt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of August 2026\Tables\NAP Q1 2000 to Q2 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C8832C4-910F-42FE-BA24-FD9440A1D727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D7E46E-A2B9-45A1-BA0C-5D2BD6273F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
@@ -521,7 +521,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="72">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -732,13 +732,13 @@
     <t>Table 9.7 Gross Value Added in Agriculture, Forestry, and Fishing, by Industry</t>
   </si>
   <si>
-    <t>Q1 2000 to Q1 2026</t>
+    <t>2025 - 2026</t>
   </si>
   <si>
-    <t>As of May 2026</t>
+    <t>Q1 2000 to Q2 2026</t>
   </si>
   <si>
-    <t>2025 - 2026</t>
+    <t>As of August 2026</t>
   </si>
 </sst>
 </file>
@@ -1248,16 +1248,16 @@
   <sheetPr transitionEvaluation="1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:DB262"/>
+  <dimension ref="A1:DC262"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
     <col min="2" max="93" width="13" style="8" customWidth="1"/>
-    <col min="94" max="106" width="13" style="17" customWidth="1"/>
-    <col min="107" max="16384" width="10" style="8"/>
+    <col min="94" max="107" width="13" style="17" customWidth="1"/>
+    <col min="108" max="16384" width="10" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1274,8 +1274,9 @@
       <c r="CZ1" s="13"/>
       <c r="DA1" s="13"/>
       <c r="DB1" s="13"/>
+      <c r="DC1" s="13"/>
     </row>
-    <row r="2" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>58</v>
       </c>
@@ -1292,10 +1293,11 @@
       <c r="CZ2" s="13"/>
       <c r="DA2" s="13"/>
       <c r="DB2" s="13"/>
+      <c r="DC2" s="13"/>
     </row>
-    <row r="3" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="CP3" s="13"/>
       <c r="CQ3" s="13"/>
@@ -1310,8 +1312,9 @@
       <c r="CZ3" s="13"/>
       <c r="DA3" s="13"/>
       <c r="DB3" s="13"/>
+      <c r="DC3" s="13"/>
     </row>
-    <row r="4" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP4" s="13"/>
       <c r="CQ4" s="13"/>
       <c r="CR4" s="13"/>
@@ -1325,8 +1328,9 @@
       <c r="CZ4" s="13"/>
       <c r="DA4" s="13"/>
       <c r="DB4" s="13"/>
+      <c r="DC4" s="13"/>
     </row>
-    <row r="5" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>61</v>
       </c>
@@ -1343,10 +1347,11 @@
       <c r="CZ5" s="13"/>
       <c r="DA5" s="13"/>
       <c r="DB5" s="13"/>
+      <c r="DC5" s="13"/>
     </row>
-    <row r="6" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="CP6" s="13"/>
       <c r="CQ6" s="13"/>
@@ -1361,8 +1366,9 @@
       <c r="CZ6" s="13"/>
       <c r="DA6" s="13"/>
       <c r="DB6" s="13"/>
+      <c r="DC6" s="13"/>
     </row>
-    <row r="7" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
@@ -1379,8 +1385,9 @@
       <c r="CZ7" s="13"/>
       <c r="DA7" s="13"/>
       <c r="DB7" s="13"/>
+      <c r="DC7" s="13"/>
     </row>
-    <row r="8" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP8" s="13"/>
       <c r="CQ8" s="13"/>
       <c r="CR8" s="13"/>
@@ -1394,8 +1401,9 @@
       <c r="CZ8" s="13"/>
       <c r="DA8" s="13"/>
       <c r="DB8" s="13"/>
+      <c r="DC8" s="13"/>
     </row>
-    <row r="9" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6"/>
       <c r="B9" s="6">
         <v>2000</v>
@@ -1556,8 +1564,9 @@
       <c r="DB9" s="14">
         <v>2026</v>
       </c>
+      <c r="DC9" s="14"/>
     </row>
-    <row r="10" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
@@ -1876,8 +1885,11 @@
       <c r="DB10" s="15" t="s">
         <v>2</v>
       </c>
+      <c r="DC10" s="15" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:106" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:107" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
       <c r="CP11" s="13"/>
       <c r="CQ11" s="13"/>
@@ -1892,8 +1904,9 @@
       <c r="CZ11" s="13"/>
       <c r="DA11" s="13"/>
       <c r="DB11" s="13"/>
+      <c r="DC11" s="13"/>
     </row>
-    <row r="12" spans="1:106" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:107" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>38</v>
       </c>
@@ -2210,10 +2223,13 @@
         <v>122721.45210135281</v>
       </c>
       <c r="DB12" s="29">
-        <v>108757.51438354692</v>
+        <v>108454.78981078946</v>
+      </c>
+      <c r="DC12" s="16">
+        <v>104538.43712014347</v>
       </c>
     </row>
-    <row r="13" spans="1:106" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:107" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>39</v>
       </c>
@@ -2530,10 +2546,13 @@
         <v>30523.532859554041</v>
       </c>
       <c r="DB13" s="29">
-        <v>39459.75368267858</v>
+        <v>39374.544554523251</v>
+      </c>
+      <c r="DC13" s="16">
+        <v>26438.803269687734</v>
       </c>
     </row>
-    <row r="14" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>40</v>
       </c>
@@ -2850,10 +2869,13 @@
         <v>26341.735475995567</v>
       </c>
       <c r="DB14" s="29">
-        <v>30162.110239639835</v>
+        <v>30100.471404724252</v>
+      </c>
+      <c r="DC14" s="16">
+        <v>23549.648416049949</v>
       </c>
     </row>
-    <row r="15" spans="1:106" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:107" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>41</v>
       </c>
@@ -3170,10 +3192,13 @@
         <v>9544.9036814210776</v>
       </c>
       <c r="DB15" s="29">
-        <v>12969.373879613013</v>
+        <v>12799.060093389689</v>
+      </c>
+      <c r="DC15" s="16">
+        <v>7385.4551240893861</v>
       </c>
     </row>
-    <row r="16" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -3490,10 +3515,13 @@
         <v>32685.266917563386</v>
       </c>
       <c r="DB16" s="29">
-        <v>31773.037706684332</v>
+        <v>31443.238972629402</v>
+      </c>
+      <c r="DC16" s="16">
+        <v>27474.125246531701</v>
       </c>
     </row>
-    <row r="17" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>43</v>
       </c>
@@ -3810,10 +3838,13 @@
         <v>8922.6460454616954</v>
       </c>
       <c r="DB17" s="29">
-        <v>6558.1369477891358</v>
+        <v>6474.5628496333502</v>
+      </c>
+      <c r="DC17" s="16">
+        <v>22840.462255730963</v>
       </c>
     </row>
-    <row r="18" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>44</v>
       </c>
@@ -4130,10 +4161,13 @@
         <v>14166.015180565282</v>
       </c>
       <c r="DB18" s="29">
-        <v>8596.8199891107197</v>
+        <v>8307.5929860086471</v>
+      </c>
+      <c r="DC18" s="16">
+        <v>5436.4798918829683</v>
       </c>
     </row>
-    <row r="19" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>45</v>
       </c>
@@ -4450,10 +4484,13 @@
         <v>9477.3859627919792</v>
       </c>
       <c r="DB19" s="29">
-        <v>6971.4273511133897</v>
+        <v>7104.5650824906788</v>
+      </c>
+      <c r="DC19" s="16">
+        <v>1850.3033062203372</v>
       </c>
     </row>
-    <row r="20" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>46</v>
       </c>
@@ -4770,10 +4807,13 @@
         <v>10181.779788558068</v>
       </c>
       <c r="DB20" s="29">
-        <v>4900.800166702038</v>
+        <v>5008.8251621362915</v>
+      </c>
+      <c r="DC20" s="16">
+        <v>9756.0339558040432</v>
       </c>
     </row>
-    <row r="21" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>47</v>
       </c>
@@ -5090,10 +5130,13 @@
         <v>5130.2907858419831</v>
       </c>
       <c r="DB21" s="29">
-        <v>2314.5240609476923</v>
+        <v>2266.6712581923325</v>
+      </c>
+      <c r="DC21" s="16">
+        <v>3958.837101793486</v>
       </c>
     </row>
-    <row r="22" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>48</v>
       </c>
@@ -5410,10 +5453,13 @@
         <v>1583.3646508136221</v>
       </c>
       <c r="DB22" s="29">
-        <v>976.81507743891757</v>
+        <v>959.97009838552344</v>
+      </c>
+      <c r="DC22" s="16">
+        <v>549.08362452024573</v>
       </c>
     </row>
-    <row r="23" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>49</v>
       </c>
@@ -5730,10 +5776,13 @@
         <v>549.4200509790071</v>
       </c>
       <c r="DB23" s="29">
-        <v>277.71710778113635</v>
+        <v>289.25136708324351</v>
+      </c>
+      <c r="DC23" s="16">
+        <v>175.6158681533131</v>
       </c>
     </row>
-    <row r="24" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>50</v>
       </c>
@@ -6050,10 +6099,13 @@
         <v>711.51753459193787</v>
       </c>
       <c r="DB24" s="29">
-        <v>682.47082975460739</v>
+        <v>681.71846422143881</v>
+      </c>
+      <c r="DC24" s="16">
+        <v>188.76397523017829</v>
       </c>
     </row>
-    <row r="25" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>51</v>
       </c>
@@ -6370,10 +6422,13 @@
         <v>40931.95821556414</v>
       </c>
       <c r="DB25" s="29">
-        <v>34612.022699261142</v>
+        <v>34112.05572161969</v>
+      </c>
+      <c r="DC25" s="16">
+        <v>20599.140684471731</v>
       </c>
     </row>
-    <row r="26" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>52</v>
       </c>
@@ -6690,10 +6745,13 @@
         <v>92749.470311403391</v>
       </c>
       <c r="DB26" s="29">
-        <v>73228.141925532691</v>
+        <v>73930.425153196586</v>
+      </c>
+      <c r="DC26" s="16">
+        <v>77565.009442004986</v>
       </c>
     </row>
-    <row r="27" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>53</v>
       </c>
@@ -7010,10 +7068,13 @@
         <v>87443.654284111981</v>
       </c>
       <c r="DB27" s="29">
-        <v>103814.20643894127</v>
+        <v>103827.79259738175</v>
+      </c>
+      <c r="DC27" s="16">
+        <v>59761.802905750883</v>
       </c>
     </row>
-    <row r="28" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>54</v>
       </c>
@@ -7332,8 +7393,11 @@
       <c r="DB28" s="29">
         <v>25394.898459068885</v>
       </c>
+      <c r="DC28" s="16">
+        <v>16274.318596373341</v>
+      </c>
     </row>
-    <row r="29" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>55</v>
       </c>
@@ -7650,10 +7714,13 @@
         <v>116.41222712115581</v>
       </c>
       <c r="DB29" s="29">
-        <v>297.84178580125354</v>
+        <v>311.66146530709148</v>
+      </c>
+      <c r="DC29" s="16">
+        <v>221.83427765125259</v>
       </c>
     </row>
-    <row r="30" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>56</v>
       </c>
@@ -7970,10 +8037,13 @@
         <v>76196.58114435288</v>
       </c>
       <c r="DB30" s="29">
-        <v>68942.99913585496</v>
+        <v>67908.612994911629</v>
+      </c>
+      <c r="DC30" s="16">
+        <v>63041.709651319718</v>
       </c>
     </row>
-    <row r="31" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>57</v>
       </c>
@@ -8292,9 +8362,12 @@
       <c r="DB31" s="29">
         <v>57714.234934125532</v>
       </c>
+      <c r="DC31" s="16">
+        <v>102150.70283358448</v>
+      </c>
     </row>
-    <row r="32" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" spans="1:106" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" spans="1:107" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>62</v>
       </c>
@@ -8611,10 +8684,13 @@
         <v>689711.94390111906</v>
       </c>
       <c r="DB33" s="30">
-        <v>618404.8468013861</v>
+        <v>616464.94342981884</v>
+      </c>
+      <c r="DC33" s="18">
+        <v>573756.56754699419</v>
       </c>
     </row>
-    <row r="34" spans="1:106" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:107" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
@@ -8721,8 +8797,9 @@
       <c r="CZ34" s="19"/>
       <c r="DA34" s="19"/>
       <c r="DB34" s="19"/>
+      <c r="DC34" s="19"/>
     </row>
-    <row r="35" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>6</v>
       </c>
@@ -8739,10 +8816,11 @@
       <c r="CZ35" s="13"/>
       <c r="DA35" s="13"/>
       <c r="DB35" s="13"/>
+      <c r="DC35" s="13"/>
     </row>
-    <row r="36" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>0</v>
       </c>
@@ -8759,8 +8837,9 @@
       <c r="CZ38" s="13"/>
       <c r="DA38" s="13"/>
       <c r="DB38" s="13"/>
+      <c r="DC38" s="13"/>
     </row>
-    <row r="39" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>58</v>
       </c>
@@ -8777,10 +8856,11 @@
       <c r="CZ39" s="13"/>
       <c r="DA39" s="13"/>
       <c r="DB39" s="13"/>
+      <c r="DC39" s="13"/>
     </row>
-    <row r="40" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="CP40" s="13"/>
       <c r="CQ40" s="13"/>
@@ -8795,8 +8875,9 @@
       <c r="CZ40" s="13"/>
       <c r="DA40" s="13"/>
       <c r="DB40" s="13"/>
+      <c r="DC40" s="13"/>
     </row>
-    <row r="41" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP41" s="13"/>
       <c r="CQ41" s="13"/>
       <c r="CR41" s="13"/>
@@ -8810,8 +8891,9 @@
       <c r="CZ41" s="13"/>
       <c r="DA41" s="13"/>
       <c r="DB41" s="13"/>
+      <c r="DC41" s="13"/>
     </row>
-    <row r="42" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>63</v>
       </c>
@@ -8828,10 +8910,11 @@
       <c r="CZ42" s="13"/>
       <c r="DA42" s="13"/>
       <c r="DB42" s="13"/>
+      <c r="DC42" s="13"/>
     </row>
-    <row r="43" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="CP43" s="13"/>
       <c r="CQ43" s="13"/>
@@ -8846,8 +8929,9 @@
       <c r="CZ43" s="13"/>
       <c r="DA43" s="13"/>
       <c r="DB43" s="13"/>
+      <c r="DC43" s="13"/>
     </row>
-    <row r="44" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>7</v>
       </c>
@@ -8864,8 +8948,9 @@
       <c r="CZ44" s="13"/>
       <c r="DA44" s="13"/>
       <c r="DB44" s="13"/>
+      <c r="DC44" s="13"/>
     </row>
-    <row r="45" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP45" s="13"/>
       <c r="CQ45" s="13"/>
       <c r="CR45" s="13"/>
@@ -8879,8 +8964,9 @@
       <c r="CZ45" s="13"/>
       <c r="DA45" s="13"/>
       <c r="DB45" s="13"/>
+      <c r="DC45" s="13"/>
     </row>
-    <row r="46" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6"/>
       <c r="B46" s="6">
         <v>2000</v>
@@ -9041,8 +9127,9 @@
       <c r="DB46" s="14">
         <v>2026</v>
       </c>
+      <c r="DC46" s="14"/>
     </row>
-    <row r="47" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>37</v>
       </c>
@@ -9361,8 +9448,11 @@
       <c r="DB47" s="15" t="s">
         <v>2</v>
       </c>
+      <c r="DC47" s="15" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="48" spans="1:106" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:107" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4"/>
       <c r="CP48" s="13"/>
       <c r="CQ48" s="13"/>
@@ -9377,8 +9467,9 @@
       <c r="CZ48" s="13"/>
       <c r="DA48" s="13"/>
       <c r="DB48" s="13"/>
+      <c r="DC48" s="13"/>
     </row>
-    <row r="49" spans="1:106" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:107" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>38</v>
       </c>
@@ -9695,10 +9786,13 @@
         <v>126644.06942511139</v>
       </c>
       <c r="DB49" s="29">
-        <v>87809.533085649833</v>
+        <v>87624.371159599643</v>
+      </c>
+      <c r="DC49" s="16">
+        <v>91056.423568641883</v>
       </c>
     </row>
-    <row r="50" spans="1:106" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:107" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>39</v>
       </c>
@@ -10015,10 +10109,13 @@
         <v>24277.008031071346</v>
       </c>
       <c r="DB50" s="29">
-        <v>29863.217815205055</v>
+        <v>29863.100485421426</v>
+      </c>
+      <c r="DC50" s="16">
+        <v>20880.665003986967</v>
       </c>
     </row>
-    <row r="51" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>40</v>
       </c>
@@ -10335,10 +10432,13 @@
         <v>21405.369379595286</v>
       </c>
       <c r="DB51" s="29">
-        <v>26264.765030406281</v>
+        <v>26264.765030406274</v>
+      </c>
+      <c r="DC51" s="16">
+        <v>13873.897288128092</v>
       </c>
     </row>
-    <row r="52" spans="1:106" s="9" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:107" s="9" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
         <v>41</v>
       </c>
@@ -10655,10 +10755,13 @@
         <v>6515.1476853874465</v>
       </c>
       <c r="DB52" s="29">
-        <v>14312.103769934742</v>
+        <v>14312.103759830959</v>
+      </c>
+      <c r="DC52" s="16">
+        <v>10784.570276214721</v>
       </c>
     </row>
-    <row r="53" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>42</v>
       </c>
@@ -10975,10 +11078,13 @@
         <v>32190.973669151022</v>
       </c>
       <c r="DB53" s="29">
-        <v>28650.550411213746</v>
+        <v>28650.55041121375</v>
+      </c>
+      <c r="DC53" s="16">
+        <v>31303.759804887937</v>
       </c>
     </row>
-    <row r="54" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>43</v>
       </c>
@@ -11295,10 +11401,13 @@
         <v>7592.4531600924947</v>
       </c>
       <c r="DB54" s="29">
-        <v>5580.8925768254903</v>
+        <v>5580.8925768254885</v>
+      </c>
+      <c r="DC54" s="16">
+        <v>19289.034055675242</v>
       </c>
     </row>
-    <row r="55" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>44</v>
       </c>
@@ -11615,10 +11724,13 @@
         <v>8955.6577287451128</v>
       </c>
       <c r="DB55" s="29">
-        <v>7811.2380724622381</v>
+        <v>7811.2380724622353</v>
+      </c>
+      <c r="DC55" s="16">
+        <v>6784.323947413046</v>
       </c>
     </row>
-    <row r="56" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>45</v>
       </c>
@@ -11935,10 +12047,13 @@
         <v>2593.0675620629127</v>
       </c>
       <c r="DB56" s="29">
-        <v>3153.3054281355685</v>
+        <v>3240.0331309286107</v>
+      </c>
+      <c r="DC56" s="16">
+        <v>658.44491225726927</v>
       </c>
     </row>
-    <row r="57" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>46</v>
       </c>
@@ -12255,10 +12370,13 @@
         <v>5203.6456562477179</v>
       </c>
       <c r="DB57" s="29">
-        <v>3480.91643731574</v>
+        <v>3480.9164373157391</v>
+      </c>
+      <c r="DC57" s="16">
+        <v>5780.9228047860324</v>
       </c>
     </row>
-    <row r="58" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>47</v>
       </c>
@@ -12577,8 +12695,11 @@
       <c r="DB58" s="29">
         <v>1055.5270307099286</v>
       </c>
+      <c r="DC58" s="16">
+        <v>2453.3195964789857</v>
+      </c>
     </row>
-    <row r="59" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>48</v>
       </c>
@@ -12897,8 +13018,11 @@
       <c r="DB59" s="29">
         <v>853.38252652886604</v>
       </c>
+      <c r="DC59" s="16">
+        <v>622.81600495578778</v>
+      </c>
     </row>
-    <row r="60" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>49</v>
       </c>
@@ -13217,8 +13341,11 @@
       <c r="DB60" s="29">
         <v>400.35078514152951</v>
       </c>
+      <c r="DC60" s="16">
+        <v>332.54919039284334</v>
+      </c>
     </row>
-    <row r="61" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>50</v>
       </c>
@@ -13537,8 +13664,11 @@
       <c r="DB61" s="29">
         <v>856.4332438234419</v>
       </c>
+      <c r="DC61" s="16">
+        <v>433.88941906696175</v>
+      </c>
     </row>
-    <row r="62" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>51</v>
       </c>
@@ -13855,10 +13985,13 @@
         <v>23946.930747284736</v>
       </c>
       <c r="DB62" s="29">
-        <v>28186.923109356303</v>
+        <v>28255.627358209666</v>
+      </c>
+      <c r="DC62" s="16">
+        <v>23440.316117102386</v>
       </c>
     </row>
-    <row r="63" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>52</v>
       </c>
@@ -14175,10 +14308,13 @@
         <v>47539.458717893867</v>
       </c>
       <c r="DB63" s="29">
-        <v>46577.615523783024</v>
+        <v>46561.99268213287</v>
+      </c>
+      <c r="DC63" s="16">
+        <v>44328.300236136827</v>
       </c>
     </row>
-    <row r="64" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>53</v>
       </c>
@@ -14495,10 +14631,13 @@
         <v>66995.26063838409</v>
       </c>
       <c r="DB64" s="29">
-        <v>63264.11831125959</v>
+        <v>63264.118315719592</v>
+      </c>
+      <c r="DC64" s="16">
+        <v>50758.790887469921</v>
       </c>
     </row>
-    <row r="65" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>54</v>
       </c>
@@ -14817,8 +14956,11 @@
       <c r="DB65" s="29">
         <v>21213.123321251296</v>
       </c>
+      <c r="DC65" s="16">
+        <v>18882.762525241338</v>
+      </c>
     </row>
-    <row r="66" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>55</v>
       </c>
@@ -15135,10 +15277,13 @@
         <v>269.33946352914387</v>
       </c>
       <c r="DB66" s="29">
-        <v>778.89280009014419</v>
+        <v>812.72426054092102</v>
+      </c>
+      <c r="DC66" s="16">
+        <v>628.72936387982406</v>
       </c>
     </row>
-    <row r="67" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>56</v>
       </c>
@@ -15455,10 +15600,13 @@
         <v>67981.303807689488</v>
       </c>
       <c r="DB67" s="29">
-        <v>43938.349624153096</v>
+        <v>43471.775128537542</v>
+      </c>
+      <c r="DC67" s="16">
+        <v>42691.706300018792</v>
       </c>
     </row>
-    <row r="68" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>57</v>
       </c>
@@ -15777,9 +15925,12 @@
       <c r="DB68" s="29">
         <v>41690.009991389001</v>
       </c>
+      <c r="DC68" s="16">
+        <v>63293.230278798794</v>
+      </c>
     </row>
-    <row r="69" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" spans="1:106" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" spans="1:107" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
         <v>62</v>
       </c>
@@ -16096,10 +16247,13 @@
         <v>528808.93452259735</v>
       </c>
       <c r="DB70" s="30">
-        <v>455741.24889463489</v>
+        <v>455263.03570798878</v>
+      </c>
+      <c r="DC70" s="18">
+        <v>448278.45158153359</v>
       </c>
     </row>
-    <row r="71" spans="1:106" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:107" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="10"/>
       <c r="B71" s="10"/>
       <c r="C71" s="10"/>
@@ -16206,8 +16360,9 @@
       <c r="CZ71" s="19"/>
       <c r="DA71" s="19"/>
       <c r="DB71" s="19"/>
+      <c r="DC71" s="19"/>
     </row>
-    <row r="72" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>6</v>
       </c>
@@ -16224,10 +16379,11 @@
       <c r="CZ72" s="13"/>
       <c r="DA72" s="13"/>
       <c r="DB72" s="13"/>
+      <c r="DC72" s="13"/>
     </row>
-    <row r="73" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>0</v>
       </c>
@@ -16244,8 +16400,9 @@
       <c r="CZ75" s="20"/>
       <c r="DA75" s="20"/>
       <c r="DB75" s="20"/>
+      <c r="DC75" s="20"/>
     </row>
-    <row r="76" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>8</v>
       </c>
@@ -16262,10 +16419,11 @@
       <c r="CZ76" s="20"/>
       <c r="DA76" s="20"/>
       <c r="DB76" s="20"/>
+      <c r="DC76" s="20"/>
     </row>
-    <row r="77" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="CP77" s="13"/>
       <c r="CQ77" s="13"/>
@@ -16280,8 +16438,9 @@
       <c r="CZ77" s="20"/>
       <c r="DA77" s="20"/>
       <c r="DB77" s="20"/>
+      <c r="DC77" s="20"/>
     </row>
-    <row r="78" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP78" s="13"/>
       <c r="CQ78" s="13"/>
       <c r="CR78" s="13"/>
@@ -16295,8 +16454,9 @@
       <c r="CZ78" s="20"/>
       <c r="DA78" s="20"/>
       <c r="DB78" s="20"/>
+      <c r="DC78" s="20"/>
     </row>
-    <row r="79" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>64</v>
       </c>
@@ -16313,10 +16473,11 @@
       <c r="CZ79" s="20"/>
       <c r="DA79" s="20"/>
       <c r="DB79" s="20"/>
+      <c r="DC79" s="20"/>
     </row>
-    <row r="80" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="CP80" s="13"/>
       <c r="CQ80" s="13"/>
@@ -16331,8 +16492,9 @@
       <c r="CZ80" s="20"/>
       <c r="DA80" s="20"/>
       <c r="DB80" s="20"/>
+      <c r="DC80" s="20"/>
     </row>
-    <row r="81" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>9</v>
       </c>
@@ -16349,8 +16511,9 @@
       <c r="CZ81" s="20"/>
       <c r="DA81" s="20"/>
       <c r="DB81" s="20"/>
+      <c r="DC81" s="20"/>
     </row>
-    <row r="82" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP82" s="13"/>
       <c r="CQ82" s="13"/>
       <c r="CR82" s="13"/>
@@ -16359,13 +16522,14 @@
       <c r="CU82" s="13"/>
       <c r="CV82" s="13"/>
       <c r="CW82" s="13"/>
-      <c r="CX82" s="20"/>
+      <c r="CX82" s="13"/>
       <c r="CY82" s="20"/>
       <c r="CZ82" s="20"/>
       <c r="DA82" s="20"/>
       <c r="DB82" s="20"/>
+      <c r="DC82" s="20"/>
     </row>
-    <row r="83" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6"/>
       <c r="B83" s="6" t="s">
         <v>10</v>
@@ -16518,14 +16682,15 @@
       <c r="CV83" s="14"/>
       <c r="CW83" s="14"/>
       <c r="CX83" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="CY83" s="21"/>
+        <v>69</v>
+      </c>
+      <c r="CY83" s="14"/>
       <c r="CZ83" s="21"/>
       <c r="DA83" s="21"/>
       <c r="DB83" s="21"/>
+      <c r="DC83" s="21"/>
     </row>
-    <row r="84" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
         <v>37</v>
       </c>
@@ -16832,12 +16997,15 @@
       <c r="CX84" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="CY84" s="22"/>
+      <c r="CY84" s="15" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ84" s="22"/>
       <c r="DA84" s="22"/>
       <c r="DB84" s="22"/>
+      <c r="DC84" s="22"/>
     </row>
-    <row r="85" spans="1:106" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:107" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="4"/>
       <c r="CP85" s="13"/>
       <c r="CQ85" s="13"/>
@@ -16848,12 +17016,13 @@
       <c r="CV85" s="13"/>
       <c r="CW85" s="13"/>
       <c r="CX85" s="13"/>
-      <c r="CY85" s="20"/>
+      <c r="CY85" s="13"/>
       <c r="CZ85" s="20"/>
       <c r="DA85" s="20"/>
       <c r="DB85" s="20"/>
+      <c r="DC85" s="20"/>
     </row>
-    <row r="86" spans="1:106" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:107" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>38</v>
       </c>
@@ -17158,14 +17327,17 @@
         <v>-22.091145629658655</v>
       </c>
       <c r="CX86" s="23">
-        <v>4.2810184765305905</v>
-      </c>
-      <c r="CY86" s="24"/>
+        <v>3.9907541491049869</v>
+      </c>
+      <c r="CY86" s="23">
+        <v>33.923404504841358</v>
+      </c>
       <c r="CZ86" s="24"/>
       <c r="DA86" s="24"/>
       <c r="DB86" s="24"/>
+      <c r="DC86" s="24"/>
     </row>
-    <row r="87" spans="1:106" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:107" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>39</v>
       </c>
@@ -17470,14 +17642,17 @@
         <v>28.795353487038682</v>
       </c>
       <c r="CX87" s="23">
-        <v>21.356740619762562</v>
-      </c>
-      <c r="CY87" s="24"/>
+        <v>21.094683685825814</v>
+      </c>
+      <c r="CY87" s="23">
+        <v>27.387059056857566</v>
+      </c>
       <c r="CZ87" s="24"/>
       <c r="DA87" s="24"/>
       <c r="DB87" s="24"/>
+      <c r="DC87" s="24"/>
     </row>
-    <row r="88" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>40</v>
       </c>
@@ -17782,14 +17957,17 @@
         <v>-2.7033396374175283</v>
       </c>
       <c r="CX88" s="23">
-        <v>0.91168581482546074</v>
-      </c>
-      <c r="CY88" s="24"/>
+        <v>0.70546421117856539</v>
+      </c>
+      <c r="CY88" s="23">
+        <v>-17.814369379460487</v>
+      </c>
       <c r="CZ88" s="24"/>
       <c r="DA88" s="24"/>
       <c r="DB88" s="24"/>
+      <c r="DC88" s="24"/>
     </row>
-    <row r="89" spans="1:106" s="9" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:107" s="9" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
         <v>41</v>
       </c>
@@ -18094,14 +18272,17 @@
         <v>-36.024765146894886</v>
       </c>
       <c r="CX89" s="23">
-        <v>-26.251320604002132</v>
-      </c>
-      <c r="CY89" s="24"/>
+        <v>-27.219788082347151</v>
+      </c>
+      <c r="CY89" s="23">
+        <v>-36.318288655409795</v>
+      </c>
       <c r="CZ89" s="24"/>
       <c r="DA89" s="24"/>
       <c r="DB89" s="24"/>
+      <c r="DC89" s="24"/>
     </row>
-    <row r="90" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>42</v>
       </c>
@@ -18406,14 +18587,17 @@
         <v>-13.623449063297926</v>
       </c>
       <c r="CX90" s="23">
-        <v>-11.110480115943972</v>
-      </c>
-      <c r="CY90" s="24"/>
+        <v>-12.033138232525147</v>
+      </c>
+      <c r="CY90" s="23">
+        <v>-21.668988931164705</v>
+      </c>
       <c r="CZ90" s="24"/>
       <c r="DA90" s="24"/>
       <c r="DB90" s="24"/>
+      <c r="DC90" s="24"/>
     </row>
-    <row r="91" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>43</v>
       </c>
@@ -18718,14 +18902,17 @@
         <v>-12.33018922016241</v>
       </c>
       <c r="CX91" s="23">
-        <v>-7.2506579510080229</v>
-      </c>
-      <c r="CY91" s="24"/>
+        <v>-8.4326159793319277</v>
+      </c>
+      <c r="CY91" s="23">
+        <v>-8.4936523531216324</v>
+      </c>
       <c r="CZ91" s="24"/>
       <c r="DA91" s="24"/>
       <c r="DB91" s="24"/>
+      <c r="DC91" s="24"/>
     </row>
-    <row r="92" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>44</v>
       </c>
@@ -19030,14 +19217,17 @@
         <v>-15.030648724471007</v>
       </c>
       <c r="CX92" s="23">
-        <v>-36.330246503202325</v>
-      </c>
-      <c r="CY92" s="24"/>
+        <v>-38.472319038797131</v>
+      </c>
+      <c r="CY92" s="23">
+        <v>-3.1897059229308127</v>
+      </c>
       <c r="CZ92" s="24"/>
       <c r="DA92" s="24"/>
       <c r="DB92" s="24"/>
+      <c r="DC92" s="24"/>
     </row>
-    <row r="93" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>45</v>
       </c>
@@ -19342,14 +19532,17 @@
         <v>46.916510818471949</v>
       </c>
       <c r="CX93" s="23">
-        <v>-16.865752201970963</v>
-      </c>
-      <c r="CY93" s="24"/>
+        <v>-15.278085201493752</v>
+      </c>
+      <c r="CY93" s="23">
+        <v>-4.3459407343739116</v>
+      </c>
       <c r="CZ93" s="24"/>
       <c r="DA93" s="24"/>
       <c r="DB93" s="24"/>
+      <c r="DC93" s="24"/>
     </row>
-    <row r="94" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>46</v>
       </c>
@@ -19654,14 +19847,17 @@
         <v>-19.585638019418383</v>
       </c>
       <c r="CX94" s="23">
-        <v>7.1084233669934918</v>
-      </c>
-      <c r="CY94" s="24"/>
+        <v>9.4693412888878186</v>
+      </c>
+      <c r="CY94" s="23">
+        <v>34.934788231505706</v>
+      </c>
       <c r="CZ94" s="24"/>
       <c r="DA94" s="24"/>
       <c r="DB94" s="24"/>
+      <c r="DC94" s="24"/>
     </row>
-    <row r="95" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>47</v>
       </c>
@@ -19966,14 +20162,17 @@
         <v>-1.8745472423500047</v>
       </c>
       <c r="CX95" s="23">
-        <v>6.0957694736805763</v>
-      </c>
-      <c r="CY95" s="24"/>
+        <v>3.9022386240926892</v>
+      </c>
+      <c r="CY95" s="23">
+        <v>-3.5493459812860806</v>
+      </c>
       <c r="CZ95" s="24"/>
       <c r="DA95" s="24"/>
       <c r="DB95" s="24"/>
+      <c r="DC95" s="24"/>
     </row>
-    <row r="96" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>48</v>
       </c>
@@ -20278,14 +20477,17 @@
         <v>13.520994875484192</v>
       </c>
       <c r="CX96" s="23">
-        <v>-32.049359052804789</v>
-      </c>
-      <c r="CY96" s="24"/>
+        <v>-33.221154154925117</v>
+      </c>
+      <c r="CY96" s="23">
+        <v>-45.67438447965624</v>
+      </c>
       <c r="CZ96" s="24"/>
       <c r="DA96" s="24"/>
       <c r="DB96" s="24"/>
+      <c r="DC96" s="24"/>
     </row>
-    <row r="97" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>49</v>
       </c>
@@ -20590,14 +20792,17 @@
         <v>3.7846540215191311</v>
       </c>
       <c r="CX97" s="23">
-        <v>-17.669929167328519</v>
-      </c>
-      <c r="CY97" s="24"/>
+        <v>-14.250563349601308</v>
+      </c>
+      <c r="CY97" s="23">
+        <v>-3.0090660788550707</v>
+      </c>
       <c r="CZ97" s="24"/>
       <c r="DA97" s="24"/>
       <c r="DB97" s="24"/>
+      <c r="DC97" s="24"/>
     </row>
-    <row r="98" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>50</v>
       </c>
@@ -20902,14 +21107,17 @@
         <v>-40.583953815609696</v>
       </c>
       <c r="CX98" s="23">
-        <v>12.099274739620043</v>
-      </c>
-      <c r="CY98" s="24"/>
+        <v>11.975694907442303</v>
+      </c>
+      <c r="CY98" s="23">
+        <v>11.200012149443907</v>
+      </c>
       <c r="CZ98" s="24"/>
       <c r="DA98" s="24"/>
       <c r="DB98" s="24"/>
+      <c r="DC98" s="24"/>
     </row>
-    <row r="99" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
         <v>51</v>
       </c>
@@ -21214,14 +21422,17 @@
         <v>8.5555826442929686</v>
       </c>
       <c r="CX99" s="23">
-        <v>3.7277077479384246</v>
-      </c>
-      <c r="CY99" s="24"/>
+        <v>2.2293720687144685</v>
+      </c>
+      <c r="CY99" s="23">
+        <v>-6.4274484150671043</v>
+      </c>
       <c r="CZ99" s="24"/>
       <c r="DA99" s="24"/>
       <c r="DB99" s="24"/>
+      <c r="DC99" s="24"/>
     </row>
-    <row r="100" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
         <v>52</v>
       </c>
@@ -21526,14 +21737,17 @@
         <v>5.2919904278688961</v>
       </c>
       <c r="CX100" s="23">
-        <v>-8.7726016705020839</v>
-      </c>
-      <c r="CY100" s="24"/>
+        <v>-7.8976993438068348</v>
+      </c>
+      <c r="CY100" s="23">
+        <v>-11.019913222008455</v>
+      </c>
       <c r="CZ100" s="24"/>
       <c r="DA100" s="24"/>
       <c r="DB100" s="24"/>
+      <c r="DC100" s="24"/>
     </row>
-    <row r="101" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>53</v>
       </c>
@@ -21838,14 +22052,17 @@
         <v>13.912235470780487</v>
       </c>
       <c r="CX101" s="23">
-        <v>2.6326613808338948</v>
-      </c>
-      <c r="CY101" s="24"/>
+        <v>2.6460929105495126</v>
+      </c>
+      <c r="CY101" s="23">
+        <v>-1.270422504703248</v>
+      </c>
       <c r="CZ101" s="24"/>
       <c r="DA101" s="24"/>
       <c r="DB101" s="24"/>
+      <c r="DC101" s="24"/>
     </row>
-    <row r="102" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
         <v>54</v>
       </c>
@@ -22152,12 +22369,15 @@
       <c r="CX102" s="23">
         <v>-3.0091451327172649</v>
       </c>
-      <c r="CY102" s="24"/>
+      <c r="CY102" s="23">
+        <v>-6.1261450559099728</v>
+      </c>
       <c r="CZ102" s="24"/>
       <c r="DA102" s="24"/>
       <c r="DB102" s="24"/>
+      <c r="DC102" s="24"/>
     </row>
-    <row r="103" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>55</v>
       </c>
@@ -22462,14 +22682,17 @@
         <v>14.421440066642006</v>
       </c>
       <c r="CX103" s="23">
-        <v>-0.6455240490270171</v>
-      </c>
-      <c r="CY103" s="24"/>
+        <v>3.9644638054950292</v>
+      </c>
+      <c r="CY103" s="23">
+        <v>5.2419528223450271</v>
+      </c>
       <c r="CZ103" s="24"/>
       <c r="DA103" s="24"/>
       <c r="DB103" s="24"/>
+      <c r="DC103" s="24"/>
     </row>
-    <row r="104" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>56</v>
       </c>
@@ -22774,14 +22997,17 @@
         <v>10.647350377498086</v>
       </c>
       <c r="CX104" s="23">
-        <v>-0.4420461052861242</v>
-      </c>
-      <c r="CY104" s="24"/>
+        <v>-1.9357636548583201</v>
+      </c>
+      <c r="CY104" s="23">
+        <v>11.426916287049266</v>
+      </c>
       <c r="CZ104" s="24"/>
       <c r="DA104" s="24"/>
       <c r="DB104" s="24"/>
+      <c r="DC104" s="24"/>
     </row>
-    <row r="105" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>57</v>
       </c>
@@ -23088,18 +23314,21 @@
       <c r="CX105" s="23">
         <v>-1.1157915071133431</v>
       </c>
-      <c r="CY105" s="24"/>
+      <c r="CY105" s="23">
+        <v>1.6229133797150297</v>
+      </c>
       <c r="CZ105" s="24"/>
       <c r="DA105" s="24"/>
       <c r="DB105" s="24"/>
+      <c r="DC105" s="24"/>
     </row>
-    <row r="106" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="CY106" s="25"/>
+    <row r="106" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="CZ106" s="25"/>
       <c r="DA106" s="25"/>
       <c r="DB106" s="25"/>
+      <c r="DC106" s="25"/>
     </row>
-    <row r="107" spans="1:106" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:107" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
         <v>62</v>
       </c>
@@ -23404,14 +23633,17 @@
         <v>-2.0499984234648139</v>
       </c>
       <c r="CX107" s="23">
-        <v>-1.3730581800920305</v>
-      </c>
-      <c r="CY107" s="24"/>
+        <v>-1.6824456920971613</v>
+      </c>
+      <c r="CY107" s="23">
+        <v>1.7830872175274237</v>
+      </c>
       <c r="CZ107" s="24"/>
       <c r="DA107" s="24"/>
       <c r="DB107" s="24"/>
+      <c r="DC107" s="24"/>
     </row>
-    <row r="108" spans="1:106" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:107" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="10"/>
       <c r="B108" s="10"/>
       <c r="C108" s="10"/>
@@ -23514,12 +23746,13 @@
       <c r="CV108" s="19"/>
       <c r="CW108" s="19"/>
       <c r="CX108" s="19"/>
-      <c r="CY108" s="22"/>
+      <c r="CY108" s="19"/>
       <c r="CZ108" s="22"/>
       <c r="DA108" s="22"/>
       <c r="DB108" s="22"/>
+      <c r="DC108" s="22"/>
     </row>
-    <row r="109" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>6</v>
       </c>
@@ -23532,24 +23765,25 @@
       <c r="CV109" s="13"/>
       <c r="CW109" s="13"/>
       <c r="CX109" s="13"/>
-      <c r="CY109" s="20"/>
+      <c r="CY109" s="13"/>
       <c r="CZ109" s="20"/>
       <c r="DA109" s="20"/>
       <c r="DB109" s="20"/>
+      <c r="DC109" s="20"/>
     </row>
-    <row r="110" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="CY110" s="25"/>
+    <row r="110" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="CZ110" s="25"/>
       <c r="DA110" s="25"/>
       <c r="DB110" s="25"/>
+      <c r="DC110" s="25"/>
     </row>
-    <row r="111" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="CY111" s="25"/>
+    <row r="111" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="CZ111" s="25"/>
       <c r="DA111" s="25"/>
       <c r="DB111" s="25"/>
+      <c r="DC111" s="25"/>
     </row>
-    <row r="112" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
         <v>0</v>
       </c>
@@ -23562,12 +23796,13 @@
       <c r="CV112" s="13"/>
       <c r="CW112" s="13"/>
       <c r="CX112" s="13"/>
-      <c r="CY112" s="20"/>
+      <c r="CY112" s="13"/>
       <c r="CZ112" s="20"/>
       <c r="DA112" s="20"/>
       <c r="DB112" s="20"/>
+      <c r="DC112" s="20"/>
     </row>
-    <row r="113" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>8</v>
       </c>
@@ -23580,14 +23815,15 @@
       <c r="CV113" s="13"/>
       <c r="CW113" s="13"/>
       <c r="CX113" s="13"/>
-      <c r="CY113" s="20"/>
+      <c r="CY113" s="13"/>
       <c r="CZ113" s="20"/>
       <c r="DA113" s="20"/>
       <c r="DB113" s="20"/>
+      <c r="DC113" s="20"/>
     </row>
-    <row r="114" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="CP114" s="13"/>
       <c r="CQ114" s="13"/>
@@ -23598,12 +23834,13 @@
       <c r="CV114" s="13"/>
       <c r="CW114" s="13"/>
       <c r="CX114" s="13"/>
-      <c r="CY114" s="20"/>
+      <c r="CY114" s="13"/>
       <c r="CZ114" s="20"/>
       <c r="DA114" s="20"/>
       <c r="DB114" s="20"/>
+      <c r="DC114" s="20"/>
     </row>
-    <row r="115" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP115" s="13"/>
       <c r="CQ115" s="13"/>
       <c r="CR115" s="13"/>
@@ -23613,12 +23850,13 @@
       <c r="CV115" s="13"/>
       <c r="CW115" s="13"/>
       <c r="CX115" s="13"/>
-      <c r="CY115" s="20"/>
+      <c r="CY115" s="13"/>
       <c r="CZ115" s="20"/>
       <c r="DA115" s="20"/>
       <c r="DB115" s="20"/>
+      <c r="DC115" s="20"/>
     </row>
-    <row r="116" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>65</v>
       </c>
@@ -23631,14 +23869,15 @@
       <c r="CV116" s="13"/>
       <c r="CW116" s="13"/>
       <c r="CX116" s="13"/>
-      <c r="CY116" s="20"/>
+      <c r="CY116" s="13"/>
       <c r="CZ116" s="20"/>
       <c r="DA116" s="20"/>
       <c r="DB116" s="20"/>
+      <c r="DC116" s="20"/>
     </row>
-    <row r="117" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="CP117" s="13"/>
       <c r="CQ117" s="13"/>
@@ -23649,12 +23888,13 @@
       <c r="CV117" s="13"/>
       <c r="CW117" s="13"/>
       <c r="CX117" s="13"/>
-      <c r="CY117" s="20"/>
+      <c r="CY117" s="13"/>
       <c r="CZ117" s="20"/>
       <c r="DA117" s="20"/>
       <c r="DB117" s="20"/>
+      <c r="DC117" s="20"/>
     </row>
-    <row r="118" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
         <v>35</v>
       </c>
@@ -23667,12 +23907,13 @@
       <c r="CV118" s="13"/>
       <c r="CW118" s="13"/>
       <c r="CX118" s="13"/>
-      <c r="CY118" s="20"/>
+      <c r="CY118" s="13"/>
       <c r="CZ118" s="20"/>
       <c r="DA118" s="20"/>
       <c r="DB118" s="20"/>
+      <c r="DC118" s="20"/>
     </row>
-    <row r="119" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP119" s="13"/>
       <c r="CQ119" s="13"/>
       <c r="CR119" s="13"/>
@@ -23682,12 +23923,13 @@
       <c r="CV119" s="13"/>
       <c r="CW119" s="13"/>
       <c r="CX119" s="13"/>
-      <c r="CY119" s="20"/>
+      <c r="CY119" s="13"/>
       <c r="CZ119" s="20"/>
       <c r="DA119" s="20"/>
       <c r="DB119" s="20"/>
+      <c r="DC119" s="20"/>
     </row>
-    <row r="120" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A120" s="6"/>
       <c r="B120" s="6" t="s">
         <v>10</v>
@@ -23840,14 +24082,15 @@
       <c r="CV120" s="14"/>
       <c r="CW120" s="14"/>
       <c r="CX120" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="CY120" s="21"/>
+        <v>69</v>
+      </c>
+      <c r="CY120" s="14"/>
       <c r="CZ120" s="21"/>
       <c r="DA120" s="21"/>
       <c r="DB120" s="21"/>
+      <c r="DC120" s="21"/>
     </row>
-    <row r="121" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
         <v>37</v>
       </c>
@@ -24154,12 +24397,15 @@
       <c r="CX121" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="CY121" s="22"/>
+      <c r="CY121" s="15" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ121" s="22"/>
       <c r="DA121" s="22"/>
       <c r="DB121" s="22"/>
+      <c r="DC121" s="22"/>
     </row>
-    <row r="122" spans="1:106" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:107" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="4"/>
       <c r="CP122" s="13"/>
       <c r="CQ122" s="13"/>
@@ -24170,12 +24416,13 @@
       <c r="CV122" s="13"/>
       <c r="CW122" s="13"/>
       <c r="CX122" s="13"/>
-      <c r="CY122" s="20"/>
+      <c r="CY122" s="13"/>
       <c r="CZ122" s="20"/>
       <c r="DA122" s="20"/>
       <c r="DB122" s="20"/>
+      <c r="DC122" s="20"/>
     </row>
-    <row r="123" spans="1:106" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:107" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>38</v>
       </c>
@@ -24480,14 +24727,17 @@
         <v>-5.2413242937608402</v>
       </c>
       <c r="CX123" s="23">
-        <v>-6.2600231023244532</v>
-      </c>
-      <c r="CY123" s="24"/>
+        <v>-6.4576904177097134</v>
+      </c>
+      <c r="CY123" s="23">
+        <v>5.7194267427267818</v>
+      </c>
       <c r="CZ123" s="24"/>
       <c r="DA123" s="24"/>
       <c r="DB123" s="24"/>
+      <c r="DC123" s="24"/>
     </row>
-    <row r="124" spans="1:106" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:107" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
         <v>39</v>
       </c>
@@ -24792,14 +25042,17 @@
         <v>2.695636478873368</v>
       </c>
       <c r="CX124" s="23">
-        <v>-5.5018838603154734</v>
-      </c>
-      <c r="CY124" s="24"/>
+        <v>-5.5022551345561936</v>
+      </c>
+      <c r="CY124" s="23">
+        <v>0.78368475869434917</v>
+      </c>
       <c r="CZ124" s="24"/>
       <c r="DA124" s="24"/>
       <c r="DB124" s="24"/>
+      <c r="DC124" s="24"/>
     </row>
-    <row r="125" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>40</v>
       </c>
@@ -25104,14 +25357,17 @@
         <v>0.11405571996236574</v>
       </c>
       <c r="CX125" s="23">
-        <v>1.4136403716252062</v>
-      </c>
-      <c r="CY125" s="24"/>
+        <v>1.4136403716251635</v>
+      </c>
+      <c r="CY125" s="23">
+        <v>2.3809623304295258</v>
+      </c>
       <c r="CZ125" s="24"/>
       <c r="DA125" s="24"/>
       <c r="DB125" s="24"/>
+      <c r="DC125" s="24"/>
     </row>
-    <row r="126" spans="1:106" s="9" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:107" s="9" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="s">
         <v>41</v>
       </c>
@@ -25416,14 +25672,17 @@
         <v>0.18924866684686492</v>
       </c>
       <c r="CX126" s="23">
-        <v>-7.9745677627628027</v>
-      </c>
-      <c r="CY126" s="24"/>
+        <v>-7.9745678277291461</v>
+      </c>
+      <c r="CY126" s="23">
+        <v>-22.537222075232904</v>
+      </c>
       <c r="CZ126" s="24"/>
       <c r="DA126" s="24"/>
       <c r="DB126" s="24"/>
+      <c r="DC126" s="24"/>
     </row>
-    <row r="127" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
         <v>42</v>
       </c>
@@ -25728,14 +25987,17 @@
         <v>-5.4755297275249859E-2</v>
       </c>
       <c r="CX127" s="23">
-        <v>-2.6569603555002459</v>
-      </c>
-      <c r="CY127" s="24"/>
+        <v>-2.6569603555002317</v>
+      </c>
+      <c r="CY127" s="23">
+        <v>-4.0027684056330344</v>
+      </c>
       <c r="CZ127" s="24"/>
       <c r="DA127" s="24"/>
       <c r="DB127" s="24"/>
+      <c r="DC127" s="24"/>
     </row>
-    <row r="128" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
         <v>43</v>
       </c>
@@ -26040,14 +26302,17 @@
         <v>2.0976342184996213</v>
       </c>
       <c r="CX128" s="23">
-        <v>-0.37392626016890063</v>
-      </c>
-      <c r="CY128" s="24"/>
+        <v>-0.37392626016892905</v>
+      </c>
+      <c r="CY128" s="23">
+        <v>7.4020292525462708</v>
+      </c>
       <c r="CZ128" s="24"/>
       <c r="DA128" s="24"/>
       <c r="DB128" s="24"/>
+      <c r="DC128" s="24"/>
     </row>
-    <row r="129" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
         <v>44</v>
       </c>
@@ -26352,14 +26617,17 @@
         <v>-2.8996150371513068</v>
       </c>
       <c r="CX129" s="23">
-        <v>6.3113749865831181</v>
-      </c>
-      <c r="CY129" s="24"/>
+        <v>6.3113749865830755</v>
+      </c>
+      <c r="CY129" s="23">
+        <v>5.51067254047652</v>
+      </c>
       <c r="CZ129" s="24"/>
       <c r="DA129" s="24"/>
       <c r="DB129" s="24"/>
+      <c r="DC129" s="24"/>
     </row>
-    <row r="130" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
         <v>45</v>
       </c>
@@ -26664,14 +26932,17 @@
         <v>8.887083275596865</v>
       </c>
       <c r="CX130" s="23">
-        <v>-0.25979614820100494</v>
-      </c>
-      <c r="CY130" s="24"/>
+        <v>2.4834328073558964</v>
+      </c>
+      <c r="CY130" s="23">
+        <v>10.320817007812707</v>
+      </c>
       <c r="CZ130" s="24"/>
       <c r="DA130" s="24"/>
       <c r="DB130" s="24"/>
+      <c r="DC130" s="24"/>
     </row>
-    <row r="131" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
         <v>46</v>
       </c>
@@ -26976,14 +27247,17 @@
         <v>-2.7472561771661503</v>
       </c>
       <c r="CX131" s="23">
-        <v>1.8370319462990778</v>
-      </c>
-      <c r="CY131" s="24"/>
+        <v>1.8370319462990494</v>
+      </c>
+      <c r="CY131" s="23">
+        <v>11.583531806941252</v>
+      </c>
       <c r="CZ131" s="24"/>
       <c r="DA131" s="24"/>
       <c r="DB131" s="24"/>
+      <c r="DC131" s="24"/>
     </row>
-    <row r="132" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
         <v>47</v>
       </c>
@@ -27290,12 +27564,15 @@
       <c r="CX132" s="23">
         <v>6.8574124018544182</v>
       </c>
-      <c r="CY132" s="24"/>
+      <c r="CY132" s="23">
+        <v>-16.429451810155797</v>
+      </c>
       <c r="CZ132" s="24"/>
       <c r="DA132" s="24"/>
       <c r="DB132" s="24"/>
+      <c r="DC132" s="24"/>
     </row>
-    <row r="133" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
         <v>48</v>
       </c>
@@ -27602,12 +27879,15 @@
       <c r="CX133" s="23">
         <v>13.556692105806704</v>
       </c>
-      <c r="CY133" s="24"/>
+      <c r="CY133" s="23">
+        <v>3.2190343587446648</v>
+      </c>
       <c r="CZ133" s="24"/>
       <c r="DA133" s="24"/>
       <c r="DB133" s="24"/>
+      <c r="DC133" s="24"/>
     </row>
-    <row r="134" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
         <v>49</v>
       </c>
@@ -27914,12 +28194,15 @@
       <c r="CX134" s="23">
         <v>0.53291406982683043</v>
       </c>
-      <c r="CY134" s="24"/>
+      <c r="CY134" s="23">
+        <v>1.6581068832039847</v>
+      </c>
       <c r="CZ134" s="24"/>
       <c r="DA134" s="24"/>
       <c r="DB134" s="24"/>
+      <c r="DC134" s="24"/>
     </row>
-    <row r="135" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
         <v>50</v>
       </c>
@@ -28226,12 +28509,15 @@
       <c r="CX135" s="23">
         <v>41.57720257038946</v>
       </c>
-      <c r="CY135" s="24"/>
+      <c r="CY135" s="23">
+        <v>10.588536797072322</v>
+      </c>
       <c r="CZ135" s="24"/>
       <c r="DA135" s="24"/>
       <c r="DB135" s="24"/>
+      <c r="DC135" s="24"/>
     </row>
-    <row r="136" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
         <v>51</v>
       </c>
@@ -28536,14 +28822,17 @@
         <v>-0.74922325829393799</v>
       </c>
       <c r="CX136" s="23">
-        <v>7.7966007191015763</v>
-      </c>
-      <c r="CY136" s="24"/>
+        <v>8.0593496701885385</v>
+      </c>
+      <c r="CY136" s="23">
+        <v>0.98829992907243991</v>
+      </c>
       <c r="CZ136" s="24"/>
       <c r="DA136" s="24"/>
       <c r="DB136" s="24"/>
+      <c r="DC136" s="24"/>
     </row>
-    <row r="137" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
         <v>52</v>
       </c>
@@ -28848,14 +29137,17 @@
         <v>1.5808547207083308</v>
       </c>
       <c r="CX137" s="23">
-        <v>5.0309169267710701</v>
-      </c>
-      <c r="CY137" s="24"/>
+        <v>4.9956879575534572</v>
+      </c>
+      <c r="CY137" s="23">
+        <v>3.6440570387989908</v>
+      </c>
       <c r="CZ137" s="24"/>
       <c r="DA137" s="24"/>
       <c r="DB137" s="24"/>
+      <c r="DC137" s="24"/>
     </row>
-    <row r="138" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
         <v>53</v>
       </c>
@@ -29160,14 +29452,17 @@
         <v>8.8696996093931659</v>
       </c>
       <c r="CX138" s="23">
-        <v>7.0421579189176668</v>
-      </c>
-      <c r="CY138" s="24"/>
+        <v>7.0421579264639433</v>
+      </c>
+      <c r="CY138" s="23">
+        <v>6.343676869024776</v>
+      </c>
       <c r="CZ138" s="24"/>
       <c r="DA138" s="24"/>
       <c r="DB138" s="24"/>
+      <c r="DC138" s="24"/>
     </row>
-    <row r="139" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
         <v>54</v>
       </c>
@@ -29474,12 +29769,15 @@
       <c r="CX139" s="23">
         <v>6.1843622652765049</v>
       </c>
-      <c r="CY139" s="24"/>
+      <c r="CY139" s="23">
+        <v>5.1482985413308597</v>
+      </c>
       <c r="CZ139" s="24"/>
       <c r="DA139" s="24"/>
       <c r="DB139" s="24"/>
+      <c r="DC139" s="24"/>
     </row>
-    <row r="140" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
         <v>55</v>
       </c>
@@ -29784,14 +30082,17 @@
         <v>15.014442596536298</v>
       </c>
       <c r="CX140" s="23">
-        <v>-1.7681875968015248</v>
-      </c>
-      <c r="CY140" s="24"/>
+        <v>2.4985429159754915</v>
+      </c>
+      <c r="CY140" s="23">
+        <v>3.2181991071652476</v>
+      </c>
       <c r="CZ140" s="24"/>
       <c r="DA140" s="24"/>
       <c r="DB140" s="24"/>
+      <c r="DC140" s="24"/>
     </row>
-    <row r="141" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
         <v>56</v>
       </c>
@@ -30096,14 +30397,17 @@
         <v>4.7059274152744734</v>
       </c>
       <c r="CX141" s="23">
-        <v>-5.0052215522969874</v>
-      </c>
-      <c r="CY141" s="24"/>
+        <v>-6.0139563186111076</v>
+      </c>
+      <c r="CY141" s="23">
+        <v>2.7009207230556171</v>
+      </c>
       <c r="CZ141" s="24"/>
       <c r="DA141" s="24"/>
       <c r="DB141" s="24"/>
+      <c r="DC141" s="24"/>
     </row>
-    <row r="142" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
         <v>57</v>
       </c>
@@ -30410,18 +30714,21 @@
       <c r="CX142" s="23">
         <v>0.10378601681553334</v>
       </c>
-      <c r="CY142" s="24"/>
+      <c r="CY142" s="23">
+        <v>3.273542161472804</v>
+      </c>
       <c r="CZ142" s="24"/>
       <c r="DA142" s="24"/>
       <c r="DB142" s="24"/>
+      <c r="DC142" s="24"/>
     </row>
-    <row r="143" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="CY143" s="25"/>
+    <row r="143" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="CZ143" s="25"/>
       <c r="DA143" s="25"/>
       <c r="DB143" s="25"/>
+      <c r="DC143" s="25"/>
     </row>
-    <row r="144" spans="1:106" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:107" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="5" t="s">
         <v>62</v>
       </c>
@@ -30726,14 +31033,17 @@
         <v>1.0256262320668554</v>
       </c>
       <c r="CX144" s="23">
-        <v>-0.20950936020631161</v>
-      </c>
-      <c r="CY144" s="24"/>
+        <v>-0.31422037471635633</v>
+      </c>
+      <c r="CY144" s="23">
+        <v>2.7003314368928955</v>
+      </c>
       <c r="CZ144" s="24"/>
       <c r="DA144" s="24"/>
       <c r="DB144" s="24"/>
+      <c r="DC144" s="24"/>
     </row>
-    <row r="145" spans="1:106" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:107" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="10"/>
       <c r="B145" s="10"/>
       <c r="C145" s="10"/>
@@ -30836,12 +31146,13 @@
       <c r="CV145" s="19"/>
       <c r="CW145" s="19"/>
       <c r="CX145" s="19"/>
-      <c r="CY145" s="22"/>
+      <c r="CY145" s="19"/>
       <c r="CZ145" s="22"/>
       <c r="DA145" s="22"/>
       <c r="DB145" s="22"/>
+      <c r="DC145" s="22"/>
     </row>
-    <row r="146" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
         <v>6</v>
       </c>
@@ -30854,25 +31165,27 @@
       <c r="CV146" s="13"/>
       <c r="CW146" s="13"/>
       <c r="CX146" s="13"/>
-      <c r="CY146" s="20"/>
+      <c r="CY146" s="13"/>
       <c r="CZ146" s="20"/>
       <c r="DA146" s="20"/>
       <c r="DB146" s="20"/>
+      <c r="DC146" s="20"/>
     </row>
-    <row r="147" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="CY147" s="25"/>
+    <row r="147" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="CZ147" s="25"/>
       <c r="DA147" s="25"/>
       <c r="DB147" s="25"/>
+      <c r="DC147" s="25"/>
     </row>
-    <row r="148" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="CX148" s="25"/>
       <c r="CY148" s="25"/>
       <c r="CZ148" s="25"/>
       <c r="DA148" s="25"/>
       <c r="DB148" s="25"/>
+      <c r="DC148" s="25"/>
     </row>
-    <row r="149" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
         <v>0</v>
       </c>
@@ -30889,10 +31202,11 @@
       <c r="CZ149" s="13"/>
       <c r="DA149" s="13"/>
       <c r="DB149" s="13"/>
+      <c r="DC149" s="13"/>
     </row>
-    <row r="150" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="CP150" s="13"/>
       <c r="CQ150" s="13"/>
@@ -30907,8 +31221,9 @@
       <c r="CZ150" s="13"/>
       <c r="DA150" s="13"/>
       <c r="DB150" s="13"/>
+      <c r="DC150" s="13"/>
     </row>
-    <row r="151" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP151" s="13"/>
       <c r="CQ151" s="13"/>
       <c r="CR151" s="13"/>
@@ -30922,8 +31237,9 @@
       <c r="CZ151" s="13"/>
       <c r="DA151" s="13"/>
       <c r="DB151" s="13"/>
+      <c r="DC151" s="13"/>
     </row>
-    <row r="152" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
         <v>66</v>
       </c>
@@ -30940,10 +31256,11 @@
       <c r="CZ152" s="13"/>
       <c r="DA152" s="13"/>
       <c r="DB152" s="13"/>
+      <c r="DC152" s="13"/>
     </row>
-    <row r="153" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="CP153" s="13"/>
       <c r="CQ153" s="13"/>
@@ -30958,8 +31275,9 @@
       <c r="CZ153" s="13"/>
       <c r="DA153" s="13"/>
       <c r="DB153" s="13"/>
+      <c r="DC153" s="13"/>
     </row>
-    <row r="154" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
         <v>36</v>
       </c>
@@ -30976,8 +31294,9 @@
       <c r="CZ154" s="13"/>
       <c r="DA154" s="13"/>
       <c r="DB154" s="13"/>
+      <c r="DC154" s="13"/>
     </row>
-    <row r="155" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP155" s="13"/>
       <c r="CQ155" s="13"/>
       <c r="CR155" s="13"/>
@@ -30991,8 +31310,9 @@
       <c r="CZ155" s="13"/>
       <c r="DA155" s="13"/>
       <c r="DB155" s="13"/>
+      <c r="DC155" s="13"/>
     </row>
-    <row r="156" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A156" s="6"/>
       <c r="B156" s="6">
         <v>2000</v>
@@ -31153,8 +31473,9 @@
       <c r="DB156" s="14">
         <v>2026</v>
       </c>
+      <c r="DC156" s="14"/>
     </row>
-    <row r="157" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A157" s="3" t="s">
         <v>37</v>
       </c>
@@ -31473,8 +31794,11 @@
       <c r="DB157" s="15" t="s">
         <v>2</v>
       </c>
+      <c r="DC157" s="15" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="158" spans="1:106" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:107" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="4"/>
       <c r="CP158" s="13"/>
       <c r="CQ158" s="13"/>
@@ -31489,8 +31813,9 @@
       <c r="CZ158" s="13"/>
       <c r="DA158" s="13"/>
       <c r="DB158" s="13"/>
+      <c r="DC158" s="13"/>
     </row>
-    <row r="159" spans="1:106" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:107" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
         <v>38</v>
       </c>
@@ -31807,10 +32132,13 @@
         <v>96.902644283648726</v>
       </c>
       <c r="DB159" s="23">
-        <v>123.85615839394606</v>
+        <v>123.77240301473793</v>
+      </c>
+      <c r="DC159" s="23">
+        <v>114.80621907068237</v>
       </c>
     </row>
-    <row r="160" spans="1:106" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:107" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
         <v>39</v>
       </c>
@@ -32127,10 +32455,13 @@
         <v>125.73020868340932</v>
       </c>
       <c r="DB160" s="23">
-        <v>132.13496926840679</v>
+        <v>131.85015592652584</v>
+      </c>
+      <c r="DC160" s="23">
+        <v>126.61858836698686</v>
       </c>
     </row>
-    <row r="161" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
         <v>40</v>
       </c>
@@ -32447,10 +32778,13 @@
         <v>123.0613450712319</v>
       </c>
       <c r="DB161" s="23">
-        <v>114.83868294546578</v>
+        <v>114.60400033991336</v>
+      </c>
+      <c r="DC161" s="23">
+        <v>169.74068588644812</v>
       </c>
     </row>
-    <row r="162" spans="1:106" s="9" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:107" s="9" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="5" t="s">
         <v>41</v>
       </c>
@@ -32767,10 +33101,13 @@
         <v>146.50325890277122</v>
       </c>
       <c r="DB162" s="23">
-        <v>90.618221388651577</v>
+        <v>89.4282231890475</v>
+      </c>
+      <c r="DC162" s="23">
+        <v>68.481682022861349</v>
       </c>
     </row>
-    <row r="163" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
         <v>42</v>
       </c>
@@ -33087,10 +33424,13 @@
         <v>101.53550263341693</v>
       </c>
       <c r="DB163" s="23">
-        <v>110.89852463793663</v>
+        <v>109.74741679071758</v>
+      </c>
+      <c r="DC163" s="23">
+        <v>87.766215361267058</v>
       </c>
     </row>
-    <row r="164" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
         <v>43</v>
       </c>
@@ -33407,10 +33747,13 @@
         <v>117.5199353531869</v>
       </c>
       <c r="DB164" s="23">
-        <v>117.51053899552961</v>
+        <v>116.0130348417528</v>
+      </c>
+      <c r="DC164" s="23">
+        <v>118.4116435784446</v>
       </c>
     </row>
-    <row r="165" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
         <v>44</v>
       </c>
@@ -33727,10 +34070,13 @@
         <v>158.17950629238996</v>
       </c>
       <c r="DB165" s="23">
-        <v>110.05707301916676</v>
+        <v>106.35436929385449</v>
+      </c>
+      <c r="DC165" s="23">
+        <v>80.132964375263526</v>
       </c>
     </row>
-    <row r="166" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
         <v>45</v>
       </c>
@@ -34047,10 +34393,13 @@
         <v>365.48935714009139</v>
       </c>
       <c r="DB166" s="23">
-        <v>221.08316209747349</v>
+        <v>219.27445786501795</v>
+      </c>
+      <c r="DC166" s="23">
+        <v>281.01110233765189</v>
       </c>
     </row>
-    <row r="167" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
         <v>46</v>
       </c>
@@ -34367,10 +34716,13 @@
         <v>195.66627824347322</v>
       </c>
       <c r="DB167" s="23">
-        <v>140.79051465197543</v>
+        <v>143.89386393885334</v>
+      </c>
+      <c r="DC167" s="23">
+        <v>168.7625710505425</v>
       </c>
     </row>
-    <row r="168" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
         <v>47</v>
       </c>
@@ -34687,10 +35039,13 @@
         <v>159.73765760699243</v>
       </c>
       <c r="DB168" s="23">
-        <v>219.27662614106481</v>
+        <v>214.74308020968539</v>
+      </c>
+      <c r="DC168" s="23">
+        <v>161.36654626960242</v>
       </c>
     </row>
-    <row r="169" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
         <v>48</v>
       </c>
@@ -35007,10 +35362,13 @@
         <v>263.83965720327484</v>
       </c>
       <c r="DB169" s="23">
-        <v>114.46391823982071</v>
+        <v>112.49001104934764</v>
+      </c>
+      <c r="DC169" s="23">
+        <v>88.161450597150903</v>
       </c>
     </row>
-    <row r="170" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
         <v>49</v>
       </c>
@@ -35327,10 +35685,13 @@
         <v>121.51106198125048</v>
       </c>
       <c r="DB170" s="23">
-        <v>69.368443397197169</v>
+        <v>72.249481659187737</v>
+      </c>
+      <c r="DC170" s="23">
+        <v>52.808989835716183</v>
       </c>
     </row>
-    <row r="171" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
         <v>50</v>
       </c>
@@ -35647,10 +36008,13 @@
         <v>58.563084232841646</v>
       </c>
       <c r="DB171" s="23">
-        <v>79.687568724889687</v>
+        <v>79.599720017638475</v>
+      </c>
+      <c r="DC171" s="23">
+        <v>43.505088378531426</v>
       </c>
     </row>
-    <row r="172" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
         <v>51</v>
       </c>
@@ -35967,10 +36331,13 @@
         <v>170.92778463981352</v>
       </c>
       <c r="DB172" s="23">
-        <v>122.79461140535805</v>
+        <v>120.72659116417898</v>
+      </c>
+      <c r="DC172" s="23">
+        <v>87.879107865112388</v>
       </c>
     </row>
-    <row r="173" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
         <v>52</v>
       </c>
@@ -36287,10 +36654,13 @@
         <v>195.09997129288402</v>
       </c>
       <c r="DB173" s="23">
-        <v>157.21745542800838</v>
+        <v>158.77848196468133</v>
+      </c>
+      <c r="DC173" s="23">
+        <v>174.97853296611021</v>
       </c>
     </row>
-    <row r="174" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
         <v>53</v>
       </c>
@@ -36607,10 +36977,13 @@
         <v>130.52214955338533</v>
       </c>
       <c r="DB174" s="23">
-        <v>164.09650400591244</v>
+        <v>164.11797929314233</v>
+      </c>
+      <c r="DC174" s="23">
+        <v>117.73685279115544</v>
       </c>
     </row>
-    <row r="175" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
         <v>54</v>
       </c>
@@ -36929,8 +37302,11 @@
       <c r="DB175" s="23">
         <v>119.71315149819681</v>
       </c>
+      <c r="DC175" s="23">
+        <v>86.18611061076902</v>
+      </c>
     </row>
-    <row r="176" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
         <v>55</v>
       </c>
@@ -37247,10 +37623,13 @@
         <v>43.221377809182215</v>
       </c>
       <c r="DB176" s="23">
-        <v>38.239124275738995</v>
+        <v>38.347749715218349</v>
+      </c>
+      <c r="DC176" s="23">
+        <v>35.282951679294271</v>
       </c>
     </row>
-    <row r="177" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
         <v>56</v>
       </c>
@@ -37567,10 +37946,13 @@
         <v>112.08461279281046</v>
       </c>
       <c r="DB177" s="23">
-        <v>156.90848592537191</v>
+        <v>156.2131125175338</v>
+      </c>
+      <c r="DC177" s="23">
+        <v>147.6673459905536</v>
       </c>
     </row>
-    <row r="178" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
         <v>57</v>
       </c>
@@ -37889,9 +38271,12 @@
       <c r="DB178" s="23">
         <v>138.43660614628374</v>
       </c>
+      <c r="DC178" s="23">
+        <v>161.39277831708597</v>
+      </c>
     </row>
-    <row r="179" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" spans="1:106" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" spans="1:107" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="5" t="s">
         <v>62</v>
       </c>
@@ -38208,10 +38593,13 @@
         <v>130.42743775193267</v>
       </c>
       <c r="DB180" s="23">
-        <v>135.69209464828543</v>
+        <v>135.40852102590358</v>
+      </c>
+      <c r="DC180" s="23">
+        <v>127.99111032947754</v>
       </c>
     </row>
-    <row r="181" spans="1:106" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:107" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="10"/>
       <c r="B181" s="10"/>
       <c r="C181" s="10"/>
@@ -38318,8 +38706,9 @@
       <c r="CZ181" s="19"/>
       <c r="DA181" s="19"/>
       <c r="DB181" s="19"/>
+      <c r="DC181" s="19"/>
     </row>
-    <row r="182" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
         <v>6</v>
       </c>
@@ -38336,8 +38725,9 @@
       <c r="CZ182" s="13"/>
       <c r="DA182" s="13"/>
       <c r="DB182" s="13"/>
+      <c r="DC182" s="13"/>
     </row>
-    <row r="185" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
         <v>0</v>
       </c>
@@ -38354,8 +38744,9 @@
       <c r="CZ185" s="13"/>
       <c r="DA185" s="13"/>
       <c r="DB185" s="13"/>
+      <c r="DC185" s="13"/>
     </row>
-    <row r="186" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
         <v>8</v>
       </c>
@@ -38372,10 +38763,11 @@
       <c r="CZ186" s="13"/>
       <c r="DA186" s="13"/>
       <c r="DB186" s="13"/>
+      <c r="DC186" s="13"/>
     </row>
-    <row r="187" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="CP187" s="13"/>
       <c r="CQ187" s="13"/>
@@ -38390,8 +38782,9 @@
       <c r="CZ187" s="13"/>
       <c r="DA187" s="13"/>
       <c r="DB187" s="13"/>
+      <c r="DC187" s="13"/>
     </row>
-    <row r="188" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP188" s="13"/>
       <c r="CQ188" s="13"/>
       <c r="CR188" s="13"/>
@@ -38405,8 +38798,9 @@
       <c r="CZ188" s="13"/>
       <c r="DA188" s="13"/>
       <c r="DB188" s="13"/>
+      <c r="DC188" s="13"/>
     </row>
-    <row r="189" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
         <v>67</v>
       </c>
@@ -38423,10 +38817,11 @@
       <c r="CZ189" s="13"/>
       <c r="DA189" s="13"/>
       <c r="DB189" s="13"/>
+      <c r="DC189" s="13"/>
     </row>
-    <row r="190" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="CP190" s="13"/>
       <c r="CQ190" s="13"/>
@@ -38441,8 +38836,9 @@
       <c r="CZ190" s="13"/>
       <c r="DA190" s="13"/>
       <c r="DB190" s="13"/>
+      <c r="DC190" s="13"/>
     </row>
-    <row r="191" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
         <v>59</v>
       </c>
@@ -38459,8 +38855,9 @@
       <c r="CZ191" s="13"/>
       <c r="DA191" s="13"/>
       <c r="DB191" s="13"/>
+      <c r="DC191" s="13"/>
     </row>
-    <row r="192" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP192" s="13"/>
       <c r="CQ192" s="13"/>
       <c r="CR192" s="13"/>
@@ -38474,8 +38871,9 @@
       <c r="CZ192" s="13"/>
       <c r="DA192" s="13"/>
       <c r="DB192" s="13"/>
+      <c r="DC192" s="13"/>
     </row>
-    <row r="193" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A193" s="6"/>
       <c r="B193" s="6">
         <v>2000</v>
@@ -38636,8 +39034,9 @@
       <c r="DB193" s="14">
         <v>2026</v>
       </c>
+      <c r="DC193" s="14"/>
     </row>
-    <row r="194" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A194" s="3" t="s">
         <v>37</v>
       </c>
@@ -38956,8 +39355,11 @@
       <c r="DB194" s="15" t="s">
         <v>2</v>
       </c>
+      <c r="DC194" s="15" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="195" spans="1:106" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:107" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="4"/>
       <c r="CP195" s="13"/>
       <c r="CQ195" s="13"/>
@@ -38972,8 +39374,9 @@
       <c r="CZ195" s="13"/>
       <c r="DA195" s="13"/>
       <c r="DB195" s="13"/>
+      <c r="DC195" s="13"/>
     </row>
-    <row r="196" spans="1:106" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:107" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
         <v>38</v>
       </c>
@@ -39290,10 +39693,13 @@
         <v>17.793145846832957</v>
       </c>
       <c r="DB196" s="23">
-        <v>17.58678233944643</v>
+        <v>17.593018218908085</v>
+      </c>
+      <c r="DC196" s="23">
+        <v>18.219998346525443</v>
       </c>
     </row>
-    <row r="197" spans="1:106" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:107" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
         <v>39</v>
       </c>
@@ -39610,10 +40016,13 @@
         <v>4.4255479594724934</v>
       </c>
       <c r="DB197" s="23">
-        <v>6.3808933398207852</v>
+        <v>6.3871506359235219</v>
+      </c>
+      <c r="DC197" s="23">
+        <v>4.6080175400383947</v>
       </c>
     </row>
-    <row r="198" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
         <v>40</v>
       </c>
@@ -39930,10 +40339,13 @@
         <v>3.8192372495396518</v>
       </c>
       <c r="DB198" s="23">
-        <v>4.8774052136960435</v>
+        <v>4.8827547657867791</v>
+      </c>
+      <c r="DC198" s="23">
+        <v>4.1044669025284994</v>
       </c>
     </row>
-    <row r="199" spans="1:106" s="9" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:107" s="9" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="5" t="s">
         <v>41</v>
       </c>
@@ -40250,10 +40662,13 @@
         <v>1.383897113254789</v>
       </c>
       <c r="DB199" s="23">
-        <v>2.0972303090273812</v>
+        <v>2.0762024231547875</v>
+      </c>
+      <c r="DC199" s="23">
+        <v>1.2872105596393844</v>
       </c>
     </row>
-    <row r="200" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
         <v>42</v>
       </c>
@@ -40570,10 +40985,13 @@
         <v>4.7389735971064075</v>
       </c>
       <c r="DB200" s="23">
-        <v>5.1379024389970409</v>
+        <v>5.1005721100195931</v>
+      </c>
+      <c r="DC200" s="23">
+        <v>4.7884637493550608</v>
       </c>
     </row>
-    <row r="201" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
         <v>43</v>
       </c>
@@ -40890,10 +41308,13 @@
         <v>1.2936771828241524</v>
       </c>
       <c r="DB201" s="23">
-        <v>1.0604924883286726</v>
+        <v>1.0502726746489266</v>
+      </c>
+      <c r="DC201" s="23">
+        <v>3.9808628863947932</v>
       </c>
     </row>
-    <row r="202" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
         <v>44</v>
       </c>
@@ -41210,10 +41631,13 @@
         <v>2.0539031266357486</v>
       </c>
       <c r="DB202" s="23">
-        <v>1.3901605127412224</v>
+        <v>1.3476180721303939</v>
+      </c>
+      <c r="DC202" s="23">
+        <v>0.94752377565380763</v>
       </c>
     </row>
-    <row r="203" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
         <v>45</v>
       </c>
@@ -41530,10 +41954,13 @@
         <v>1.3741078498925792</v>
       </c>
       <c r="DB203" s="23">
-        <v>1.1273241772234059</v>
+        <v>1.1524686291102122</v>
+      </c>
+      <c r="DC203" s="23">
+        <v>0.32248925953580232</v>
       </c>
     </row>
-    <row r="204" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
         <v>46</v>
       </c>
@@ -41850,10 +42277,13 @@
         <v>1.4762365475314698</v>
       </c>
       <c r="DB204" s="23">
-        <v>0.79249058154229424</v>
+        <v>0.81250770469911049</v>
+      </c>
+      <c r="DC204" s="23">
+        <v>1.7003786113533184</v>
       </c>
     </row>
-    <row r="205" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
         <v>47</v>
       </c>
@@ -42170,10 +42600,13 @@
         <v>0.74383093278394641</v>
       </c>
       <c r="DB205" s="23">
-        <v>0.37427327307010111</v>
+        <v>0.36768858997581921</v>
+      </c>
+      <c r="DC205" s="23">
+        <v>0.68998549658766783</v>
       </c>
     </row>
-    <row r="206" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
         <v>48</v>
       </c>
@@ -42490,10 +42923,13 @@
         <v>0.2295689765582227</v>
       </c>
       <c r="DB206" s="23">
-        <v>0.15795721564786547</v>
+        <v>0.1557217662766919</v>
+      </c>
+      <c r="DC206" s="23">
+        <v>9.5699754142730992E-2</v>
       </c>
     </row>
-    <row r="207" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
         <v>49</v>
       </c>
@@ -42810,10 +43246,13 @@
         <v>7.9659349941281432E-2</v>
       </c>
       <c r="DB207" s="23">
-        <v>4.4908624053900906E-2</v>
+        <v>4.6920975826125491E-2</v>
+      </c>
+      <c r="DC207" s="23">
+        <v>3.0608079817566372E-2</v>
       </c>
     </row>
-    <row r="208" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
         <v>50</v>
       </c>
@@ -43130,10 +43569,13 @@
         <v>0.10316155039558732</v>
       </c>
       <c r="DB208" s="23">
-        <v>0.11035987723650514</v>
+        <v>0.11058511460985433</v>
+      </c>
+      <c r="DC208" s="23">
+        <v>3.2899662663071365E-2</v>
       </c>
     </row>
-    <row r="209" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
         <v>51</v>
       </c>
@@ -43450,10 +43892,13 @@
         <v>5.9346454092191818</v>
       </c>
       <c r="DB209" s="23">
-        <v>5.5969843830117219</v>
+        <v>5.5334948215920994</v>
+      </c>
+      <c r="DC209" s="23">
+        <v>3.5902230753610564</v>
       </c>
     </row>
-    <row r="210" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
         <v>52</v>
       </c>
@@ -43770,10 +44215,13 @@
         <v>13.447566209568276</v>
       </c>
       <c r="DB210" s="23">
-        <v>11.84145666132715</v>
+        <v>11.992640610165232</v>
+      </c>
+      <c r="DC210" s="23">
+        <v>13.518801148302661</v>
       </c>
     </row>
-    <row r="211" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
         <v>53</v>
       </c>
@@ -44090,10 +44538,13 @@
         <v>12.678286211707013</v>
       </c>
       <c r="DB211" s="23">
-        <v>16.787417979646499</v>
+        <v>16.842448821131054</v>
+      </c>
+      <c r="DC211" s="23">
+        <v>10.415881278928632</v>
       </c>
     </row>
-    <row r="212" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
         <v>54</v>
       </c>
@@ -44410,10 +44861,13 @@
         <v>4.1117662427894812</v>
       </c>
       <c r="DB212" s="23">
-        <v>4.1065167245083058</v>
+        <v>4.1194391878603156</v>
+      </c>
+      <c r="DC212" s="23">
+        <v>2.8364500760229423</v>
       </c>
     </row>
-    <row r="213" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
         <v>55</v>
       </c>
@@ -44730,10 +45184,13 @@
         <v>1.6878383526709711E-2</v>
       </c>
       <c r="DB213" s="23">
-        <v>4.8162912587409228E-2</v>
+        <v>5.0556234969843412E-2</v>
+      </c>
+      <c r="DC213" s="23">
+        <v>3.8663483818524309E-2</v>
       </c>
     </row>
-    <row r="214" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
         <v>56</v>
       </c>
@@ -45050,10 +45507,13 @@
         <v>11.0475948427648</v>
       </c>
       <c r="DB214" s="23">
-        <v>11.1485217964337</v>
+        <v>11.015810991147244</v>
+      </c>
+      <c r="DC214" s="23">
+        <v>10.987536041782427</v>
       </c>
     </row>
-    <row r="215" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="s">
         <v>57</v>
       </c>
@@ -45370,11 +45830,14 @@
         <v>13.248315417655231</v>
       </c>
       <c r="DB215" s="23">
-        <v>9.3327591516535602</v>
+        <v>9.3621276520642862</v>
+      </c>
+      <c r="DC215" s="23">
+        <v>17.803840271548214</v>
       </c>
     </row>
-    <row r="216" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" spans="1:106" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" spans="1:107" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="5" t="s">
         <v>62</v>
       </c>
@@ -45693,8 +46156,11 @@
       <c r="DB217" s="23">
         <v>100</v>
       </c>
+      <c r="DC217" s="23">
+        <v>100</v>
+      </c>
     </row>
-    <row r="218" spans="1:106" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:107" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="10"/>
       <c r="B218" s="10"/>
       <c r="C218" s="10"/>
@@ -45801,8 +46267,9 @@
       <c r="CZ218" s="19"/>
       <c r="DA218" s="19"/>
       <c r="DB218" s="19"/>
+      <c r="DC218" s="19"/>
     </row>
-    <row r="219" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
         <v>6</v>
       </c>
@@ -45819,10 +46286,11 @@
       <c r="CZ219" s="13"/>
       <c r="DA219" s="13"/>
       <c r="DB219" s="13"/>
+      <c r="DC219" s="13"/>
     </row>
-    <row r="220" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
         <v>0</v>
       </c>
@@ -45839,8 +46307,9 @@
       <c r="CZ222" s="13"/>
       <c r="DA222" s="13"/>
       <c r="DB222" s="13"/>
+      <c r="DC222" s="13"/>
     </row>
-    <row r="223" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
         <v>8</v>
       </c>
@@ -45857,10 +46326,11 @@
       <c r="CZ223" s="13"/>
       <c r="DA223" s="13"/>
       <c r="DB223" s="13"/>
+      <c r="DC223" s="13"/>
     </row>
-    <row r="224" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="CP224" s="13"/>
       <c r="CQ224" s="13"/>
@@ -45875,8 +46345,9 @@
       <c r="CZ224" s="13"/>
       <c r="DA224" s="13"/>
       <c r="DB224" s="13"/>
+      <c r="DC224" s="13"/>
     </row>
-    <row r="225" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP225" s="13"/>
       <c r="CQ225" s="13"/>
       <c r="CR225" s="13"/>
@@ -45890,8 +46361,9 @@
       <c r="CZ225" s="13"/>
       <c r="DA225" s="13"/>
       <c r="DB225" s="13"/>
+      <c r="DC225" s="13"/>
     </row>
-    <row r="226" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A226" s="1" t="s">
         <v>68</v>
       </c>
@@ -45908,10 +46380,11 @@
       <c r="CZ226" s="13"/>
       <c r="DA226" s="13"/>
       <c r="DB226" s="13"/>
+      <c r="DC226" s="13"/>
     </row>
-    <row r="227" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="CP227" s="13"/>
       <c r="CQ227" s="13"/>
@@ -45926,8 +46399,9 @@
       <c r="CZ227" s="13"/>
       <c r="DA227" s="13"/>
       <c r="DB227" s="13"/>
+      <c r="DC227" s="13"/>
     </row>
-    <row r="228" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A228" s="1" t="s">
         <v>60</v>
       </c>
@@ -45944,8 +46418,9 @@
       <c r="CZ228" s="13"/>
       <c r="DA228" s="13"/>
       <c r="DB228" s="13"/>
+      <c r="DC228" s="13"/>
     </row>
-    <row r="229" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CP229" s="13"/>
       <c r="CQ229" s="13"/>
       <c r="CR229" s="13"/>
@@ -45959,8 +46434,9 @@
       <c r="CZ229" s="13"/>
       <c r="DA229" s="13"/>
       <c r="DB229" s="13"/>
+      <c r="DC229" s="13"/>
     </row>
-    <row r="230" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A230" s="6"/>
       <c r="B230" s="6">
         <v>2000</v>
@@ -46121,8 +46597,9 @@
       <c r="DB230" s="14">
         <v>2026</v>
       </c>
+      <c r="DC230" s="14"/>
     </row>
-    <row r="231" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A231" s="3" t="s">
         <v>37</v>
       </c>
@@ -46441,8 +46918,11 @@
       <c r="DB231" s="15" t="s">
         <v>2</v>
       </c>
+      <c r="DC231" s="15" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="232" spans="1:106" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:107" s="1" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="4"/>
       <c r="CP232" s="13"/>
       <c r="CQ232" s="13"/>
@@ -46457,8 +46937,9 @@
       <c r="CZ232" s="13"/>
       <c r="DA232" s="13"/>
       <c r="DB232" s="13"/>
+      <c r="DC232" s="13"/>
     </row>
-    <row r="233" spans="1:106" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:107" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="s">
         <v>38</v>
       </c>
@@ -46775,10 +47256,13 @@
         <v>23.948927704756766</v>
       </c>
       <c r="DB233" s="23">
-        <v>19.267409587924082</v>
+        <v>19.246976865436309</v>
+      </c>
+      <c r="DC233" s="23">
+        <v>20.312469458969833</v>
       </c>
     </row>
-    <row r="234" spans="1:106" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:107" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="1" t="s">
         <v>39</v>
       </c>
@@ -47095,10 +47579,13 @@
         <v>4.5908846175203815</v>
       </c>
       <c r="DB234" s="23">
-        <v>6.5526694999928097</v>
+        <v>6.5595267226078908</v>
+      </c>
+      <c r="DC234" s="23">
+        <v>4.6579675936506977</v>
       </c>
     </row>
-    <row r="235" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
         <v>40</v>
       </c>
@@ -47415,10 +47902,13 @@
         <v>4.0478456361407371</v>
       </c>
       <c r="DB235" s="23">
-        <v>5.7630870793700231</v>
+        <v>5.7691406879896157</v>
+      </c>
+      <c r="DC235" s="23">
+        <v>3.0949284399419064</v>
       </c>
     </row>
-    <row r="236" spans="1:106" s="9" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:107" s="9" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="5" t="s">
         <v>41</v>
       </c>
@@ -47735,10 +48225,13 @@
         <v>1.2320419077770022</v>
       </c>
       <c r="DB236" s="23">
-        <v>3.1404012264958774</v>
+        <v>3.1436999354832129</v>
+      </c>
+      <c r="DC236" s="23">
+        <v>2.4057748567138533</v>
       </c>
     </row>
-    <row r="237" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="1" t="s">
         <v>42</v>
       </c>
@@ -48055,10 +48548,13 @@
         <v>6.0874489002748531</v>
       </c>
       <c r="DB237" s="23">
-        <v>6.2865826783736241</v>
+        <v>6.2931861723978315</v>
+      </c>
+      <c r="DC237" s="23">
+        <v>6.9831060793682527</v>
       </c>
     </row>
-    <row r="238" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
         <v>43</v>
       </c>
@@ -48375,10 +48871,13 @@
         <v>1.4357649170483238</v>
       </c>
       <c r="DB238" s="23">
-        <v>1.2245748196726791</v>
+        <v>1.2258611262270676</v>
+      </c>
+      <c r="DC238" s="23">
+        <v>4.3029135100344931</v>
       </c>
     </row>
-    <row r="239" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="1" t="s">
         <v>44</v>
       </c>
@@ -48695,10 +49194,13 @@
         <v>1.69355265088896</v>
       </c>
       <c r="DB239" s="23">
-        <v>1.713963370971531</v>
+        <v>1.7157637365209806</v>
+      </c>
+      <c r="DC239" s="23">
+        <v>1.5134173689317081</v>
       </c>
     </row>
-    <row r="240" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="1" t="s">
         <v>45</v>
       </c>
@@ -49015,10 +49517,13 @@
         <v>0.49036001337683605</v>
       </c>
       <c r="DB240" s="23">
-        <v>0.6919069616330904</v>
+        <v>0.71168376889855989</v>
+      </c>
+      <c r="DC240" s="23">
+        <v>0.1468830165568443</v>
       </c>
     </row>
-    <row r="241" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="1" t="s">
         <v>46</v>
       </c>
@@ -49335,10 +49840,13 @@
         <v>0.98403134223621036</v>
       </c>
       <c r="DB241" s="23">
-        <v>0.76379227154847917</v>
+        <v>0.7645945671610469</v>
+      </c>
+      <c r="DC241" s="23">
+        <v>1.289583022425201</v>
       </c>
     </row>
-    <row r="242" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="1" t="s">
         <v>47</v>
       </c>
@@ -49655,10 +50163,13 @@
         <v>0.60734559487739326</v>
       </c>
       <c r="DB242" s="23">
-        <v>0.2316066481298385</v>
+        <v>0.23184993024273473</v>
+      </c>
+      <c r="DC242" s="23">
+        <v>0.54727582551060272</v>
       </c>
     </row>
-    <row r="243" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="s">
         <v>48</v>
       </c>
@@ -49975,10 +50486,13 @@
         <v>0.11348594717417194</v>
       </c>
       <c r="DB243" s="23">
-        <v>0.1872515442915644</v>
+        <v>0.18744823532658514</v>
+      </c>
+      <c r="DC243" s="23">
+        <v>0.13893507545555289</v>
       </c>
     </row>
-    <row r="244" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
         <v>49</v>
       </c>
@@ -50295,10 +50809,13 @@
         <v>8.5504683577113966E-2</v>
       </c>
       <c r="DB244" s="23">
-        <v>8.7846071891133248E-2</v>
+        <v>8.793834634936612E-2</v>
+      </c>
+      <c r="DC244" s="23">
+        <v>7.4183621635080715E-2</v>
       </c>
     </row>
-    <row r="245" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="1" t="s">
         <v>50</v>
       </c>
@@ -50615,10 +51132,13 @@
         <v>0.22975389477639285</v>
       </c>
       <c r="DB245" s="23">
-        <v>0.18792094108239149</v>
+        <v>0.18811833525899707</v>
+      </c>
+      <c r="DC245" s="23">
+        <v>9.679015744258794E-2</v>
       </c>
     </row>
-    <row r="246" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="1" t="s">
         <v>51</v>
       </c>
@@ -50935,10 +51455,13 @@
         <v>4.5284656109117654</v>
       </c>
       <c r="DB246" s="23">
-        <v>6.1848522989133636</v>
+        <v>6.2064400449882271</v>
+      </c>
+      <c r="DC246" s="23">
+        <v>5.2289633896977588</v>
       </c>
     </row>
-    <row r="247" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="1" t="s">
         <v>52</v>
       </c>
@@ -51255,10 +51778,13 @@
         <v>8.9899121619062541</v>
       </c>
       <c r="DB247" s="23">
-        <v>10.220188678719213</v>
+        <v>10.227492467013793</v>
+      </c>
+      <c r="DC247" s="23">
+        <v>9.8885636995813364</v>
       </c>
     </row>
-    <row r="248" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="s">
         <v>53</v>
       </c>
@@ -51575,10 +52101,13 @@
         <v>12.669086368381171</v>
       </c>
       <c r="DB248" s="23">
-        <v>13.881587077031499</v>
+        <v>13.896168446299681</v>
+      </c>
+      <c r="DC248" s="23">
+        <v>11.323049481497961</v>
       </c>
     </row>
-    <row r="249" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="1" t="s">
         <v>54</v>
       </c>
@@ -51895,10 +52424,13 @@
         <v>4.0975822613219952</v>
       </c>
       <c r="DB249" s="23">
-        <v>4.65464194270369</v>
+        <v>4.6595312286362844</v>
+      </c>
+      <c r="DC249" s="23">
+        <v>4.2122842306210906</v>
       </c>
     </row>
-    <row r="250" spans="1:106" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:107" s="9" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="1" t="s">
         <v>55</v>
       </c>
@@ -52215,10 +52747,13 @@
         <v>5.09332286097436E-2</v>
       </c>
       <c r="DB250" s="23">
-        <v>0.17090680336249753</v>
+        <v>0.17851751554506001</v>
+      </c>
+      <c r="DC250" s="23">
+        <v>0.14025420174930489</v>
       </c>
     </row>
-    <row r="251" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="1" t="s">
         <v>56</v>
       </c>
@@ -52535,10 +53070,13 @@
         <v>12.855551290762934</v>
       </c>
       <c r="DB251" s="23">
-        <v>9.6410736861590127</v>
+        <v>9.5487161748007274</v>
+      </c>
+      <c r="DC251" s="23">
+        <v>9.5234794689331519</v>
       </c>
     </row>
-    <row r="252" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="1" t="s">
         <v>57</v>
       </c>
@@ -52855,11 +53393,14 @@
         <v>11.261521267680999</v>
       </c>
       <c r="DB252" s="23">
-        <v>9.1477368117336066</v>
+        <v>9.1573456928160262</v>
+      </c>
+      <c r="DC252" s="23">
+        <v>14.119177501282799</v>
       </c>
     </row>
-    <row r="253" spans="1:106" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" spans="1:106" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:107" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" spans="1:107" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="5" t="s">
         <v>62</v>
       </c>
@@ -53178,8 +53719,11 @@
       <c r="DB254" s="23">
         <v>100</v>
       </c>
+      <c r="DC254" s="23">
+        <v>100</v>
+      </c>
     </row>
-    <row r="255" spans="1:106" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:107" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="10"/>
       <c r="B255" s="10"/>
       <c r="C255" s="10"/>
@@ -53286,8 +53830,9 @@
       <c r="CZ255" s="19"/>
       <c r="DA255" s="19"/>
       <c r="DB255" s="19"/>
+      <c r="DC255" s="19"/>
     </row>
-    <row r="256" spans="1:106" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A256" s="1" t="s">
         <v>6</v>
       </c>
@@ -53304,8 +53849,9 @@
       <c r="CZ256" s="13"/>
       <c r="DA256" s="13"/>
       <c r="DB256" s="13"/>
+      <c r="DC256" s="13"/>
     </row>
-    <row r="257" spans="1:106" s="12" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:107" s="12" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="1"/>
       <c r="CP257" s="26"/>
       <c r="CQ257" s="26"/>
@@ -53320,8 +53866,9 @@
       <c r="CZ257" s="27"/>
       <c r="DA257" s="27"/>
       <c r="DB257" s="27"/>
+      <c r="DC257" s="27"/>
     </row>
-    <row r="258" spans="1:106" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:107" x14ac:dyDescent="0.2">
       <c r="CT258" s="28"/>
       <c r="CU258" s="28"/>
       <c r="CV258" s="28"/>
@@ -53331,49 +53878,33 @@
       <c r="CZ258" s="28"/>
       <c r="DA258" s="28"/>
       <c r="DB258" s="28"/>
+      <c r="DC258" s="28"/>
     </row>
-    <row r="259" spans="1:106" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:107" x14ac:dyDescent="0.2">
       <c r="CT259" s="28"/>
       <c r="CU259" s="28"/>
       <c r="CV259" s="28"/>
       <c r="CW259" s="28"/>
-      <c r="CX259" s="28"/>
-      <c r="CY259" s="28"/>
-      <c r="CZ259" s="28"/>
-      <c r="DA259" s="28"/>
-      <c r="DB259" s="28"/>
     </row>
-    <row r="260" spans="1:106" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:107" x14ac:dyDescent="0.2">
       <c r="CT260" s="28"/>
       <c r="CU260" s="28"/>
       <c r="CV260" s="28"/>
       <c r="CW260" s="28"/>
-      <c r="CX260" s="28"/>
-      <c r="CY260" s="28"/>
-      <c r="CZ260" s="28"/>
-      <c r="DA260" s="28"/>
     </row>
-    <row r="261" spans="1:106" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:107" x14ac:dyDescent="0.2">
       <c r="CS261" s="28"/>
       <c r="CT261" s="28"/>
       <c r="CU261" s="28"/>
       <c r="CV261" s="28"/>
       <c r="CW261" s="28"/>
-      <c r="CX261" s="28"/>
-      <c r="CY261" s="28"/>
-      <c r="CZ261" s="28"/>
-      <c r="DA261" s="28"/>
     </row>
-    <row r="262" spans="1:106" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:107" x14ac:dyDescent="0.2">
       <c r="CS262" s="28"/>
       <c r="CT262" s="28"/>
       <c r="CU262" s="28"/>
       <c r="CV262" s="28"/>
       <c r="CW262" s="28"/>
-      <c r="CX262" s="28"/>
-      <c r="CY262" s="28"/>
-      <c r="CZ262" s="28"/>
-      <c r="DA262" s="28"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
